--- a/ml/бодлогын_сан.xlsx
+++ b/ml/бодлогын_сан.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нэр_томьёо" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Бодлого'!$A$1:$O$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Бодлого'!$A$1:$P$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сэдвүүд'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сэдвийн_граф'!$A$1:$D$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Нэр_томьёо'!$A$1:$D$33</definedName>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:P201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,7 @@
     <col width="38" customWidth="1" min="13" max="13"/>
     <col width="38" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,6 +533,11 @@
           <t>sympy_шалгалт</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>бодолтын_алхам</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -603,6 +609,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Ижил суурьтай зэргийг үржүүлэхэд илтгэгч нэмэгдэнэ: $a^m \cdot a^n = a^{m+n}$. || $2^3 \cdot 2^2 = 2^{3+2} = 2^5$. || $2^5 = 32$.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -674,6 +685,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Хуваарийг ижил болгоно: 4 ба 6-ийн ХБЕХ нь 12. || $\frac{3}{4} = \frac{9}{12}$, $\frac{1}{6} = \frac{2}{12}$. || $\frac{9}{12} + \frac{2}{12} = \frac{11}{12}$.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -745,6 +761,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Хүртвэр: $3^4 \cdot 3^{-2} = 3^{4-2} = 3^2$. || Хуваах: $3^2 : 3^1 = 3^{2-1} = 3^1$. || Хариу: $3$.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -816,6 +837,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Язгуур доорхыг бүтэн квадратаар задална: $50 = 25 \cdot 2$, $18 = 9 \cdot 2$. || $\sqrt{50} = 5\sqrt{2}$, $\sqrt{18} = 3\sqrt{2}$. || $5\sqrt{2} - 3\sqrt{2} = 2\sqrt{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -887,6 +913,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Сөрөг илтгэгч урвуулна: $(\tfrac{1}{2})^{-3} = 2^3 = 8$. || $16^{1/2} = \sqrt{16} = 4$. || $8 + 4 = 12$.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -958,6 +989,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>$a^{m/n} = (\sqrt[n]{a})^m$: $27^{2/3} = (\sqrt[3]{27})^2 = 3^2 = 9$. || $8^{1/3} = \sqrt[3]{8} = 2$. || $9 - 2 = 7$.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1033,6 +1069,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Хаалт задлах: $3(x-4) = 3x - 12$. || $3x - 12 + 2x$. || Төсөөтэй гишүүд: $5x - 12$.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1108,6 +1149,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>$a$-тай гишүүд: $4a + a = 5a$. || $b$-тэй гишүүд: $-2b + 5b = 3b$. || Хариу: $5a + 3b$.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1183,6 +1229,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>$9 = 3^2$ тул энэ нь квадратуудын ялгавар. || $a^2 - b^2 = (a-b)(a+b)$, энд $a = x$, $b = 3$. || $(x-3)(x+3)$.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1258,6 +1309,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>$(a+b)^2 = a^2 + 2ab + b^2$. || $a = x$, $b = 3$: $x^2 + 2 \cdot x \cdot 3 + 3^2$. || $x^2 + 6x + 9$.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1333,6 +1389,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Үржвэр нь 6, нийлбэр нь $-5$ болох хоёр тоо хайна. || $-2$ ба $-3$: $(-2)(-3) = 6$, $-2 + (-3) = -5$. || $(x-2)(x-3)$.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1408,6 +1469,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Хүртвэрийг задална: $x^2 - 4 = (x-2)(x+2)$. || $\frac{(x-2)(x+2)}{x-2}$ — $x \ne 2$ тул $(x-2)$-оор хураана. || Хариу: $x + 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1483,6 +1549,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>5-ыг баруун тал руу шилжүүлнэ (тэмдэг солигдоно): $2x = 13 - 5$. || $2x = 8$. || $x = 8 : 2 = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1558,6 +1629,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>$x$-тэй гишүүдийг зүүн, тоонуудыг баруун тийш: $3x - 2x = 1 + 7$. || $x = 8$. || Шалгалт: $3 \cdot 8 - 7 = 17 = 2 \cdot 8 + 1$ ✓</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1633,6 +1709,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Хөндлөн үржүүлнэ: $5(x-1) = 3(x+1)$. || $5x - 5 = 3x + 3$ → $2x = 8$. || $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1708,6 +1789,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Үзэгний үнийг $x$ гэвэл дэвтэр $x + 300$. || $2(x+300) + 3x = 3600$ → $5x + 600 = 3600$. || $5x = 3000$ → $x = 600$ төгрөг.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1783,6 +1869,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр тэгшитгэлийг нэмнэ: $2x = 14$ → $x = 7$. || $x = 7$-г эхнийхэд орлуулна: $7 + y = 10$. || $y = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1858,6 +1949,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Хүүгийн насыг $x$ гэвэл аав $4x$. || 5 жилийн дараа: $4x + 5 = 3(x + 5)$ → $4x + 5 = 3x + 15$. || $x = 10$ настай.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1933,6 +2029,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 = 16$. || Квадрат нь 16 болох тоо хоёр: $4$ ба $-4$. || $x = -4$; $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2008,6 +2109,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>$x$-ийг хаалтын өмнө гаргана: $x(x-5) = 0$. || Үржвэр 0 бол аль нэг үржигдэхүүн 0: $x = 0$ эсвэл $x - 5 = 0$. || $x = 0$; $x = 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2083,6 +2189,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Виет: үржвэр 12, нийлбэр 7. || $3 \cdot 4 = 12$, $3 + 4 = 7$. || $x = 3$; $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2158,6 +2269,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>$D = b^2 - 4ac = 9 + 16 = 25$, $\sqrt{D} = 5$. || $x = \frac{-3 \pm 5}{2 \cdot 2}$. || $x_1 = \frac{2}{4} = \frac{1}{2}$, $x_2 = \frac{-8}{4} = -2$.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2233,6 +2349,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>$D = 4 + 4 = 8$, $\sqrt{8} = 2\sqrt{2}$. || $x = \frac{2 \pm 2\sqrt{2}}{2}$. || $x = 1 \pm \sqrt{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2308,6 +2429,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Давхар язгуур ⇔ $D = 0$. || $D = k^2 - 4 \cdot 9 = k^2 - 36 = 0$. || $k = \pm 6$.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2383,6 +2509,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>$2x &gt; 5 + 3$. || $2x &gt; 8$. || $x &gt; 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2458,6 +2589,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>$-3x \le -6$. || Сөрөг тоонд хуваахад тэмдэг эргэнэ. || $x \ge 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2533,6 +2669,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 4-өөр үржүүлнэ: $2(x-1) &lt; x + 3$. || $2x - 2 &lt; x + 3$ → $x &lt; 5$. || Хариу: $x &lt; 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2608,6 +2749,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>$|t| &lt; a$ ⇔ $-a &lt; t &lt; a$. || $-3 &lt; x - 2 &lt; 3$. || $-1 &lt; x &lt; 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2683,6 +2829,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Язгуурууд: $x^2 - 5x + 6 = (x-2)(x-3)$ → $2$ ба $3$. || Дээш харсан парабол язгууруудын хооронд сөрөг. || $2 &lt; x &lt; 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2758,6 +2909,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>$(x-2)(x+2) \ge 0$, язгуурууд $\pm 2$. || Дээш харсан парабол язгууруудын гадна эерэг. || $x \le -2$ эсвэл $x \ge 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2833,6 +2989,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>$x$-ийн оронд 4 орлуулна: $f(4) = 3 \cdot 4 - 2$. || $12 - 2$. || $f(4) = 10$.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2908,6 +3069,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>$y = kx + b$ хэлбэрт $k$ нь өнцгийн коэффициент. || $y = 2x + 1$ → $k = 2$, $b = 1$. || Хариу: $2$.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2983,6 +3149,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Язгуур доорх илэрхийлэл сөрөг биш байх ёстой: $x - 3 \ge 0$. || $x \ge 3$. || Тодорхойлогдох муж: $[3; +\infty)$.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3058,6 +3229,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>$k = \frac{y_2 - y_1}{x_2 - x_1} = \frac{7-3}{3-1} = 2$. || $y = 2x + b$-д $(1;3)$ орлуулна: $3 = 2 + b$ → $b = 1$. || $y = 2x + 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3133,6 +3309,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Оройн абсцисс $x_0 = -\frac{b}{2a} = \frac{4}{2} = 2$. || $y_0 = f(2) = 4 - 8 + 1 = -3$. || Орой: $(2; -3)$.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3208,6 +3389,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Дотоод функц эхлээд: $g(2) = 2^2 = 4$. || $f(4) = 2 \cdot 4 + 3$. || $f(g(2)) = 11$.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3283,6 +3469,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>$8 = 2^3$. || $2^x = 2^3$ → суурь ижил тул илтгэгчүүд тэнцүү. || $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3358,6 +3549,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{1}{9} = 3^{-2}$. || $3^x = 3^{-2}$. || $x = -2$.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3433,6 +3629,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>$4 = 2^2$, $32 = 2^5$. || $(2^2)^x = 2^5$ → $2^{2x} = 2^5$. || $2x = 5$ → $x = \frac{5}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3508,6 +3709,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>$125 = 5^3$. || $5^{x+1} = 5^3$ → $x + 1 = 3$. || $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3583,6 +3789,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>$t = 2^x$ ($t &gt; 0$): $t^2 - 3t - 4 = 0$. || $t = 4$ эсвэл $t = -1$ (тохирохгүй). || $2^x = 4$ → $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3658,6 +3869,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>$9^x = (3^x)^2$, $t = 3^x$: $t^2 - 4t + 3 = 0$. || $t = 1$ эсвэл $t = 3$. || $3^x = 1$ → $x = 0$; $3^x = 3$ → $x = 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3733,6 +3949,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 16$: 2-ыг хэдэн зэрэгт дэвшүүлбэл 16? || $2^4 = 16$. || Хариу: $4$.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3808,6 +4029,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>$\lg$ = 10 суурьтай логарифм. || $10^3 = 1000$. || $\lg 1000 = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3883,6 +4109,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 27 = 3$ ($3^3 = 27$). || $\log_3 \frac{1}{3} = -1$ ($3^{-1} = \frac{1}{3}$). || $3 + (-1) = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3958,6 +4189,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Тодорхойлолт: $x - 1 = 2^3$. || $x - 1 = 8$. || $x = 9$ (шалгалт: $9 - 1 = 8 &gt; 0$ ✓).</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4033,6 +4269,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>ТМ: $x &gt; 2$. $\log_2 [x(x-2)] = 3$. || $x(x-2) = 8$ → $x^2 - 2x - 8 = 0$ → $x = 4$, $x = -2$. || $x = -2$ ТМ-д орохгүй → $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4108,6 +4349,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>$\log_a b - \log_a c = \log_a \frac{b}{c}$. || $\log_5 \frac{50}{2} = \log_5 25$. || $5^2 = 25$ → $2$.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4183,6 +4429,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>$30°$ тусгай өнцөг. || Хүснэгт: $\sin 30° = \frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4258,6 +4509,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>$\cos 60° = \frac{1}{2}$. || $\sin 90° = 1$. || $\frac{1}{2} + 1 = \frac{3}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4333,6 +4589,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>$\sin^2\alpha + \cos^2\alpha = 1$ → $\cos^2\alpha = 1 - \frac{9}{25} = \frac{16}{25}$. || Хурц өнцөгт $\cos\alpha &gt; 0$. || $\cos\alpha = \frac{4}{5}$.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4408,6 +4669,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{tg}45° = 1$, $\cos 0° = 1$, $\sin 30° = \frac{1}{2}$. || $1 \cdot 1 - (\tfrac{1}{2})^2 = 1 - \frac{1}{4}$. || $\frac{3}{4}$.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4483,6 +4749,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Нэгж тойрог дээр $\sin x = \frac{1}{2}$: I мөчлөгт $x = \frac{\pi}{6}$. || II мөчлөгт $x = \pi - \frac{\pi}{6} = \frac{5\pi}{6}$. || $x = \frac{\pi}{6}$; $x = \frac{5\pi}{6}$.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4558,6 +4829,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>$1 - \cos^2\alpha = \sin^2\alpha$. || $\frac{\sin^2\alpha}{\sin\alpha}$. || $\sin\alpha$.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4633,6 +4909,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Боломжит үр дүн: 1, 2, 3, 4, 5, 6 — нийт 6. || Тэгш: 2, 4, 6 — 3 ширхэг. || $P = \frac{3}{6} = \frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4708,6 +4989,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Нийт бөмбөг: $3 + 5 = 8$. || Таатай (улаан): 3. || $P = \frac{3}{8}$.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4783,6 +5069,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>5 хүний сэлгэмэл: $P_5 = 5!$. || $5 \cdot 4 \cdot 3 \cdot 2 \cdot 1$. || $120$.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4858,6 +5149,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Дараалал чухал биш → хэсэглэл $C_8^3 = \frac{8!}{3! \cdot 5!}$. || $\frac{8 \cdot 7 \cdot 6}{3 \cdot 2 \cdot 1} = \frac{336}{6}$. || $56$.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4933,6 +5229,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Нийт үр дүн $6 \cdot 6 = 36$. || Нийлбэр 7: (1,6),(2,5),(3,4),(4,3),(5,2),(6,1) — 6 хос. || $P = \frac{6}{36} = \frac{1}{6}$.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5008,6 +5309,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Нийт үр дүн $2^3 = 8$. || Яг 2 сүлд: ССТ, СТС, ТСС — $C_3^2 = 3$. || $P = \frac{3}{8}$.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5079,6 +5385,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>$5 = 5^1$ гэж бичнэ. || $5^2 \cdot 5^1 = 5^{2+1} = 5^3$. || $5^3 = 125$.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5150,6 +5461,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Ижил суурьтай зэргийг хуваахад илтгэгч хасагдана: $a^m : a^n = a^{m-n}$. || $7^{5-3} = 7^2$. || $7^2 = 49$.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5221,6 +5537,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Үйлдлийн дараалал: эхлээд зэрэг $4^2 = 16$. || Дараа нь үржих: $2 \cdot 16 = 32$. || Сүүлд нэмэх: $3 + 32 = 35$.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5292,6 +5613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Үржүүлэхээс өмнө хураана: 2 ба 4-ийг 2-т, 3 ба 9-ийг 3-т. || $\frac{1}{1} \cdot \frac{3}{2}$. || Хариу: $\frac{3}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5363,6 +5689,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>ХБЕХ(6, 4) = 12. || $\frac{5}{6} = \frac{10}{12}$, $\frac{1}{4} = \frac{3}{12}$. || $\frac{10}{12} - \frac{3}{12} = \frac{7}{12}$.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5434,6 +5765,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Зэргийн зэрэг: $(a^m)^n = a^{mn}$, тэгэхээр $(2^3)^2 = 2^6$. || $2^6 : 2^4 = 2^{6-4} = 2^2$. || $2^2 = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5505,6 +5841,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>$2^{-3} = \frac{1}{2^3} = \frac{1}{8}$. || $4^{-1} = \frac{1}{4} = \frac{2}{8}$. || $\frac{1}{8} + \frac{2}{8} = \frac{3}{8}$.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5576,6 +5917,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>$12 = 4 \cdot 3$, $27 = 9 \cdot 3$. || $\sqrt{12} = 2\sqrt{3}$, $\sqrt{27} = 3\sqrt{3}$. || $2\sqrt{3} + 3\sqrt{3} = 5\sqrt{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5647,6 +5993,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>$\sqrt{a} \cdot \sqrt{b} = \sqrt{ab}$. || $\sqrt{3 \cdot 12} = \sqrt{36}$. || $\sqrt{36} = 6$.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5718,6 +6069,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Тоонуудыг тусад нь: $3 \cdot 2 = 6$. || 10-ын зэргүүдийг тусад нь: $10^4 \cdot 10^{-2} = 10^2$. || $6 \cdot 10^2 = 600$.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5789,6 +6145,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>$32 = 2^5$ тул $32^{2/5} = (2^5)^{2/5} = 2^2 = 4$. || $9^{-1/2} = \frac{1}{\sqrt{9}} = \frac{1}{3}$. || $4 + \frac{1}{3} = \frac{13}{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5860,6 +6221,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>$6^5 = (2 \cdot 3)^5 = 2^5 \cdot 3^5$. || $\frac{2^5 \cdot 3^5}{2^5 \cdot 3^3} = 3^{5-3}$. || $3^2 = 9$.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5931,6 +6297,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>$(a-b)(a+b) = a^2 - b^2$ томьёо. || $(\sqrt{5})^2 - 1^2 = 5 - 1$. || Хариу: $4$.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6002,6 +6373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Анхны үнийг $x$ гэвэл 20% нэмэгдсэн үнэ $1{,}2x$. || $1{,}2x = 24000$. || $x = 24000 : 1{,}2 = 20000$ төгрөг.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6077,6 +6453,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>$2(3x+1) = 6x + 2$. || $6x + 2 - 4x$. || $2x + 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -6152,6 +6533,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Хаалтын өмнөх хасах тэмдэг гишүүн бүрийн тэмдгийг солино: $-(x-5) = -x + 5$. || $-x + 5 + 3x$. || $2x + 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6227,6 +6613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>$x^2$-тэй гишүүд: $3x^2 - x^2 = 2x^2$. || $x$-тэй гишүүд: $2x + 4x = 6x$. || $2x^2 + 6x$ ($x^2$ ба $x$ нэгтгэгдэхгүй).</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6302,6 +6693,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Коэффициентуудын ЕХ: $6$ ба $9$ → $3$; $x^2$ ба $x$ → $x$. || Ерөнхий үржигдэхүүн $3x$. || $6x^2 : 3x = 2x$, $9x : 3x = 3$ → $3x(2x+3)$.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6377,6 +6773,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>$x = -2$-ыг хаалттай орлуулна: $(-2)^2 - 3(-2) + 1$. || $(-2)^2 = 4$, $-3 \cdot (-2) = +6$. || $4 + 6 + 1 = 11$.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6452,6 +6853,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>$(a-b)^2 = a^2 - 2ab + b^2$, $a = 2x$, $b = 1$. || $(2x)^2 - 2 \cdot 2x \cdot 1 + 1^2$. || $4x^2 - 4x + 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -6527,6 +6933,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>$(a-b)(a+b) = a^2 - b^2$. || $a = x$, $b = 4$. || $x^2 - 16$.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -6602,6 +7013,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>$4x^2 = (2x)^2$, $25 = 5^2$. || Квадратуудын ялгавар: $(2x)^2 - 5^2$. || $(2x-5)(2x+5)$.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6677,6 +7093,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Үржвэр 10, нийлбэр 7 болох хоёр тоо. || $2 \cdot 5 = 10$, $2 + 5 = 7$. || $(x+2)(x+5)$.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -6752,6 +7173,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр хоёроор бүлэглэнэ: $(x^2 + 3x) + (xy + 3y)$. || $x(x+3) + y(x+3)$. || Ерөнхий хаалт: $(x+3)(x+y)$.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -6827,6 +7253,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Хүртвэр бүтэн квадрат: $x^2 + 6x + 9 = (x+3)^2$. || $\frac{(x+3)^2}{x+3}$, $x \ne -3$. || $x + 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -6902,6 +7333,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Ерөнхий хуваарь $x(x+1)$. || $\frac{x+1}{x(x+1)} + \frac{x}{x(x+1)}$. || $\frac{2x+1}{x(x+1)}$.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -6977,6 +7413,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>$(a+b)^3 = a^3 + 3a^2b + 3ab^2 + b^3$. || $a = x$, $b = 2$: $x^3 + 3x^2 \cdot 2 + 3x \cdot 4 + 8$. || $x^3 + 6x^2 + 12x + 8$.</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7052,6 +7493,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 6x$ нь $(x-3)^2 = x^2 - 6x + 9$-ийн эхлэл. || $x^2 - 6x + 13 = (x-3)^2 - 9 + 13$. || $= (x-3)^2 + 4$, тэгэхээр $b = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7127,6 +7573,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>$5x = 12 + 3$. || $5x = 15$. || $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -7202,6 +7653,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 4-өөр үржүүлнэ. || $x = 6 \cdot 4$. || $x = 24$.</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7277,6 +7733,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>$-2x = 1 - 7$. || $-2x = -6$. || $x = -6 : (-2) = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7352,6 +7813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 3-т хуваана: $x - 2 = 3$. || $x = 3 + 2$. || $x = 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7427,6 +7893,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Хаалт задлах: $2x + 6 = 5x - 6$. || $6 + 6 = 5x - 2x$ → $12 = 3x$. || $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -7502,6 +7973,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 6-аар үржүүлнэ: $3x + 2x = 30$. || $5x = 30$. || $x = 6$.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -7577,6 +8053,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Хөндлөн үржүүлнэ: $3 \cdot 12 = 9x$. || $36 = 9x$. || $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -7652,6 +8133,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Бага тоог $x$ гэвэл $x,\ x+1,\ x+2$. || $3x + 3 = 48$ → $3x = 45$. || $x = 15$.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -7727,6 +8213,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Нэмнэ: $2x = 8$ → $x = 4$. || $4 + y = 7$. || $y = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -7802,6 +8293,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>$y$-ийн коэффициентууд $+1$, $-1$ — нэмнэ: $3x = 9$ → $x = 3$. || $3 - y = 1$. || $y = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -7877,6 +8373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>$x = 2y$-г орлуулна: $3(2y) + 2y = 12$. || $8y = 12$ → $y = \frac{3}{2}$. || $x = 2 \cdot \frac{3}{2} = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -7952,6 +8453,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Бага тоо $x$, их тоо $x + 8$. || $x + x + 8 = 30$ → $2x = 22$. || $x = 11$.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -8027,6 +8533,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Эхний хэсгийн зам: $60 \cdot 2 = 120$ км. || Үлдсэн зам: $280 - 120 = 160$ км, $80t = 160$. || $t = 2$ цаг.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -8102,6 +8613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 2-оор үржүүлнэ: $x + 3 = 4x - 6$. || $3 + 6 = 4x - x$ → $9 = 3x$. || $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -8177,6 +8693,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Квадрат нь 49 болох тоо. || $7^2 = 49$ ба $(-7)^2 = 49$. || $x = \pm 7$.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -8252,6 +8773,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 3-т хуваана: $x^2 - 9 = 0$. || $x^2 = 9$. || $x = \pm 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -8327,6 +8853,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>$x(x+4) = 0$. || $x = 0$ эсвэл $x + 4 = 0$. || $x = -4$; $x = 0$.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -8402,6 +8933,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Үржвэр 6, нийлбэр 5. || $2 \cdot 3 = 6$, $2 + 3 = 5$. || $x = 2$; $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -8477,6 +9013,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>Үржвэр $-15$, нийлбэр $-2$. || $-5 \cdot 3 = -15$, $-5 + 3 = -2$ → $(x+5)(x-3) = 0$. || $x = -5$; $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -8552,6 +9093,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>$D = 36 - 36 = 0$ → ганц (давхар) язгуур. || $x = \frac{-b}{2a} = \frac{6}{2}$. || $x = 3$ (мөн $(x-3)^2 = 0$).</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -8627,6 +9173,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>$D = 25 - 16 = 9$, $\sqrt{D} = 3$. || $x = \frac{5 \pm 3}{4}$. || $x_1 = 2$, $x_2 = \frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -8702,6 +9253,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>$D = b^2 - 4ac = 9 - 20 = -11$. || $D &lt; 0$ бол бодит шийд байхгүй. || Хариу: 0 шийдтэй.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8777,6 +9333,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>Өргөн $x$, урт $x + 3$: $x(x+3) = 40$. || $x^2 + 3x - 40 = 0$ → үржвэр $-40$, нийлбэр 3: $8$ ба $-5$. || $x = 5$ ($x = -8$ урт байж болохгүй).</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -8852,6 +9413,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>$D = 16 - 4 = 12$, $\sqrt{12} = 2\sqrt{3}$. || $x = \frac{-4 \pm 2\sqrt{3}}{2}$. || $x = -2 \pm \sqrt{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -8927,6 +9493,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>Язгуур $x = 2$-ыг орлуулна: $4 - 16 + c = 0$. || $-12 + c = 0$. || $c = 12$.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -9002,6 +9573,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>Виет: $x_1 + x_2 = 7$, $x_1 x_2 = 10$. || $x_1^2 + x_2^2 = (x_1+x_2)^2 - 2x_1x_2$. || $49 - 20 = 29$.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -9077,6 +9653,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>$t = x^2$: $t^2 - 5t + 4 = 0$ → $t = 1$, $t = 4$. || $x^2 = 1$ → $x = \pm 1$; $x^2 = 4$ → $x = \pm 2$. || $x = -2; -1; 1; 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -9152,6 +9733,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>$x(x+1) = 72$ → $x^2 + x - 72 = 0$. || Үржвэр $-72$, нийлбэр 1: $9$ ба $-8$. || $x = 8$ (натурал тоо).</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9227,6 +9813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P118" s="2" t="inlineStr">
+        <is>
+          <t>$x &lt; 9 - 4$. || Тэмдэг хэвээр. || $x &lt; 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -9302,6 +9893,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг 3-т хуваана (эерэг — тэмдэг хэвээр). || $x \ge 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -9377,6 +9973,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр талыг $-2$-т хуваана. || Сөрөг тоонд хуваахад тэмдэг эргэнэ: $x &lt; -4$.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -9452,6 +10053,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>$-x \le 2 - 5 = -3$. || $-1$-ээр үржүүлж тэмдэг эргүүлнэ. || $x \ge 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -9527,6 +10133,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>$2x - 2 &gt; x + 3$. || $2x - x &gt; 3 + 2$. || $x &gt; 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -9602,6 +10213,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>Гурван хэсгээс 3 хасна: $-4 \le 2x &lt; 4$. || Гурван хэсгийг 2-т хуваана. || $-2 \le x &lt; 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -9677,6 +10293,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>$|x| \le 3$ гэдэг нь $x$ нь $-3$ ба $3$-ын хооронд. || $-3 \le x \le 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -9752,6 +10373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>$|t| &gt; a$ ⇔ $t &lt; -a$ эсвэл $t &gt; a$. || $x + 1 &lt; -2$ эсвэл $x + 1 &gt; 2$. || $x &lt; -3$ эсвэл $x &gt; 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -9827,6 +10453,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр нөхцөл зэрэг биелэх ёстой — огтлолцол. || $x &gt; 1$ ба $x \le 4$. || $1 &lt; x \le 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -9902,6 +10533,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>$(x-3)(x+3) &lt; 0$, язгуурууд $\pm 3$. || Язгууруудын хооронд сөрөг. || $-3 &lt; x &lt; 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -9977,6 +10613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>Язгуурууд: $x^2 + x - 6 = (x+3)(x-2)$ → $-3$, $2$. || Дээш харсан парабол, $\ge 0$ гадна талд. || $x \le -3$ эсвэл $x \ge 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -10052,6 +10693,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>Чухал цэгүүд: $x = 2$ (хүртвэр 0), $x = -1$ (хуваарь 0, оруулахгүй). || Мужууд: $x &lt; -1$: $\frac{-}{-} &gt; 0$ ✓; $-1 &lt; x &lt; 2$: $\frac{-}{+} &lt; 0$; $x &gt; 2$: $\frac{+}{+} &gt; 0$ ✓. || $x &lt; -1$ эсвэл $x &gt; 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -10127,6 +10773,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>$1000 + 800x \le 9000$. || $800x \le 8000$. || $x \le 10$ → дээд тал нь 10 км.</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -10202,6 +10853,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>Квадрат үргэлж $\ge 0$, зөвхөн $x - 1 = 0$ үед 0. || $x = 1$-ээс бусад бүх $x$-д $&gt; 0$. || $x \ne 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -10277,6 +10933,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>$f(-3) = (-3)^2 + 1$. || $(-3)^2 = 9$. || $9 + 1 = 10$.</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -10352,6 +11013,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = 1$ гэдэг нь $5 - 2x = 1$. || $-2x = -4$. || $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -10427,6 +11093,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>$Oy$ тэнхлэг дээр $x = 0$. || $y = -3 \cdot 0 + 4$. || $y = 4$ → цэг $(0; 4)$.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -10502,6 +11173,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>$Ox$ тэнхлэг дээр $y = 0$. || $2x - 6 = 0$. || $x = 3$ → цэг $(3; 0)$.</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -10577,6 +11253,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>$k = \frac{y_2 - y_1}{x_2 - x_1}$. || $\frac{7 - 1}{2 - 0} = \frac{6}{2}$. || $k = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -10652,6 +11333,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Хуваарь 0 байж болохгүй. || $x - 4 = 0$ → $x = 4$. || $x = 4$ мужид орохгүй.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -10727,6 +11413,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P138" s="2" t="inlineStr">
+        <is>
+          <t>$6 - 2x \ge 0$. || $-2x \ge -6$ → тэмдэг эргэнэ. || $x \le 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -10802,6 +11493,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>$Ox$ дээр $y = 0$: $x^2 - 2x - 3 = 0$. || Үржвэр $-3$, нийлбэр 2: $3$ ба $-1$. || $x = -1$; $x = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -10877,6 +11573,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>$x_0 = -\frac{b}{2a}$, $a = 1$, $b = -6$. || $x_0 = \frac{6}{2}$. || $x_0 = 3$.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -10952,6 +11653,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>Шугаман функц $y = kx + b$: $k &gt; 0$ өснө, $k &lt; 0$ буурна. || $k = -2 &lt; 0$. || Буурна → $-1$.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -11027,6 +11733,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>$a = -1 &lt; 0$ тул парабол доош харсан, оройд хамгийн их утга. || $x_0 = -\frac{4}{2 \cdot (-1)} = 2$. || $y(2) = -4 + 8 + 1 = 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -11102,6 +11813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>$f(4) = 3$ → $g(3) = 9$. || $g(4) = 12$ → $f(12) = 11$. || $9 - 11 = -2$.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -11177,6 +11893,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P144" s="2" t="inlineStr">
+        <is>
+          <t>Параллель шулуунууд ижил налалттай: $k = 3$. || $y = 3x + b$-д $(2;5)$: $5 = 6 + b$. || $b = -1$.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -11252,6 +11973,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>Дээш харсан парабол оройноосоо баруун тийш өснө. || $x_0 = -\frac{0}{2} = 0$. || Өсөх завсар: $x \ge 0$.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -11327,6 +12053,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>$32 = 2^5$. || $2^x = 2^5$. || $x = 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -11402,6 +12133,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>Ямар ч тооны тэг зэрэг 1: $a^0 = 1$. || $5^x = 5^0$. || $x = 0$.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -11477,6 +12213,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>$0{,}001 = \frac{1}{1000} = 10^{-3}$. || $10^x = 10^{-3}$. || $x = -3$.</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -11552,6 +12293,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>$f(2) = 3^2 = 9$. || $f(0) = 3^0 = 1$. || $9 + 1 = 10$.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -11627,6 +12373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>$8 = 2^3$, $16 = 2^4$. || $2^{3x} = 2^4$ → $3x = 4$. || $x = \frac{4}{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -11702,6 +12453,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>$27 = 3^3$. || $2x - 1 = 3$. || $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -11777,6 +12533,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{1}{2} = 2^{-1}$, $8 = 2^3$. || $2^{-x} = 2^3$ → $-x = 3$. || $x = -3$.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -11852,6 +12613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>Илтгэгч функц $y = a^x$: $a &gt; 1$ өснө, $0 &lt; a &lt; 1$ буурна. || $a = 0{,}5 &lt; 1$. || Буурна → $-1$.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -11927,6 +12693,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>$2^{x+2} = 4 \cdot 2^x$. || $4 \cdot 2^x - 2^x = 3 \cdot 2^x = 12$ → $2^x = 4$. || $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -12002,6 +12773,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>$4^x = (2^x)^2$, $t = 2^x$: $t^2 - 5t + 4 = 0$. || $t = 1$ эсвэл $t = 4$. || $2^x = 1$ → $x = 0$; $2^x = 4$ → $x = 2$.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -12077,6 +12853,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>$t = 5^x$: $t^2 - 6t + 5 = 0$. || $t = 1$ эсвэл $t = 5$. || $x = 0$; $x = 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -12152,6 +12933,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>$16 = 2^4$: $2^x &gt; 2^4$. || Суурь $2 &gt; 1$ — функц өснө, тэмдэг хадгалагдана. || $x &gt; 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -12227,6 +13013,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P158" s="2" t="inlineStr">
+        <is>
+          <t>$9 = (\tfrac{1}{3})^{-2}$: $(\tfrac{1}{3})^x \ge (\tfrac{1}{3})^{-2}$. || Суурь $&lt; 1$ — функц буурна, тэмдэг эргэнэ. || $x \le -2$.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -12302,6 +13093,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>$100 \cdot 2^t = 1600$ → $2^t = 16$. || $16 = 2^4$. || $t = 4$ цаг.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -12377,6 +13173,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>$3^? = 81$. || $3^4 = 81$. || $4$.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -12452,6 +13253,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{1}{25} = 5^{-2}$. || $\log_5 5^{-2}$. || $-2$.</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -12527,6 +13333,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>$\log_a a = 1$ → $\log_7 7 = 1$. || $\log_a 1 = 0$ → $\log_7 1 = 0$. || $1 + 0 = 1$.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -12602,6 +13413,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>$0{,}01 = \frac{1}{100} = 10^{-2}$. || $\lg 10^{-2}$. || $-2$.</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -12677,6 +13493,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P164" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 8 = 3$, $\log_2 4 = 2$. || $3 + 2$. || $5$ (= $\log_2 32$).</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -12752,6 +13573,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 \frac{54}{2} = \log_3 27$. || $3^3 = 27$. || $3$.</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -12827,6 +13653,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>$\sqrt{8} = 8^{1/2}$. || $\log_a b^n = n \log_a b$: $\frac{1}{2} \log_2 8$. || $\frac{1}{2} \cdot 3 = \frac{3}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -12902,6 +13733,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>Тодорхойлолт: $x = 3^4$. || $3^4 = 81$. || $x = 81$.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -12977,6 +13813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>Тодорхойлолт: $x^2 = 25$. || $x = \pm 5$; суурь эерэг, $\ne 1$. || $x = 5$.</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -13052,6 +13893,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>ТМ: $x &gt; -3$ ба $x &gt; \frac{1}{2}$. Аргументууд тэнцүү: $x + 3 = 2x - 1$. || $x = 4$. || Шалгалт: $7 = 7 &gt; 0$ ✓ → $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -13127,6 +13973,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>Баруун тал: $\log_3 x + \log_3 2 = \log_3 2x$. || $x^2 - 8 = 2x$ → $x^2 - 2x - 8 = 0$ → $x = 4$, $x = -2$. || $x = -2$ ТМ-д орохгүй → $x = 4$.</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -13202,6 +14053,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P171" s="2" t="inlineStr">
+        <is>
+          <t>Суурь солих: $\log_4 8 = \frac{\log_2 8}{\log_2 4}$. || $\frac{3}{2}$. || Хариу: $\frac{3}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -13277,6 +14133,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>ТМ: $x &gt; 0$. || Суурь $2 &gt; 1$: $x &lt; 2^3 = 8$. || $0 &lt; x &lt; 8$.</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -13352,6 +14213,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>$50 = \frac{100}{2}$. || $\lg 50 = \lg 100 - \lg 2$. || $2 - a$.</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -13427,6 +14293,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>$30°$ тусгай өнцөг. || $\cos 30° = \frac{\sqrt{3}}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -13502,6 +14373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha}$. || $\frac{\sqrt{3}/2}{1/2}$. || $\sqrt{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -13577,6 +14453,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Тодорхойлолт: $180° = \pi$ рад.</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -13652,6 +14533,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>$\pi = 180°$. || $\frac{180°}{4}$. || $45°$.</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -13727,6 +14613,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>Үндсэн адилтгал: $\sin^2\alpha + \cos^2\alpha = 1$ ямар ч $\alpha$-д. || Шалгалт: $(\tfrac{\sqrt{2}}{2})^2 + (\tfrac{\sqrt{2}}{2})^2 = \tfrac{1}{2} + \tfrac{1}{2}$. || $1$.</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -13802,6 +14693,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>$\sin^2\alpha = 1 - \cos^2\alpha = 1 - \frac{25}{169} = \frac{144}{169}$. || Хурц өнцөгт $\sin\alpha &gt; 0$. || $\sin\alpha = \frac{12}{13}$.</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -13877,6 +14773,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>$\cos\alpha = \sqrt{1 - \tfrac{9}{25}} = \frac{4}{5}$. || $\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha} = \frac{3/5}{4/5}$. || $\frac{3}{4}$.</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -13952,6 +14853,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>$150° = 180° - 30°$. || $\sin(180° - \alpha) = \sin\alpha$. || $\sin 30° = \frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -14027,6 +14933,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>$120° = 180° - 60°$. || $\cos(180° - \alpha) = -\cos\alpha$. || $-\cos 60° = -\frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -14102,6 +15013,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>Нэгж тойрог дээр $\cos x = 0$ — $x$ координат нь 0 цэгүүд. || Дээд цэг $\frac{\pi}{2}$, доод цэг $\frac{3\pi}{2}$. || $x = \frac{\pi}{2}$; $x = \frac{3\pi}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -14177,6 +15093,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>$\sin x = \frac{1}{2}$. || I мөчлөг: $\frac{\pi}{6}$; II мөчлөг: $\pi - \frac{\pi}{6} = \frac{5\pi}{6}$. || $x = \frac{\pi}{6}$; $x = \frac{5\pi}{6}$.</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -14252,6 +15173,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{ctg}\alpha = \frac{\cos\alpha}{\sin\alpha}$. || $\sin\alpha \cdot \frac{\cos\alpha}{\sin\alpha}$. || $\cos\alpha$.</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -14327,6 +15253,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>$(1-s)(1+s) = 1 - s^2$. || $1 - \sin^2\alpha$. || $= \cos^2\alpha$ (үндсэн адилтгал).</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -14402,6 +15333,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>$390° = 360° + 30°$. || Үе $360°$: $\sin 390° = \sin 30°$. || $\frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -14477,6 +15413,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P188" s="2" t="inlineStr">
+        <is>
+          <t>Үр дүн 2: сүлд, тоо. || Таатай нь 1. || $P = \frac{1}{2}$.</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -14552,6 +15493,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P189" s="2" t="inlineStr">
+        <is>
+          <t>5-аас их тоо шоон дээр: зөвхөн 6. || Таатай 1, нийт 6. || $P = \frac{1}{6}$.</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -14627,6 +15573,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>3-т хуваагдах: 3, 6, 9 — 3 ширхэг. || Нийт 10. || $P = \frac{3}{10}$.</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -14702,6 +15653,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>$P(A) + P(\bar A) = 1$. || $P(\bar A) = 1 - 0{,}3$. || $0{,}7$.</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -14777,6 +15733,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Нийт $4 + 6 = 10$. || Таатай (хар) 6. || $\frac{6}{10} = \frac{3}{5}$.</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -14852,6 +15813,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P193" s="2" t="inlineStr">
+        <is>
+          <t>Эхний байранд 4 сонголт, дараа нь 3, 2, 1. || $4! = 4 \cdot 3 \cdot 2 \cdot 1$. || $24$.</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -14927,6 +15893,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P194" s="2" t="inlineStr">
+        <is>
+          <t>Албан тушаал өөр тул дараалал чухал (байрлуулал). || Ахлагч 6 сонголт, орлогч үлдсэн 5. || $6 \cdot 5 = 30$.</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -15002,6 +15973,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>Дараалал чухал биш → хэсэглэл. || $C_5^2 = \frac{5 \cdot 4}{2}$. || $10$.</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -15077,6 +16053,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>Үржүүлэх дүрэм: цамц бүрт 4 өмд тохирно. || $3 \cdot 4$. || $12$.</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -15152,6 +16133,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр шоо бие даасан. || $P = P_1 \cdot P_2 = \frac{1}{6} \cdot \frac{1}{6}$. || $\frac{1}{36}$.</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -15227,6 +16213,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>Нийт 36. Нийлбэр 10: (4,6),(5,5),(6,4); 11: (5,6),(6,5); 12: (6,6). || Таатай $3 + 2 + 1 = 6$. || $\frac{6}{36} = \frac{1}{6}$.</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -15302,6 +16293,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>Тэгш: {2, 4, 6}; 3-т хуваагдах: {3, 6}. || Нэгдэл: {2, 3, 4, 6} — 6-г нэг л удаа тоолно. || $\frac{4}{6} = \frac{2}{3}$.</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -15377,6 +16373,11 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>Сүлд 4 хаялтын алинд нь ч буух боломжтой: $C_4^1 = 4$. || Тодорхой нэг дараалал: $(\tfrac{1}{2})^4 = \frac{1}{16}$. || $4 \cdot \frac{1}{16} = \frac{1}{4}$.</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -15452,9 +16453,14 @@
           <t>OK</t>
         </is>
       </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>Эхний бөмбөг улаан: $\frac{3}{5}$. || Буцаагаагүй: үлдсэн 4-өөс улаан 2 → $\frac{2}{4}$. || $\frac{3}{5} \cdot \frac{2}{4} = \frac{3}{10}$.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
+  <autoFilter ref="A1:P201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/ml/бодлогын_сан.xlsx
+++ b/ml/бодлогын_сан.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Бодлого" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сэдвүүд" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сэдвийн_граф" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нэр_томьёо" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Бодлого" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сэдвүүд" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Сэдвийн_граф" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Нэр_томьёо" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Бодлого'!$A$1:$P$201</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Сэдвүүд'!$A$1:$F$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Сэдвийн_граф'!$A$1:$D$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Нэр_томьёо'!$A$1:$D$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Нэр_томьёо'!$A$1:$D$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -586,17 +586,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай зэргийг үржүүлэхэд илтгэгч нь юу болдог вэ?</t>
+          <t>Ижил суурьтай зэргүүдийн үржвэрийн дүрэм: $a^m \cdot a^n = a^{m+n}$. Энэ нь зэргийн тодорхойлолтоос гардаг — $m$ ширхэг ба $n$ ширхэг ижил үржигдэхүүнийг нийлүүлбэл $m+n$ ширхэг болно.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>a^m · a^n = a^(m+n) дүрмийг ашигла.</t>
+          <t>Хоёр зэргийн суурь ижил (2) тул дүрмээр нэг зэрэг болгон бичиж, илтгэгчүүдийг нэм. Дараа нь гарсан зэргийг тодорхойлолт ёсоор тооцоол.</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2^(3+2) = 2^5-ийг тооцоол.</t>
+          <t>Илтгэгчийг үржүүлэх $(a^m)^n = a^{mn}$ дүрэм нь зөвхөн зэргийн зэрэгт хамаарна — энд хэрэглэхгүй. Шалгахдаа зэрэг тус бүрийг тусад нь бодоод үржүүлж, гарсан утгатайгаа харьцуул.</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -662,17 +662,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Хоёр бутархайг нэмэхийн өмнө хуваарийг нь ижил болгох хэрэгтэй.</t>
+          <t>Ялгаатай хуваарьтай бутархайг нэмэхдээ ерөнхий хуваарьт шилжүүлнэ, ихэвчлэн хамгийн бага ерөнхий хуваагдагчийг (ХБЕХ) авна. Бутархайн үндсэн шинж чанар $\frac{a}{b} = \frac{ak}{bk}$ ($k \ne 0$) нь утгыг өөрчлөхгүйгээр хуваарийг өөрчлөх боломж олгоно.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>4 ба 6-ийн хамгийн бага ерөнхий хуваагдагч 12.</t>
+          <t>4 ба 6-ийн хамгийн бага ерөнхий хуваагдагчийг ол. Бутархай бүрийн хүртвэр, хуваарийг нэмэлт үржигдэхүүнээр үржүүлж ижил хуваарьтай болгоод, зөвхөн хүртвэрүүдийг нэм.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3/4 = 9/12, 1/6 = 2/12 болгоод нэм.</t>
+          <t>Хүртвэрийг хүртвэртэй, хуваарийг хуваарьтай тус тусад нь нэмж болохгүй — $\frac{3+1}{4+6}$ нь $\frac{3}{4}$-өөс ч бага гарч утгагүй. Эцэст нь бутархай хураагдах эсэхийг шалгаж, үр дүн $\frac{3}{4}$-өөс их, 1-ээс бага байгааг тулга.</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -738,17 +738,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэр дэх зэргүүдийг эхлээд нэг зэрэг болго.</t>
+          <t>Ижил суурьтай зэргийн дүрмүүд: $a^m \cdot a^n = a^{m+n}$, $\frac{a^m}{a^n} = a^{m-n}$ ($a \ne 0$). Сөрөг илтгэгчийн тодорхойлолт $a^{-n} = \frac{1}{a^n}$ тул эдгээр дүрэм сөрөг илтгэгчтэй үед ч хүчинтэй.</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3^4 · 3^(−2) = 3^2. Хуваахад илтгэгчийг хасна.</t>
+          <t>Хуваарийн 3-ыг $3^1$ гэж бич. Эхлээд хүртвэрийн хоёр зэргийг нэг зэрэг болгож илтгэгчүүдийг нэм, дараа нь хуваарийн илтгэгчийг хас.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3^2 : 3^1 = 3^(2−1).</t>
+          <t>$3^{-2}$ бол сөрөг тоо биш: $3^{-2} = \frac{1}{9} &gt; 0$, эерэг суурьтай зэрэг үргэлж эерэг. Шалгахдаа зэрэг бүрийг тоогоор бодож ($81$, $\frac{1}{9}$) үйлдлүүдийг шууд гүйцэтгээд харьцуул.</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Язгуур доорх тоог бүтэн квадрат үржигдэхүүнтэй болгож задал.</t>
+          <t>Сөрөг биш $a, b$-ийн хувьд $\sqrt{a^2 b} = a\sqrt{b}$ (үржвэрийн язгуур $\sqrt{ab} = \sqrt{a}\sqrt{b}$-ээс гарна). Язгууруудыг зөвхөн язгуур доорх илэрхийлэл нь ижил үед төсөөтэй гишүүн шиг нэмж, хасна.</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50 = 25·2, 18 = 9·2.</t>
+          <t>50 ба 18-ыг тус бүр бүтэн квадрат ба үлдэх үржигдэхүүний үржвэр болгон задал. Квадрат хэсгийг язгуураас гаргаж, ижил язгууртай хоёр гишүүний коэффициентуудыг хас.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5√2 − 3√2-г тооцоол.</t>
+          <t>$\sqrt{a} - \sqrt{b} \ne \sqrt{a-b}$ — язгуур доор хасаж болохгүй. Шалгахдаа ойролцоо утгаар үнэл: $\sqrt{50} \approx 7{,}07$, $\sqrt{18} \approx 4{,}24$-ийн ялгавар таны хариуны ойролцоо утгатай тохирох ёстой.</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -890,17 +890,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Сөрөг илтгэгч нь бутархайг урвуу болгодог.</t>
+          <t>Сөрөг илтгэгч: $a^{-n} = \frac{1}{a^n}$, иймээс $\left(\frac{a}{b}\right)^{-n} = \left(\frac{b}{a}\right)^n$ ($a, b \ne 0$). Бутархай илтгэгч: $a^{\frac{1}{n}} = \sqrt[n]{a}$ ($a \ge 0$), тухайлбал $a^{\frac{1}{2}} = \sqrt{a}$.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>(1/2)^(−3) = 2^3, 16^(1/2) = √16.</t>
+          <t>Эхний гишүүнд бутархайг урвуулж илтгэгчийг эерэг болгоод зэрэгт дэвшүүл. Хоёр дахь гишүүнийг квадрат язгуур хэлбэрт бичиж утгыг ол, дараа нь хоёр утгаа нэм.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8 + 4-ийг тооцоол.</t>
+          <t>Сөрөг илтгэгч тоог сөрөг болгодоггүй, зөвхөн урвуу тоо руу шилжүүлнэ — $\left(\frac{1}{2}\right)^{-3}$ эерэг бөгөөд 1-ээс их. $16^{\frac{1}{2}}$-ийг $16 \cdot \frac{1}{2}$ гэж бүү үржүүл.</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>a^(m/n) = (ⁿ√a)^m.</t>
+          <t>Рационал илтгэгчтэй зэрэг: $a^{\frac{m}{n}} = \left(\sqrt[n]{a}\right)^m = \sqrt[n]{a^m}$ ($a &gt; 0$, $n \ge 2$ натурал). Хуваарь $n$ нь язгуурын зэрэг, хүртвэр $m$ нь зэргийн илтгэгч.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>∛27 = 3, ∛8 = 2.</t>
+          <t>27 ба 8 нь бүтэн куб тул эхлээд куб язгуурыг гарга. Дараа нь эхний гишүүнд гарсан тоог квадрат зэрэгт дэвшүүлж, хоёр утгын ялгаврыг ол.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3^2 − 2-ийг тооцоол.</t>
+          <t>$27^{\frac{2}{3}}$-ийг $27 \cdot \frac{2}{3}$ гэж үржүүлэх нь алдаа — илтгэгч бол үржигдэхүүн биш. Шалгахдаа олсон куб язгуураа куб зэрэгт дэвшүүлж анхны тоо гарч байгааг тулга.</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Эхлээд 3-ыг хаалтан доторх гишүүн бүрээр үржүүл.</t>
+          <t>Хуваарилах хууль: $a(b + c) = ab + ac$, $a(b - c) = ab - ac$. Төсөөтэй гишүүдийг нэгтгэхдээ коэффициентуудыг нэмж, үсэгтэй хэсгийг өөрчлөхгүй үлдээнэ.</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3(x − 4) = 3x − 12.</t>
+          <t>3-ыг хаалтан доторх гишүүн бүрээр тэмдэгтэй нь үржүүл. Дараа нь $x$-тэй гишүүдийг нэгтгэж, сул гишүүнийг тусад нь үлдээ.</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3x + 2x төсөөтэй гишүүдийг нэгтгэ.</t>
+          <t>3-ыг зөвхөн эхний гишүүнээр үржүүлж, $-4$-ийг үржүүлэхээ мартах нь түгээмэл алдаа. Шалгахдаа $x = 1$-ийг анхны болон хялбарчилсан илэрхийлэлд орлуулж, утгууд тэнцүү эсэхийг тулга.</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Ижил үсэгтэй гишүүдийг бүлэглэ.</t>
+          <t>Төсөөтэй гишүүд гэдэг нь үсэгтэй хэсэг (хувьсагч ба тэдгээрийн зэрэг) нь яг ижил гишүүд; тэдгээрийг $ma + na = (m+n)a$ хуулиар нэгтгэнэ. Ялгаатай үсэгтэй гишүүд нэгтгэгдэхгүй.</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>a-тай: 4a + a, b-тэй: −2b + 5b.</t>
+          <t>$a$-тай гишүүдийг нэг бүлэг, $b$-тэй гишүүдийг нөгөө бүлэг болгон, гишүүн бүрийн өмнөх тэмдгийг хамт авч бүлэглэ. Бүлэг тус бүрийн коэффициентуудыг нэм; ганц $a$-ийн коэффициент 1 гэдгийг сана.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Коэффициентуудыг нэм.</t>
+          <t>$a$ ба $b$-тэй гишүүдийг хооронд нь нэгтгэж $ab$ гаргах нь алдаа — нэмэхэд үсгүүд үржигддэггүй. $-2b$-ийн хасах тэмдгийг алдаж болохгүй; $a = 1$, $b = 1$ гэж орлуулж шалга.</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1206,17 +1206,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9 нь ямар тооны квадрат вэ?</t>
+          <t>Квадратуудын ялгавар: $a^2 - b^2 = (a - b)(a + b)$. Хоёр гишүүн хоёулаа бүтэн квадрат бөгөөд хооронд нь хасах тэмдэгтэй үед хэрэглэгдэнэ.</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>a² − b² = (a − b)(a + b) томьёо.</t>
+          <t>Хоёр гишүүн тус бүр юуны квадрат болохыг тодорхойлж $a$ ба $b$-г ол. Тэдгээрийг томьёоны баруун талд орлуул.</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>a = x, b = 3 гэж орлуул.</t>
+          <t>Бүтэн квадрат $(x-b)^2$ гэж бичих нь алдаа: $(a-b)^2 = a^2 - 2ab + b^2$ нь дунд гишүүнтэй. Шалгахдаа хаалтуудаа үржүүлж задлахад анхны илэрхийлэл гарах ёстой.</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>(a + b)² = (a + b)(a + b).</t>
+          <t>Нийлбэрийн квадрат: $(a+b)^2 = a^2 + 2ab + b^2$. Энэ нь $(a+b)(a+b)$-г гишүүнчлэн үржүүлэхэд $ab$ гишүүн хоёр удаа гардгаас үүснэ.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>(a + b)² = a² + 2ab + b².</t>
+          <t>$a = x$, $b = 3$ гэж тааруулаад томьёоны гурван гишүүнийг тус тусад нь бич. Эхнийх нь $a$-ийн квадрат, дунд нь давхар үржвэр, сүүлийнх нь $b$-ийн квадрат.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>a = x, b = 3: x² + 2·x·3 + 9.</t>
+          <t>$(a+b)^2 \ne a^2 + b^2$ — дунд гишүүн $2ab$-г мартах нь хамгийн түгээмэл алдаа. Шалгахдаа $x = 1$ орлуул: $(1+3)^2$ нь таны гаргасан олон гишүүнтийн утгатай тэнцэх ёстой.</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр нь 6, нийлбэр нь −5 болох хоёр тоо ол.</t>
+          <t>$(x+p)(x+q) = x^2 + (p+q)x + pq$ адилтгал хүчинтэй. Иймээс $x^2 + bx + c$-г задлахын тулд $p + q = b$, $pq = c$ байх $p$, $q$ тоонуудыг олно (Виетийн теоремтой ижил санаа).</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>−2 ба −3: үржвэр 6, нийлбэр −5.</t>
+          <t>Үржвэр нь 6, нийлбэр нь $-5$ байх хоёр бүхэл тоог 6-ийн хуваагчдаас хай. Үржвэр эерэг, нийлбэр сөрөг байгаа нь хоёр тооны тэмдгийн талаар юу хэлж байгааг эхлээд дүгнэ.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>(x + p)(x + q) хэлбэрт бич.</t>
+          <t>Тэмдгийг андуурч хаалтанд эерэг тоо тавих нь түгээмэл алдаа — дунд гишүүний тэмдгийг шалга. Хаалтуудаа үржүүлж задлахад анхны гурван гишүүнт яг гарах ёстой.</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1446,17 +1446,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэрийг үржигдэхүүнд задалж болох уу?</t>
+          <t>Рационал илэрхийллийг хураахдаа хүртвэр, хуваарийг үржигдэхүүнд задалж, ерөнхий үржигдэхүүнд хуваана: $\frac{ac}{bc} = \frac{a}{b}$ ($b, c \ne 0$). Зөвхөн үржигдэхүүнийг хураана, нэмэгдэхүүнийг хураахгүй.</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>x² − 4 = (x − 2)(x + 2).</t>
+          <t>Хүртвэрийг квадратуудын ялгаврын томьёогоор задал. Хуваарьтай ижил үржигдэхүүн гарч ирэх бөгөөд $x \ne 2$ нөхцөлөөр түүнийг хураа.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Ижил үржигдэхүүнийг хураа.</t>
+          <t>$x^2$-ийг $x$-д, 4-ийг 2-т тус тусад нь хуваах нь алдаа — нийлбэр, ялгаврын гишүүдийг хураадаггүй. $x = 3$ гэх мэт утгыг анхны бутархай ба хялбарчилсан илэрхийлэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1526,17 +1526,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>x-ийг ганцааранг нь үлдээхийн тулд эхлээд юуг шилжүүлэх вэ?</t>
+          <t>Тэгшитгэлийн тэнцүү чанарын шинж: хоёр талд ижил тоо нэмэх (хасах), эсвэл хоёр талыг тэгээс ялгаатай ижил тоонд хуваахад шийд өөрчлөгдөхгүй. Иймээс гишүүнийг нөгөө тал руу эсрэг тэмдэгтэйгээр шилжүүлж болно: $a + b = c \iff a = c - b$.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5-ыг баруун тал руу шилжүүлэхэд тэмдэг нь өөрчлөгдөнө.</t>
+          <t>Эхлээд чөлөөт гишүүнийг баруун тал руу шилжүүлж, зүүн талд зөвхөн $x$-тэй гишүүнийг үлдээ. Дараа нь хоёр талыг $x$-ийн коэффициентод хуваа.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2x = 8, хоёр талыг 2-т хуваа.</t>
+          <t>Шилжүүлэхдээ тэмдгийг заавал соль: $+5$ баруун талд $-5$ болно, нэмбэл буруу утга гарна. Олсон $x$-ээ анхны тэгшитгэлд орлуулж, зүүн тал $13$ болж байгаа эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>x-тэй гишүүдийг нэг талд, тоонуудыг нөгөө талд цуглуул.</t>
+          <t>Шугаман тэгшитгэлийг $ax = b$ ($a \ne 0$) хэлбэрт оруулбал цорын ганц шийд $x = \frac{b}{a}$ гарна. Үүний тулд үл мэдэгдэгчтэй гишүүдийг нэг талд, тоонуудыг нөгөө талд эсрэг тэмдэгтэйгээр шилжүүлнэ.</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3x − 2x = 1 + 7.</t>
+          <t>$2x$-ийг зүүн тал руу, $-7$-г баруун тал руу шилжүүлж, ижил төстэй гишүүдийг нэгтгэ. Үлдсэн тэгшитгэлээс $x$-ийг илэрхийл.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Хялбарчил.</t>
+          <t>Хоёр гишүүнийг хоёуланг нь шилжүүлэх ёстой — зөвхөн нэгийг нь шилжүүлж нөгөөг мартвал тэмдгийн алдаа гарна. Шалгахдаа олсон утгаа хоёр талд орлуулж, ижил тоо гарч байгааг нягтал.</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1686,17 +1686,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Хуваарийг арилгах арга бод.</t>
+          <t>Пропорцын үндсэн чанар: $\frac{a}{b} = \frac{c}{d}$ ($b, d \ne 0$) бол $ad = bc$, өөрөөр хэлбэл хөндлөн үржвэрүүд тэнцүү. Энэ нь хоёр талыг ерөнхий хуваарь $bd$-ээр үржүүлсэнтэй ижил.</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 15-аар үржүүл: 5(x − 1) = 3(x + 1).</t>
+          <t>Зүүн талын хүртвэрийг баруун талын хуваариар, баруун талын хүртвэрийг зүүн талын хуваариар үржүүлж тэнцүүл. Хаалтуудыг задлаад $x$-тэй гишүүдийг нэг тал руу цуглуул.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5x − 5 = 3x + 3.</t>
+          <t>Хүртвэрүүдийг шууд тэнцүүлж болохгүй — хуваарь өөр тул энэ нь буруу. Хаалт задлахдаа хаалтын доторх гишүүн бүрийг үржүүлж, олсон утгаа хоёр бутархайд орлуулж тэнцүү эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Үзэгний үнийг x гэвэл дэвтрийн үнэ хэд вэ?</t>
+          <t>Үгэн бодлогыг тэгшитгэл зохиож бодно: үл мэдэгдэх хэмжигдэхүүнийг $x$ гэж тэмдэглээд, бусдыг $x$-ээр илэрхийлж, нөхцөлд өгсөн тэнцүү хамаарлыг бичнэ. Нийт үнэ = нэгжийн үнэ $\times$ тоо ширхэг гэсэн хамаарал энд хэрэглэгдэнэ.</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>Дэвтэр = x + 300. Нийт: 2(x + 300) + 3x = 3600.</t>
+          <t>Асуусан зүйл болох үзэгний үнийг $x$ гэвэл дэвтэр $300$-гаар үнэтэй тул $x + 300$ болно. Хоёр дэвтэр ба гурван үзэгний үнийн нийлбэрийг $3600$-тай тэнцүүлж, хаалтыг задлаад шугаман тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5x + 600 = 3600.</t>
+          <t>Дэвтэр үзэгнээс үнэтэй тул түүний үнэ $x - 300$ биш, $x + 300$ байна. Хаалтыг задлахдаа $300$-г $2$-оор үржүүлэхээ бүү март, хариугаа нийт үнэ $3600$ гарч байгаагаар шалга.</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1846,17 +1846,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Хоёр тэгшитгэлийг нэмэхэд y юу болох вэ?</t>
+          <t>Хоёр үл мэдэгдэгчтэй шугаман системийн шийд нь хоёр тэгшитгэлийг зэрэг хангах $(x; y)$ хос юм. Нэмэх арга: нэг хувьсагчийн коэффициентууд эсрэг тоо бол тэгшитгэлүүдийг гишүүнчлэн нэмэхэд тэр хувьсагч устана.</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Нэмбэл: 2x = 14.</t>
+          <t>Хоёр тэгшитгэлд $y$-ийн коэффициентууд $1$ ба $-1$ тул тэдгээрийг гишүүнчлэн нэмж $y$-ийг устга. Гарсан нэг хувьсагчтай тэгшитгэлээс $x$-ийг олоод, аль нэг тэгшитгэлд орлуулж $y$-ийг ол.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>x-ийг олоод эхний тэгшитгэлд орлуулж y-ийг ол.</t>
+          <t>Хариу нь хос тоо — зөвхөн $x$-ийг олоод зогсож болохгүй. Олсон хосоо хоёр тэгшитгэлд хоёуланд нь орлуулж, хоёулаа үнэн тэнцэтгэл болж байгааг шалга.</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Хүүгийн одоогийн насыг x гэвэл аав хэдэн настай вэ?</t>
+          <t>Насны бодлогод хүн бүрийн нас хугацаа өнгөрөхөд ижил тоогоор нэмэгддэг: одоо $a$ настай бол $n$ жилийн дараа $a + n$ настай. Нэг хэмжигдэхүүнийг $x$ гэж аваад нөгөөг нь $x$-ээр илэрхийлж, ирээдүйн харьцааг тэгшитгэл болгоно.</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5 жилийн дараа: аав 4x + 5, хүү x + 5.</t>
+          <t>Хүүгийн одоогийн насыг $x$ гэвэл аав $4x$ настай. $5$ жилийн дараах хоёулангийн насыг бичиж, аавынх хүүгийнхээс $3$ дахин их гэдгийг тэгшитгэлээр илэрхийлээд бод.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4x + 5 = 3(x + 5) тэгшитгэлийг бод.</t>
+          <t>$5$ жилийг хоёр хүний насанд хоёуланд нь нэмэх ёстой, мөн $3(x+5)$-ийн хаалтыг бүрэн задал. Шалгахдаа одоогийн ба $5$ жилийн дараах насуудыг тооцоолж, хоёр харьцаа хоёулаа биелж байгааг нягтал.</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>x² = 16 болгож бич.</t>
+          <t>$x^2 = a$ ($a &gt; 0$) тэгшитгэл $x = \sqrt{a}$ ба $x = -\sqrt{a}$ гэсэн хоёр язгууртай, учир нь $(-m)^2 = m^2$. Мөн квадратуудын ялгаврын томьёо $a^2 - b^2 = (a-b)(a+b)$-ээр үржигдэхүүнд задалж болно.</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Ямар тоонуудын квадрат 16 вэ?</t>
+          <t>Чөлөөт гишүүнийг баруун тал руу шилжүүлж $x^2 = a$ хэлбэрт оруул, эсвэл зүүн талыг квадратуудын ялгавраар задал. Хоёр язгуурыг хоёуланг нь бич.</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Эерэг ба сөрөг хоёр шийд бий.</t>
+          <t>Зөвхөн эерэг язгуурыг бичих нь түгээмэл алдаа — сөрөг тооны квадрат ч эерэг. Хоёр утгаа анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Хоёр гишүүнд ерөнхий үржигдэхүүн бий юу?</t>
+          <t>Үржвэр тэгтэй тэнцүү байх нөхцөл: $A \cdot B = 0 \iff A = 0$ эсвэл $B = 0$. $c = 0$ үеийн бүрэн биш квадрат тэгшитгэл $ax^2 + bx = 0$-ийг $x(ax + b) = 0$ хэлбэрт задалж бодно.</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>x(x − 5) = 0.</t>
+          <t>Хоёр гишүүнд ерөнхий $x$ үржигдэхүүнийг хаалтын өмнө гарга. Үржигдэхүүн бүрийг тэгтэй тэнцүүлж хоёр шугаман тэгшитгэл бод.</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр тэгтэй тэнцүү бол аль нэг үржигдэхүүн нь тэг.</t>
+          <t>Хоёр талыг $x$-т хувааж болохгүй: $x$ тэг байж болох тул нэг язгуур алдагдана. Хоёр утгаа анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр нь 12, нийлбэр нь 7 болох хоёр тоо бий юу?</t>
+          <t>Виетийн теорем: $x^2 + px + q = 0$ тэгшитгэлийн язгуурууд байвал $x_1 + x_2 = -p$, $x_1 x_2 = q$. Урвуу теоремоор нийлбэр ба үржвэр нь эдгээр нөхцөлийг хангах хоёр тоо нь язгуурууд болно.</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>Виетийн теорем: x₁ + x₂ = 7, x₁·x₂ = 12.</t>
+          <t>Энд $p = -7$, $q = 12$ тул язгууруудын нийлбэр $7$, үржвэр $12$ байх ёстой. $12$-ыг хоёр үржигдэхүүнд задлах хувилбаруудаас нийлбэр нь $7$ болохыг сонго.</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3 ба 4-ийг шалга.</t>
+          <t>Нийлбэр нь $-p$ тул $p$ сөрөг үед язгууруудын нийлбэр эерэг — тэмдгийг бүү андуур. Олсон тоонуудаа тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>a, b, c коэффициентуудыг ялга.</t>
+          <t>$ax^2 + bx + c = 0$ ($a \ne 0$) тэгшитгэлийн дискриминант $D = b^2 - 4ac$; $D \ge 0$ бол язгуурууд $x_{1,2} = \frac{-b \pm \sqrt{D}}{2a}$. Энд $a \ne 1$ тул Виетийн сонголтоос томьёо илүү найдвартай.</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>D = b² − 4ac = 9 + 16 = 25.</t>
+          <t>$a$, $b$, $c$ коэффициентуудыг тэмдэгтэй нь ялгаж бичээд $D$-г тооцоол. $\sqrt{D}$-г олоод томьёонд орлуулж, $+$ ба $-$ тохиолдлыг тус тусад нь хялбарчил.</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>x = (−b ± √D) / (2a).</t>
+          <t>Хуваарь нь $2$ биш $2a$ — энд $a = 2$ гэдгийг анхаар. $c$ сөрөг тул $-4ac$ эерэг болно, хоёр язгуураа тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2326,17 +2326,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Энэ тэгшитгэлийг бүхэл тоогоор задлах боломжгүй. Ямар томьёо хэрэглэх вэ?</t>
+          <t>$ax^2 + bx + c = 0$-ийн язгуурын томьёо: $x_{1,2} = \frac{-b \pm \sqrt{D}}{2a}$, $D = b^2 - 4ac$. $D$ нь бүтэн квадрат биш бол язгуурууд иррационал тул хялбарчилсан язгуур хэлбэрээр бичнэ.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>D = 4 + 4 = 8, √8 = 2√2.</t>
+          <t>$a$, $b$, $c$-г тэмдэгтэй нь авч $D$-г ол. $\sqrt{D}$-г $\sqrt{m^2 k} = m\sqrt{k}$ дүрмээр хялбарчлаад томьёонд орлуулж, хүртвэр ба хуваарийг ерөнхий үржигдэхүүнээр хураа.</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>x = (2 ± 2√2) / 2-ыг хялбарчил.</t>
+          <t>Хураахдаа хүртвэрийн хоёр гишүүнийг хоёуланг нь хуваа. $-4ac$-ийн тэмдгийг шалгаж, язгууруудын нийлбэр $-\frac{b}{a}$-тай тэнцүү эсэхээр хариугаа нягтал.</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2406,17 +2406,17 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Квадрат тэгшитгэл хэзээ ганц язгууртай байдаг вэ?</t>
+          <t>Квадрат тэгшитгэл давхар (ганц) язгууртай байх зайлшгүй ба хүрэлцээтэй нөхцөл: $D = b^2 - 4ac = 0$. Энэ үед $ax^2 + bx + c = a(x - x_0)^2$ болно.</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>D = 0 байх ёстой: k² − 4·1·9 = 0.</t>
+          <t>Коэффициентуудыг ялгаж ($b$ нь параметр $k$) $D$-г $k$-гаар илэрхийл. $D = 0$ тэгшитгэлийг $k$-ийн хувьд бод.</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>k² = 36.</t>
+          <t>$k^2 = m$ ($m &gt; 0$) хэлбэрийн тэгшитгэл хоёр шийдтэй — сөрөг утгыг бүү орхи. Олсон утга бүрээ буцааж тавиад тэгшитгэл бүтэн квадрат болж байгааг шалга.</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Тэгшитгэл бодохтой адилаар эхэл.</t>
+          <t>Тэнцэтгэл бишийн хоёр талд ижил тоо нэмэх (хасах) нь тэмдгийг өөрчлөхгүй; хоёр талыг эерэг $c$-д хуваахад $a &gt; b \Rightarrow \frac{a}{c} &gt; \frac{b}{c}$ хэвээр байна. Шугаман тэнцэтгэл бишийг тэгшитгэлтэй ижил алхмаар бодно.</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2x &gt; 8.</t>
+          <t>Чөлөөт гишүүн $-3$-ыг баруун тал руу эсрэг тэмдэгтэй шилжүүлж, $2x &gt; \dots$ хэлбэрт оруул. Дараа нь хоёр талыг $x$-ийн коэффициентод хуваа.</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Эерэг тоонд хуваахад тэмдэг өөрчлөгдөхгүй.</t>
+          <t>Анхны тэмдэг хатуу ($&gt;$) тул хариу ч хатуу тэмдэгтэй байна — $\ge$ болгож болохгүй. Шалгахдаа хилийн утгыг орлуулахад тэнцэтгэл биш биелэхгүй, түүнээс арай их утгад биелэхийг шалга.</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2566,17 +2566,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6-г баруун тал руу шилжүүл.</t>
+          <t>Хоёр талыг сөрөг тоо $c&lt;0$-д хуваахад тэнцэтгэл бишийн тэмдэг эсрэгээр эргэнэ: $a \le b \Rightarrow \frac{a}{c} \ge \frac{b}{c}$. Учир нь сөрөг тоогоор үржүүлэхэд тоон шулуун дээрх дараалал урвуу болдог.</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>−3x ≤ −6.</t>
+          <t>Эхлээд $6$-г баруун тал руу шилжүүлж $-3x \le \dots$ хэлбэрт оруул. Дараа нь хоёр талыг $-3$-т хувааж, тэмдгийг эргүүл.</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Сөрөг тоонд хуваахад тэнцэтгэл бишийн тэмдэг эсрэгээр эргэнэ.</t>
+          <t>Хамгийн түгээмэл алдаа — $-3$-т хуваахдаа тэмдгийг эргүүлэхгүй орхих. Шалгахдаа хариуныхаа завсраас нэг тоо ($x = 10$ гэх мэт) авч анхны тэнцэтгэл бишид орлуулж үнэн эсэхийг харь.</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг ямар тоогоор үржүүлбэл хуваарь арилах вэ?</t>
+          <t>Тэнцэтгэл бишийн хоёр талыг ижил эерэг тоогоор үржүүлэхэд тэмдэг хадгалагдана: $a&lt;b,\ c&gt;0 \Rightarrow ac&lt;bc$. Хуваарийн хамгийн бага ерөнхий хуваагдагчаар үржүүлбэл бутархай арилна.</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4-өөр үржүүл: 2(x − 1) &lt; x + 3.</t>
+          <t>Хуваарь $2$ ба $4$-ийн ХБЕХ нь $4$; хоёр талыг бүхэлд нь $4$-өөр үржүүлж $2(x-1) &lt; x+3$ хэлбэрт оруул. Хаалтыг задлаад $x$-тэй гишүүдийг зүүн, тоонуудыг баруун талд цуглуул.</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2x − 2 &lt; x + 3.</t>
+          <t>Хоёр талыг хоёуланг нь үржүүлэх ёстой — зөвхөн нэг талыг үржүүлбэл тэнцэтгэл биш өөр болно. $4 &gt; 0$ тул тэмдэг эргэхгүй; хариугаа завсраас нэг утга авч анхны бутархай хэлбэрт орлуулж шалга.</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>|x − 2| нь x-ээс 2 хүртэлх зай. Зай 3-аас бага гэдэг юу гэсэн үг вэ?</t>
+          <t>$a &gt; 0$ үед $|t| &lt; a \iff -a &lt; t &lt; a$. Модуль нь зай тул $|x - m| &lt; a$ гэдэг нь $x$ цэг $m$-ээс $a$-аас бага зайд байна гэсэн үг.</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>−3 &lt; x − 2 &lt; 3.</t>
+          <t>$t = x - 2$ гэж үзээд давхар тэнцэтгэл биш $-3 &lt; x - 2 &lt; 3$ бич. Гурван хэсэг тус бүрд ижил тоо нэмж $x$-ийг дунд нь ганцааршуул.</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Бүх хэсэгт 2-ыг нэм.</t>
+          <t>Зөвхөн $x - 2 &lt; 3$ гэж бодвол зүүн хязгаар алга болно — модуль хоёр талын нөхцөл өгдөг. Шалгахдаа хариуны хоёр захын гадна, дотор талын утгуудыг орлуулж үзээрэй; захын цэгүүд хатуу тэмдэг тул орохгүй.</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2806,17 +2806,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Эхлээд x² − 5x + 6 = 0 тэгшитгэлийн язгуурыг ол.</t>
+          <t>$a &gt; 0$ үед $ax^2+bx+c$ ($D &gt; 0$) язгууруудынхаа хооронд сөрөг, гадна талд эерэг утгатай — парабол дээш харсан тул. Иймд квадрат тэнцэтгэл бишийг язгуур ба $a$-гийн тэмдгээр бодно.</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>Язгуурууд 2 ба 3. Парабол дээшээ харсан.</t>
+          <t>$x^2 - 5x + 6 = 0$ тэгшитгэлийн язгуурыг Виетийн теорем эсвэл үржигдэхүүнд задлах аргаар ол. Язгууруудыг тоон шулуунд тэмдэглээд илэрхийлэл сөрөг байх завсрыг сонго.</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Парабол тэнхлэгээс доор байх завсрыг сонго.</t>
+          <t>$&lt;0$ гэдэг нь парабол $Ox$ тэнхлэгээс доор байх хэсэг — язгууруудын гадна талыг сонгох нь түгээмэл алдаа. Хатуу тэмдэг тул язгуурууд өөрсдөө орохгүй; завсрын дундах нэг тоог орлуулж шалга.</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>x² − 4 = 0 үед x хэдтэй тэнцүү вэ?</t>
+          <t>Квадратуудын ялгавар $a^2 - b^2 = (a-b)(a+b)$. Дээш харсан парабол ($a&gt;0$) язгууруудынхаа гадна талд эерэг, язгуурууд дээр тэг байна.</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>Язгуурууд −2 ба 2. Тоон шулуунд тэмдэглэ.</t>
+          <t>$x^2 - 4$-ийг үржигдэхүүнд задалж язгууруудыг ол. Тоон шулууныг язгуураар гурван завсарт хувааж, илэрхийлэл $\ge 0$ байх завсруудыг сонго.</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Илэрхийлэл эерэг байх завсруудыг сонго.</t>
+          <t>$x^2 \ge 4$-ээс зөвхөн эерэг талыг авах нь алдаа — сөрөг $x$-ийн квадрат ч их байж болно. $\ge$ тул язгуурууд хариунд орно; хариу хоёр завсрын нэгдэл байж болохыг санаарай.</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>f(4) гэдэг нь x-ийн оронд юу тавихыг хэлж байна вэ?</t>
+          <t>$f(a)$ гэдэг нь $f(x)$ функцийн томьёонд $x$-ийн оронд $a$-г орлуулж олсон функцийн утга. Энэ нь үржвэр биш — аргументын тодорхой утгад харгалзах утга юм.</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>x = 4-ийг орлуул: 3·4 − 2.</t>
+          <t>$f(x) = 3x - 2$ томьёонд $x$ бүрийн оронд $4$-ийг тавь. Үйлдлийн дарааллаар эхлээд үржүүлж, дараа нь хас.</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Тооцоол.</t>
+          <t>$f(4)$-ийг $4 \cdot f$ гэж ойлгох нь алдаа. Шалгахдаа: шугаман функц тул $f(4) - f(3)$ нь $x$-ийн коэффициенттэй тэнцүү байх ёстой.</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>y = kx + b хэлбэрт k нь юуг илэрхийлдэг вэ?</t>
+          <t>$y = kx + b$ шулууны $k$ нь өнцгийн коэффициент (налалт): $x$ нэгээр өсөхөд $y$ хэдээр өөрчлөгдөхийг заана, $k = \tan \alpha$. $b$ нь $Oy$ тэнхлэгийг огтлох цэгийн ордината.</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>k нь x-ийн өмнөх коэффициент.</t>
+          <t>Тэгшитгэл аль хэдийн $y = kx + b$ хэлбэрт байгаа эсэхийг шалга. $x$-ийн өмнөх коэффициентыг $k$, чөлөөт гишүүнийг $b$ гэж ялга.</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Энэ тэгшитгэлд k = ?</t>
+          <t>Чөлөөт гишүүн $b$-г налалт гэж андуурах нь түгээмэл. Шалгахдаа $x = 0$ ба $x = 1$ үеийн $y$-ийн утгуудын зөрүүг ол.</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Квадрат язгуурын доор ямар тоо байж болохгүй вэ?</t>
+          <t>Бодит тоон квадрат язгуур $\sqrt{u}$ зөвхөн $u \ge 0$ үед тодорхойлогдоно. Иймд $\sqrt{g(x)}$ функцийн тодорхойлогдох муж нь $g(x) \ge 0$ тэнцэтгэл бишийн шийд.</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>x − 3 ≥ 0 байх ёстой.</t>
+          <t>Язгуур доорх илэрхийлэлд сөрөг биш байх нөхцөл тавьж шугаман тэнцэтгэл биш бич. Түүнийг бодоод завсар хэлбэрээр илэрхийл.</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Тэнцэтгэл бишийг бод.</t>
+          <t>$\sqrt{0} = 0$ тодорхойлогдох тул тэнцэх тохиолдол орно — $&gt;$ биш $\ge$ бич. Хилийн цэгийг орлуулж язгуур утгатай эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3206,17 +3206,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>y = kx + b хэлбэрээр хайя. Хоёр цэгээс юуг олж болох вэ?</t>
+          <t>$(x_1; y_1)$, $(x_2; y_2)$ цэгүүдийг ($x_1 \ne x_2$) дайрсан шулууны налалт $k = \frac{y_2 - y_1}{x_2 - x_1}$. $k$-г мэдсэний дараа $y = kx + b$-д нэг цэгийг орлуулж $b$-г олно.</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>k = (7 − 3)/(3 − 1).</t>
+          <t>Эхлээд ординатуудын зөрүүг абсциссуудын зөрүүнд хувааж $k$-г ол. Дараа нь $(1; 3)$ цэгийг $y = kx + b$-д орлуулж $b$-г тодорхойл.</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>k-г олоод нэг цэгийг орлуулж b-г ол.</t>
+          <t>Хүртвэр ба хуваарийг сольж ($\frac{x_2 - x_1}{y_2 - y_1}$) бичих нь алдаа. Олсон тэгшитгэлдээ хоёр цэгийг хоёуланг нь орлуулж шалга.</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3286,17 +3286,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Параболын оройн абсцисс x₀ = −b/(2a).</t>
+          <t>$f(x) = ax^2 + bx + c$ ($a \ne 0$) параболын оройн абсцисс $x_0 = -\frac{b}{2a}$, ордината $y_0 = f(x_0)$. Энэ нь бүтэн квадрат ялгах аргаас гарна.</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>x₀ = 4/2 = 2.</t>
+          <t>$a$, $b$-г тэмдэгтэй нь тодорхойлж $x_0$-ийн томьёонд орлуул. Дараа нь $x_0$-ийг функцид орлуулж ординатыг ол.</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>y₀ = f(2)-ыг тооцоол.</t>
+          <t>Томьёоны хасах тэмдгийг орхих ($x_0 = \frac{b}{2a}$) нь түгээмэл алдаа — $b$ сөрөг үед давхар хасах гарахыг анхаар. Бүтэн квадрат ялгаж $(x - x_0)^2 + y_0$ хэлбэрт оруулж шалгаж болно.</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3366,17 +3366,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Дотор талын функцээс эхэл.</t>
+          <t>Функцийн найрлага $f(g(x))$: эхлээд дотоод функц $g$-ийн утгыг олж, тэр утгыг гадаад функц $f$-ийн аргумент болгоно. Ерөнхийдөө $f(g(x)) \ne g(f(x))$.</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>g(2) = 4.</t>
+          <t>Эхлээд $g(2)$-ийг $g(x) = x^2$-д орлуулж ол. Гарсан тоог $f(x) = 2x + 3$-ын $x$-ийн оронд тавь.</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>f(4)-ийг тооцоол.</t>
+          <t>Дарааллыг сольж $g(f(2))$-ийг бодох нь алдаа — гадаад функц хамгийн сүүлд хэрэглэгдэнэ. Алхам бүрийн завсрын утгыг тусад нь бичиж шалга.</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3446,17 +3446,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>8-ыг 2-ын зэргээр бичиж болох уу?</t>
+          <t>Илтгэгч функц $y=a^x$ ($a&gt;0$, $a \ne 1$) харилцан нэг утгатай тул $a^{f(x)} = a^{g(x)}$ тэгшитгэл $f(x) = g(x)$-тэй тэнцүү чанартай. Иймд хоёр талыг ижил суурьтай зэрэгт оруулбал илтгэгчүүдийг тэнцүүлж болно.</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>8 = 2³.</t>
+          <t>Баруун талын $8$-ыг 2 суурьтай зэрэг хэлбэрээр бич: 2-ыг хэдэн удаа үржүүлэхэд $8$ гарахыг тоол. Дараа нь хоёр талын илтгэгчийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Суурь ижил бол илтгэгчийг тэнцүүл.</t>
+          <t>$8$-ыг суурь $2$-т хуваах нь илтгэгчийг өгөхгүй — зэрэг бол давтан үржвэр. Шалгахдаа олсон $x$-ээ $2^x$-д орлуулж $8$ гарахыг тулга.</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3526,17 +3526,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1/9-ийг 3-ын зэргээр бичих арга бод.</t>
+          <t>Сөрөг илтгэгчтэй зэргийн тодорхойлолт: $a^{-n} = \frac{1}{a^n}$ ($a \ne 0$). Энэ нь бутархайг ижил суурьтай зэрэг болгож, $a^{f(x)} = a^{g(x)} \Leftrightarrow f(x) = g(x)$ дүрмийг хэрэглэх боломж олгоно.</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1/9 = 3^(−2).</t>
+          <t>Эхлээд $9$-ийг 3 суурьтай зэрэг болго, дараа нь $\frac{1}{9}$-ийг сөрөг илтгэгчтэй зэрэг хэлбэрт шилжүүл. Хоёр тал ижил суурьтай болсны дараа илтгэгчүүдийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Илтгэгчийг тэнцүүл.</t>
+          <t>$a &gt; 1$ үед $a^x &lt; 1$ байх нь зөвхөн $x &lt; 0$ үед биелнэ — хариу эерэг гарвал тэмдгээ алдсан байна. Олсон $x$-ээ орлуулж $\frac{1}{9}$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3606,17 +3606,17 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>4 ба 32 хоёулаа ямар тооны зэрэг вэ?</t>
+          <t>Зэргийн зэргийн дүрэм: $(a^m)^n = a^{mn}$. Суурь нь өөр боловч нэг тооны зэрэг болох тоонуудыг нийтлэг суурьт шилжүүлж, $a^{f(x)} = a^{g(x)} \Leftrightarrow f(x) = g(x)$ дүрмийг хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>4^x = 2^(2x), 32 = 2⁵.</t>
+          <t>$4$ ба $32$-ыг хоёуланг нь 2 суурьтай зэрэг болгон бич. Зүүн талын $(2^k)^x$-ийг зэргийн зэргийн дүрмээр хялбарчилж, илтгэгчүүдийг тэнцүүлэн шугаман тэгшитгэл бод.</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2x = 5.</t>
+          <t>$4^x$-ийг $2^x$ гэж солих нь алдаа: $4^x = (2^2)^x$ тул илтгэгч нь $x$ биш, хоёр дахин их. Хариу бутархай гарч болно; шалгахдаа $4^x = (\sqrt{4})^{2x}$ гэж бодоод орлуул.</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3686,17 +3686,17 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>125 = 5^?</t>
+          <t>Ижил суурьтай илтгэгч тэгшитгэл: $a^{f(x)} = a^{g(x)}$ ($a&gt;0$, $a \ne 1$) бол $f(x) = g(x)$. Илтгэгч нь $x+1$ шиг илэрхийлэл байсан ч дүрэм хэвээр — илтгэгчийг бүтнээр нь тэнцүүлнэ.</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>x + 1 = 3.</t>
+          <t>$125$-ыг 5 суурьтай зэрэг болгон бич. Дараа нь зүүн талын илтгэгч $x+1$-ийг баруун талын илтгэгчтэй тэнцүүлж, шугаман тэгшитгэлийг $x$-ийн хувьд бод.</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>x-ийг ол.</t>
+          <t>Илтгэгчүүдийг тэнцүүлээд зогсож болохгүй: олдсон тоо нь $x+1$-ийн утга, $x$-ийнх биш. Олсон $x$-ээ $5^{x+1}$-д орлуулж $125$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3766,17 +3766,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>2^(2x)-ийг (2^x)² гэж бичиж болно. t = 2^x гэж тэмдэглэ.</t>
+          <t>$A \cdot a^{2x} + B \cdot a^x + C = 0$ хэлбэрийн тэгшитгэлийг $t = a^x$ орлуулгаар квадрат тэгшитгэлд шилжүүлнэ, учир нь $a^{2x} = (a^x)^2$. Илтгэгч функцийн утга үргэлж эерэг тул $t &gt; 0$ нөхцөл заавал мөрдөгдөнө.</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>t² − 3t − 4 = 0 → t = 4 эсвэл t = −1.</t>
+          <t>$t = 2^x$ гэж тэмдэглээд тэгшитгэлийг $t$-ийн квадрат тэгшитгэл болгон бич; Виетийн теорем эсвэл дискриминантаар язгууруудыг ол. Зөвхөн $t &gt; 0$ язгуурын хувьд $2^x = t$ тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2^x &gt; 0 тул t = −1 тохирохгүй. 2^x = 4.</t>
+          <t>Сөрөг $t$ язгуур гарвал хая: $2^x$ хэзээ ч сөрөг утга авдаггүй тул түүнээс шийд гарахгүй. Эцэст нь олсон $x$-ээ анхны тэгшитгэлд орлуулж $0$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>9^x = (3^x)². t = 3^x гэж тэмдэглэ.</t>
+          <t>$a^{2x} = (a^x)^2$ адилтгалын ачаар $9^x$ ба $3^x$ агуулсан тэгшитгэлийг $t = 3^x$ ($t&gt;0$) орлуулгаар квадрат тэгшитгэл болгоно. $t$-ийн эерэг язгуур бүр $3^x = t$ гэсэн энгийн илтгэгч тэгшитгэл үүсгэнэ.</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>t² − 4t + 3 = 0 → t = 1 эсвэл t = 3.</t>
+          <t>$9^x$-ийг $(3^x)^2$ гэж бичээд $t = 3^x$ орлуул, гарсан квадрат тэгшитгэлийн язгууруудыг ол. Эерэг язгуур бүрийг 3 суурьтай зэрэг хэлбэрт бичиж, $x$-ийг тус бүр гарга.</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3^x = 1 ба 3^x = 3-ыг тус тусад нь бод.</t>
+          <t>$3^x = t$-ээс $x = t$ гэж бичих алдаанаас сэргийл: $x$ бол $3$-ыг $t$ болгох илтгэгч. Тэг зэргийн тодорхойлолтыг сана; хоёр шийдийг тус бүр анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>log₂16 гэдэг нь 2-ыг хэдэн зэрэгт дэвшүүлбэл 16 болохыг асууж байна.</t>
+          <t>Логарифмын тодорхойлолт: $a &gt; 0$, $a \ne 1$, $b &gt; 0$ үед $\log_a b = c \Leftrightarrow a^c = b$. Өөрөөр хэлбэл $\log_a b$ нь $b$-г гаргахын тулд $a$-г дэвшүүлэх илтгэгч юм.</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2^? = 16.</t>
+          <t>$\log_2 16 = c$ гэж тэмдэглээд $2^c = 16$ хэлбэрт шилжүүл. $16$-г 2-ын зэрэг хэлбэрт задалж $c$-г ол.</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2⁴ = 16.</t>
+          <t>$16 : 2$ гэж хуваах нь логарифм биш — логарифм бол илтгэгч. Шалгахдаа олсон $c$-ээ $2^c$-д орлуулж $16$ гарахыг тулга.</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -4006,17 +4006,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>lg нь ямар суурьтай логарифм вэ?</t>
+          <t>Аравтын логарифм: $\lg b = \log_{10} b$ ($b &gt; 0$), өөрөөр хэлбэл $\lg b = c \Leftrightarrow 10^c = b$. Натурал логарифм $\ln$ нь $e$ суурьтай тул түүнээс ялгаатай.</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>10^? = 1000.</t>
+          <t>$\lg 1000 = c$ гэж тэмдэглээд $10^c = 1000$ хэлбэрт шилжүүл. $1000$-ыг $10^n$ хэлбэрт бичээд $c$-г ол.</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1000 = 10³.</t>
+          <t>$\lg$-ийг натурал логарифм гэж андуурах нь түгээмэл; $\lg$-ийн суурь $10$. Шалгахдаа олсон $c$-ээр $10^c$-ийг тооцоолж $1000$-тай тулга.</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Гишүүн бүрийг тус тусад нь тооцоолж болно.</t>
+          <t>Тодорхойлолтоор $\log_a a^n = n$ ($a&gt;0$, $a \ne 1$), үүнд $n$ сөрөг байж болно: $\log_a \frac{1}{a} = \log_a a^{-1}$. Мөн $\log_a b + \log_a c = \log_a (bc)$ чанарыг ашиглаж болно.</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>log₃27 = 3, log₃(1/3) = −1.</t>
+          <t>Нэмэгдэхүүн тус бүрийн аргументыг $3^n$ хэлбэрт бичээд тодорхойлолтоор логарифмыг ол, эсвэл үржвэрийн чанараар нэг логарифм болгон нэгтгэ. Хоёр аргаар бодоод харьцуулж болно.</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Нэм.</t>
+          <t>$\log_3 \frac{1}{3}$-ийг $\frac{1}{3}$ гэж үзэх алдаа: логарифм бол аргумент биш, илтгэгч. $a &gt; 1$ үед $1$-ээс бага аргументын логарифм сөрөг байдгийг сана.</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -4166,17 +4166,17 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Логарифмын тодорхойлолтоор зэрэгт хэлбэрт шилжүүл.</t>
+          <t>Хамгийн энгийн логарифм тэгшитгэл: $\log_a f(x) = c \Leftrightarrow f(x) = a^c$, тодорхойлогдох муж $f(x) &gt; 0$. Энэ нь логарифмын тодорхойлолтоос шууд гарна.</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>x − 1 = 2³.</t>
+          <t>Тодорхойлогдох мужийг бич: $x - 1 &gt; 0$. Тодорхойлолтоор логарифмыг арилгаж $x - 1$-ийг 2-ын зэргээр илэрхийлээд шугаман тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>x − 1 = 8 → x = ? Тодорхойлогдох мужийг шалга.</t>
+          <t>$x - 1 = 3 \cdot 2$ гэж үржүүлэх алдаа: $3$ нь илтгэгч болно, үржигдэхүүн биш. Олсон $x$-ээ орлуулж аргумент эерэг, логарифм $3$-тай тэнцүү эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -4246,17 +4246,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай логарифмуудын нийлбэрийг нэг логарифм болго.</t>
+          <t>Үржвэрийн логарифм: $\log_a b + \log_a c = \log_a (bc)$, зөвхөн $b&gt;0$, $c&gt;0$ үед. Энэ хувиргалт тодорхойлогдох мужийг өргөсгөдөг тул илүү шийд гарч болно.</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>log₂(x(x − 2)) = 3 → x(x − 2) = 8.</t>
+          <t>Эхлээд ТМ-ийг ол: $x &gt; 0$ ба $x - 2 &gt; 0$. Логарифмуудыг $\log_2 [x(x-2)]$ болгон нэгтгэж, тодорхойлолтоор квадрат тэгшитгэлд шилжүүлж бод.</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>x = 4 эсвэл x = −2. Тодорхойлогдох муж x &gt; 2 тул аль нь тохирох вэ?</t>
+          <t>Квадрат тэгшитгэлийн хоёр язгуурыг хоёуланг нь хариу болгох алдаа: ТМ-д ороогүй язгуур нь илүү шийд. Язгуур бүрийг анхны тэгшитгэлийн аргумент бүрт орлуулж эерэг эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай логарифмуудын ялгавар юутай тэнцүү вэ?</t>
+          <t>Ялгаврын логарифм: $\log_a b - \log_a c = \log_a \frac{b}{c}$ ($a&gt;0$, $a \ne 1$, $b, c &gt; 0$). Тус тусдаа бүхэл утгагүй логарифмуудыг нэгтгэхэд тохиромжтой.</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>log₅50 − log₅2 = log₅(50/2).</t>
+          <t>Хоёр логарифмыг нэг логарифм болгон нэгтгэ: аргументуудыг хуваа. Гарсан аргументыг 5-ын зэрэг хэлбэрт бичээд тодорхойлолтоор утгыг ол.</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>log₅25 = ?</t>
+          <t>$\log_5 (50 - 2)$ гэж аргументуудыг хасах нь алдаа — логарифмын ялгавар аргументын хуваалтад шилжинэ. Шалгахдаа $5^c$-ийг тооцоолж нэгтгэсэн аргументтай тулга.</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Тэгш өнцөгт гурвалжинд 30°-ийн эсрэг катет гипотенузын хэдэн хувь вэ?</t>
+          <t>Тэгш өнцөгт гурвалжны хурц өнцгийн синус нь эсрэг катетыг гипотенузад харьцуулсан харьцаа: $\sin\alpha = \frac{a}{c}$. Тусгай өнцгийн утгыг тэгш талт гурвалжныг өндрөөр нь хагаслахад үүсэх $30^\circ$–$60^\circ$–$90^\circ$ гурвалжнаас гаргадаг.</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>Эсрэг катет нь гипотенузын хагас.</t>
+          <t>Тал нь $2$ тэгш талт гурвалжныг өндрөөр хувааж тэгш өнцөгт гурвалжин үүсгэ: гипотенуз нь анхны тал, $30^\circ$-ын эсрэг катет нь хуваагдсан суурийн хагас. Энэ хоёр уртыг синусын тодорхойлолтод орлуул.</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>sin = эсрэг катет / гипотенуз.</t>
+          <t>$\sin 30^\circ$-ыг $\cos 30^\circ$-тай бүү андуур: синус эсрэг катетыг, косинус налсан катетыг ашиглана. Шалгах: $30^\circ$ бага өнцөг тул эсрэг катет нь богино бөгөөд $\sin 30^\circ &lt; \cos 30^\circ$ байх ёстой.</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4486,17 +4486,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Утга бүрийг хүснэгтээс санаж үз.</t>
+          <t>Нэгж тойргийн $\alpha$ өнцөгт харгалзах цэг нь $(\cos\alpha;\ \sin\alpha)$ координаттай — энэ нь синус, косинусын ерөнхий тодорхойлолт. Хурц өнцгийн хувьд энэ нь тэгш өнцөгт гурвалжны харьцаатай давхцана.</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>cos 60° = 1/2, sin 90° = 1.</t>
+          <t>$\cos 60^\circ$-ыг $30^\circ$–$60^\circ$–$90^\circ$ гурвалжнаас ($60^\circ$-ын налсан катет / гипотенуз) ол. $\sin 90^\circ$-ыг нэгж тойргийн $90^\circ$-д харгалзах цэгийн $y$ координатаар тодорхойлоод хоёр утгыг нэм.</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Нэм.</t>
+          <t>$\sin 90^\circ$-ыг $0$ гэж бүү бод — $90^\circ$-ын цэг нь тойргийн хамгийн дээд цэг тул синус хамгийн их утгаа авна. Шалгах: синус, косинус $[-1;1]$ мужид оршдог тул нийлбэр нь $2$-оос хэтрэхгүй.</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -4566,17 +4566,17 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>sin²α + cos²α = 1 адилтгалыг ашигла.</t>
+          <t>Тригонометрийн үндсэн адилтгал: ямар ч $\alpha$-д $\sin^2\alpha + \cos^2\alpha = 1$ (нэгж тойрог дээрх Пифагорын теорем). Нэг функцийн утга мэдэгдэж байвал нөгөөгийнх нь квадратыг олоход хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>cos²α = 1 − 9/25 = 16/25.</t>
+          <t>Адилтгалаас $\cos^2\alpha = 1 - \sin^2\alpha$ гэж илэрхийлээд синусын утгыг квадрат зэрэгт дэвшүүлж орлуул. Дараа нь квадрат язгуур гаргаж, тэмдгийг өнцгийн мөчлөгөөр сонго.</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Хурц өнцөг тул cos α &gt; 0.</t>
+          <t>$\cos\alpha = 1 - \sin\alpha$ гэж квадратгүй хасах нь алдаа — адилтгал квадратуудын тухай. Хурц өнцөгт $\cos\alpha &gt; 0$ тул эерэг язгуурыг ав; гарсан утгуудын квадратын нийлбэр $1$ эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Утга бүрийг тусад нь ол.</t>
+          <t>$\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha}$, харин $\sin^2\alpha$ гэдэг нь $(\sin\alpha)^2$ гэсэн тэмдэглэгээ. Тусгай өнцгийн утгыг тэгш өнцөгт гурвалжин ба нэгж тойргоос гаргана.</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>tg 45° = 1, cos 0° = 1, sin 30° = 1/2.</t>
+          <t>$\operatorname{tg}45^\circ$-ыг тэгш өнцөгт адил хажуут гурвалжнаас (катетууд тэнцүү), $\cos 0^\circ$-ыг нэгж тойргийн $0^\circ$-ын цэгээс, $\sin 30^\circ$-ыг $30^\circ$–$60^\circ$–$90^\circ$ гурвалжнаас ол. Орлуулаад эхлээд зэрэг, үржвэрээ бодоод дараа нь хас.</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1·1 − (1/2)².</t>
+          <t>$\sin^2 30^\circ$-ыг $2\sin 30^\circ$ гэж бүү ойлго — синусын утгыг өөрөөр нь үржүүлнэ. Үйлдлийн дарааллыг баримтал; хариу $0$ ба $1$-ийн хооронд байх ёстойг шалга.</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -4726,17 +4726,17 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Нэгж тойрог дээр синус нь y координат. y = 1/2 шулуун тойргийг хэдэн цэгт огтлох вэ?</t>
+          <t>Нэгж тойрог дээр $x$ өнцөгт харгалзах цэгийн ординат нь $\sin x$. $\sin x = a$ ($0 &lt; a &lt; 1$) тэгшитгэл $[0; 2\pi)$ завсарт хоёр шийдтэй: $x_1 = \arcsin a$ (I мөчлөг) ба $x_2 = \pi - \arcsin a$ (II мөчлөг).</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>Нэг шийд нь π/6.</t>
+          <t>$y = \frac{1}{2}$ хэвтээ шулууныг нэгж тойрогтой огтлолцуул. I мөчлөгийн огтлолцлын цэгийн өнцгийг тусгай өнцгөөс радианаар олоод, II мөчлөгийн шийдийг $\pi - x_1$ томьёогоор гарга.</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Хоёр дахь шийд нь π − π/6.</t>
+          <t>Ганц шийд бичих нь түгээмэл алдаа — синус I ба II мөчлөгт хоёуланд нь эерэг. Шийд бүр $[0; 2\pi]$ завсарт орж, тэгшитгэлд орлуулахад биелж байгааг шалга.</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4806,17 +4806,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэрийг өөр хэлбэрээр бичих адилтгал бий юу?</t>
+          <t>Үндсэн адилтгал $\sin^2\alpha + \cos^2\alpha = 1$-ээс $1 - \cos^2\alpha$ хэлбэрийн илэрхийллийг нэг гишүүнээр сольж болно. Бутархайг хураахдаа хүртвэр, хуваарийн тэгээс ялгаатай ерөнхий үржигдэхүүнийг л хураана.</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1 − cos²α = sin²α.</t>
+          <t>Хүртвэрийг үндсэн адилтгалаар нэг функцийн квадрат болгон бич. Дараа нь квадратыг хоёр ижил үржигдэхүүн болгон задлаад хуваарьтай ижил үржигдэхүүнийг хураа.</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>sin²α / sin α-г хураа.</t>
+          <t>$1 - \cos^2\alpha$ нь $(1-\cos\alpha)^2$ биш — квадрат зөвхөн косинуст хамаарна. Хураалт $\sin\alpha \ne 0$ нөхцөлөөр зөвшөөрөгдөнө; $\alpha = 30^\circ$ орлуулж анхны ба хялбарчилсан илэрхийллийг харьцуулж шалга.</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -4886,17 +4886,17 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Шоо хаяхад нийт хэдэн боломжит үр дүн бий вэ?</t>
+          <t>Сонгодог магадлал: бүх үр дүн адил боломжтой үед $P(A) = \frac{m}{n}$, энд $n$ — бүх боломжит үр дүнгийн тоо, $m$ — $A$ үзэгдэлд таатай үр дүнгийн тоо. Магадлал үргэлж $0 \le P(A) \le 1$ байна.</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Тэгш тоонууд: 2, 4, 6.</t>
+          <t>Шооны боломжит үр дүнгийн олонлогийг бичиж $n$-ийг ол. Түүнээс тэгш тоонуудыг ялгаж $m$-ийг тоолоод $\frac{m}{n}$-ийг бичиж хураа.</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>P = таатай / нийт.</t>
+          <t>Тэгш тоог тоолохдоо хамгийн их нүүрийг мартах нь түгээмэл — элемент бүрийг $2$-т хуваагдах эсэхээр нэг бүрчлэн шалга. Тэгш ба сондгой үр дүнгийн магадлалын нийлбэр $1$ болохыг шалгаж болно.</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4966,17 +4966,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Нийт хэдэн бөмбөг байна вэ?</t>
+          <t>Сонгодог магадлал: бүх үр дүн адил боломжтой үед $P(A) = \frac{m}{n}$, энд $n$ — бүх боломжит үр дүнгийн тоо, $m$ — $A$ үзэгдэлд таатай үр дүнгийн тоо. Магадлал үргэлж $0 \le P(A) \le 1$ байна.</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>Нийт 8, улаан 3.</t>
+          <t>Нийт бөмбөгийн тоо нь бүх боломжит үр дүнгийн тоо $n$, улаан бөмбөгийн тоо нь таатай үр дүнгийн тоо $m$. Хоёуланг нь тодорхойлоод $\frac{m}{n}$ харьцааг бич.</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>P = 3/8.</t>
+          <t>Улааныг цэнхэрт харьцуулах нь алдаа — хуваарь нь заавал бүх бөмбөгийн тоо. Шалгах: улаан ба цэнхэр гарах магадлалын нийлбэр $1$ байх ёстой.</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5046,17 +5046,17 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Эхний байранд хэдэн сурагч зогсож болох вэ? Хоёр дахь байранд?</t>
+          <t>$n$ ялгаатай элементийг бүгдийг нь дараалуулан байрлуулах арга бүрийг сэлгэмэл гэнэ, тоо нь $P_n = n! = 1 \cdot 2 \cdot \ldots \cdot n$. Үржүүлэх дүрмээс гарна: байр бүрт өмнөх байрнаасаа нэгээр цөөн сонголт үлдэнэ.</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>5 · 4 · 3 · 2 · 1.</t>
+          <t>Эгнээний байруудыг дараалан бөглөнө гэж үзээд байр бүрт хэдэн сурагч сонгох боломжтойг тоол. Сонголтын тоонуудыг үржүүлж факториалыг бод.</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Энэ нь 5! = ?</t>
+          <t>$5 \cdot 5$ гэх нь алдаа — нэг сурагч хоёр байрт зогсохгүй тул байр бүрт сонголт нэгээр багасна. Шалгах: $3$ сурагчийн бүх байрлалыг жагсааж тоо нь $3!$-тай тэнцэхийг тулга.</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -5126,17 +5126,17 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Багт гишүүдийн дараалал чухал уу?</t>
+          <t>Хэсэглэл: $n$ элементээс $k$-г дараалал харгалзахгүй сонгох арга, тоо нь $C_n^k = \frac{n!}{k!\,(n-k)!}$. Багийн гишүүд ялгаатай албан тушаалгүй тул дараалал чухал биш.</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>Дараалал чухал биш тул хэсэглэл: C(8,3) = 8!/(3!·5!).</t>
+          <t>Томьёонд $n = 8$, $k = 3$-ыг орлуул. Хүртвэрийн $8!$-ийг $8 \cdot 7 \cdot 6 \cdot 5!$ гэж задлаад хуваарийн $5!$-тэй хураавал тооцоо хялбарна.</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>(8·7·6)/(3·2·1).</t>
+          <t>$8 \cdot 7 \cdot 6$ нь байрлуулал — нэг багийг $3!$ янзаар давтан тоолсон байна. Шалгах: $C_8^3 = C_8^5$ байх ёстой, мөн хариу бүхэл тоо гарна.</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Хоёр шоо хаяхад нийт хэдэн хос үр дүн бий вэ?</t>
+          <t>Хоёр шооны туршилтын үр дүнгийн огторгуй нь адил боломжтой $(a; b)$ эрэмбэлэгдсэн хосуудаас тогтоно. Сонгодог магадлал $P = \frac{m}{n}$-ийг хосоор тоолж хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>Нийт 6 · 6 = 36. Нийлбэр 7 болох хосуудыг жагсаа.</t>
+          <t>Үржүүлэх дүрмээр нийт хосын тоог ол. Эхний шооны утга бүрд нийлбэрийг $7$ болгох хоёр дахь шооны утга байгаа эсэхийг шалгаж таатай хосуудыг жагсаа.</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>(1,6), (2,5), … нийт 6 хос.</t>
+          <t>Нийлбэрийн $2$-оос $12$ хүртэлх утгууд адил магадлалтай биш — нийлбэр бүрийг өгөх хосын тоо өөр. $(1;6)$ ба $(6;1)$ нь өөр хос тул тус тусад нь тоол.</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5286,17 +5286,17 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Нийт хэдэн боломжит үр дүн бий вэ?</t>
+          <t>Бернуллийн томьёо: $n$ бие даасан туршилт бүрт үзэгдэл $p$ магадлалтай бол яг $k$ удаа биелэх магадлал $P_n(k) = C_n^k p^k (1-p)^{n-k}$. Зоосны хаялтууд бие биеэсээ хамааралгүй, $p = \frac{1}{2}$.</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>Нийт 2³ = 8. Яг 2 сүлд байх хувилбаруудыг жагсаа (ССТ, СТС, ...).</t>
+          <t>Нийт үр дүн нь хаялт бүрийн $2$ боломжийн үржвэр; яг $2$ сүлдтэй дарааллууд нь сүлд аль хаялтуудад буухаар ялгагдана. Тэр сонголтын тоог хэсэглэлээр олоод нийт үр дүнд харьцуул.</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Ийм хувилбар C(3,2) = 3.</t>
+          <t>Дарааллыг үл тоомсорлож ганц хувилбар гэж үзэх нь алдаа — ССТ ба СТС нь өөр үр дүн. Шалгах: $k = 0, 1, 2, 3$ бүх тохиолдлын магадлалын нийлбэр $1$ болох ёстой.</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -5362,17 +5362,17 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>5 нь 5^1 гэдгийг сана.</t>
+          <t>Ижил суурьтай зэргийн үржвэр: $a^m \cdot a^n = a^{m+n}$. Илтгэгчгүй бичигдсэн тоо нь нэгдүгээр зэрэг: $a = a^1$.</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай бол илтгэгчийг нэмнэ: 5^(2+1).</t>
+          <t>Үржигдэхүүн 5-ыг илтгэгчтэй хэлбэрээр бичээд, хоёр зэргийн илтгэгчийг нэмж нэг зэрэг болго. Гарсан зэргийг тодорхойлолт ёсоор тооцоол.</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5^3-ыг тооцоол.</t>
+          <t>Суурийг илтгэгчээр үржүүлэх нь алдаа: $5^2 = 5 \cdot 5$, харин $5 \cdot 2$ биш. Шалгахдаа $5^2$-ийг тоогоор бодоод 5-аар үржүүлж, хариугаа харьцуул.</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай зэргийг хуваахад илтгэгч нь юу болдог вэ?</t>
+          <t>Ижил суурьтай зэргийн ногдвор: $\frac{a^m}{a^n} = a^{m-n}$ ($a \ne 0$). Учир нь хүртвэр, хуваарийн $n$ ширхэг ижил үржигдэхүүн хураагдаж, $m - n$ ширхэг үлдэнэ.</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>a^m : a^n = a^(m−n).</t>
+          <t>Суурь ижил тул нэг зэрэг болгон бичиж, хүртвэрийн илтгэгчээс хуваарийн илтгэгчийг хас. Гарсан зэргийг тоогоор тооцоол.</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>7^2-ыг тооцоол.</t>
+          <t>Илтгэгчийг хуваах ($7^{5/3}$) нь буруу — зэргийг хуваахад илтгэгч хасагдана. Шалгахдаа хүртвэр, хуваарийг $7 \cdot 7 \cdot \ldots$ гэж задлан бичээд ижил үржигдэхүүнийг хураа.</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -5514,17 +5514,17 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Эхлээд зэрэг, дараа нь үржих, хамгийн сүүлд нэмэх.</t>
+          <t>Үйлдлийн дараалал: хаалт → зэрэг, язгуур → үржих, хуваах (зүүнээс баруун) → нэмэх, хасах (зүүнээс баруун). Зэрэг нь зөвхөн шууд өмнөх суурьдаа хамаарна.</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>4^2 = 16.</t>
+          <t>Эхлээд $4^2$-ийг бод, дараа нь гарсан тоог 2-оор үржүүл. Хамгийн сүүлд 3-ыг нэм.</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3 + 2·16-г тооцоол.</t>
+          <t>Зүүнээс баруун тийш дараалан бодож $(3+2) \cdot 4^2$ гэх нь алдаа — хаалт байхгүй тул нэмэх үйлдэл хамгийн сүүлд хийгдэнэ. Мөн $2 \cdot 4^2$-ийг $8^2$ гэж бүү бод.</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5590,17 +5590,17 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Бутархайг үржүүлэхдээ хүртвэрийг хүртвэрээр, хуваарийг хуваариар үржүүлнэ.</t>
+          <t>Бутархайн үржвэр: $\frac{a}{b} \cdot \frac{c}{d} = \frac{ac}{bd}$ ($b, d \ne 0$). Үржүүлэхээс өмнө аль ч хүртвэр ба аль ч хуваарийг ерөнхий хуваагчид нь хувааж хураах нь тооцоог хялбарчилна.</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>Үржүүлэхээс өмнө 2 ба 4, 3 ба 9-ийг хураа.</t>
+          <t>Нэг бутархайн хүртвэр ба нөгөөгийн хуваарийн ерөнхий хуваагчийг ол (2 ба 4; 9 ба 3) — тэдгээрийг хураа. Дараа нь үлдсэн хүртвэрүүдийг хооронд нь, хуваариудыг хооронд нь үржүүл.</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>1·3 / 1·2.</t>
+          <t>Үржүүлэхэд ерөнхий хуваарь хэрэггүй — энэ нь нэмэх, хасахын дүрэм. Шалгахдаа хураалгүйгээр шууд үржүүлж, дараа нь хураасан үр дүнгээ эхний аргын хариутай харьцуул.</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -5666,17 +5666,17 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Хасахын өмнө хуваарийг ижил болго.</t>
+          <t>Ялгаатай хуваарьтай бутархайг хасахдаа ерөнхий хуваарьт шилжүүлнэ: $\frac{a}{b} - \frac{c}{d} = \frac{ad - cb}{bd}$ ($b, d \ne 0$). Хамгийн бага ерөнхий хуваагдагчийг (ХБЕХ) авбал тооцоо хялбар.</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>6 ба 4-ийн хамгийн бага ерөнхий хуваагдагч 12.</t>
+          <t>6 ба 4-ийн ХБЕХ-ийг ол. Бутархай бүрийг тэр хуваарьтай болгож өргөтгөөд, хүртвэрүүдийг хас.</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>10/12 − 3/12.</t>
+          <t>Хүртвэрийг хүртвэрээс, хуваарийг хуваариас тус тусад нь хасах нь алдаа. Үр дүн хураагдах эсэхийг шалгаж, ойролцоо утгаар $0{,}83 - 0{,}25$ гэж үнэлэн хариугаа тулга.</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5742,17 +5742,17 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>(a^m)^n = a^(m·n).</t>
+          <t>Зэргийн зэрэг: $(a^m)^n = a^{mn}$; ижил суурьтай зэргийн ногдвор: $a^m : a^n = a^{m-n}$ ($a \ne 0$). Зэргийн зэрэгт илтгэгчүүд үржигдэнэ, учир нь $a^m$-ийг $n$ удаа өөрөөр нь үржүүлж байна.</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>(2^3)^2 = 2^6.</t>
+          <t>Эхлээд хаалтыг зэргийн зэргийн дүрмээр нэг зэрэг болго. Дараа нь 2-ын хоёр зэргийг хувааж, илтгэгчүүдийг хас.</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>2^6 : 2^4 = 2^2.</t>
+          <t>$(2^3)^2$-д илтгэгчийг нэмэх нь алдаа — нэмэх нь $a^m \cdot a^n$ үржвэрийн дүрэм. Шалгахдаа $2^3$-ийг тоогоор бодож квадрат зэрэгт дэвшүүлээд, $2^4$-ийн утгад хуваа.</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -5818,17 +5818,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>a^(−n) = 1/a^n.</t>
+          <t>Сөрөг илтгэгчийн тодорхойлолт: $a^{-n} = \frac{1}{a^n}$ ($a \ne 0$). Иймээс сөрөг илтгэгчтэй зэрэг нь $a^n$-ийн урвуу тоо бөгөөд тэмдэг нь сөрөг болохгүй.</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>2^(−3) = 1/8, 4^(−1) = 1/4.</t>
+          <t>Гишүүн бүрийг $\frac{1}{a^n}$ хэлбэрт бичиж энгийн бутархай болго. Дараа нь хоёр бутархайг ерөнхий хуваарьт оруулж нэм.</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>1/8 + 2/8.</t>
+          <t>$2^{-3}$-ийг $-8$ эсвэл $-6$ гэж бодох нь түгээмэл алдаа — эерэг суурьтай зэрэг үргэлж эерэг. Хариу эерэг бөгөөд 1-ээс бага байх ёстойг шалга.</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5894,17 +5894,17 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Язгуур доорх тоог бүтэн квадратаар задал.</t>
+          <t>Сөрөг биш $a, b$-ийн хувьд $\sqrt{a^2 b} = a\sqrt{b}$. Язгуур доорх илэрхийлэл нь ижил язгууруудыг төсөөтэй гишүүн шиг нэмнэ: $m\sqrt{b} + n\sqrt{b} = (m+n)\sqrt{b}$.</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>12 = 4·3, 27 = 9·3.</t>
+          <t>12 ба 27-г бүтэн квадрат ба 3-ын үржвэр болгон задал. Квадрат хэсгийг язгуураас гаргаад, ижил язгууртай гишүүдийн коэффициентуудыг нэм.</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>2√3 + 3√3.</t>
+          <t>$\sqrt{a} + \sqrt{b} \ne \sqrt{a+b}$ — язгуур доор нэмж болохгүй. Шалгахдаа $\sqrt{12} \approx 3{,}46$ ба $\sqrt{27} \approx 5{,}20$-ийн нийлбэрийг хариуныхаа ойролцоо утгатай харьцуул.</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -5970,17 +5970,17 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>√a · √b = √(a·b).</t>
+          <t>Язгуурын үржвэр: $\sqrt{a} \cdot \sqrt{b} = \sqrt{ab}$ ($a, b \ge 0$). Энэ дүрэм зөвхөн үржих, хуваахад хүчинтэй, нэмэхэд хамаарахгүй.</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>√36.</t>
+          <t>Хоёр язгуурыг нэг язгуурын дор нэгтгэж, язгуур доорх тоонуудыг үржүүл. Гарсан тоо бүтэн квадрат эсэхийг шалгаж язгуураас гарга.</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>36-ийн квадрат язгуур.</t>
+          <t>Язгуур доорх тоонуудыг нэмэх ($\sqrt{3+12}$) нь алдаа. Хариу бүхэл тоо гарах ёстой бөгөөд $\sqrt{3} \approx 1{,}73$ ба $\sqrt{12} \approx 3{,}46$-ийн үржвэртэй ойролцоо эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -6046,17 +6046,17 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Тоонуудыг тус тусад нь, 10-ын зэргүүдийг тус тусад нь үржүүл.</t>
+          <t>Үржвэрийн солих, бүлэглэх хуулиар $(a \cdot 10^m)(b \cdot 10^n) = ab \cdot 10^{m+n}$. Энэ нь ижил суурьтай зэргийн үржвэрийн дүрэм $a^m \cdot a^n = a^{m+n}$ дээр тулгуурлана.</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>3·2 = 6, 10^4 · 10^(−2) = 10^2.</t>
+          <t>Тоон коэффициентуудыг хооронд нь, 10-ын зэргүүдийг хооронд нь бүлэглэ. 10-ын зэргүүдийн илтгэгчийг тэмдгийг нь анхааран нэмээд, үр дүнг энгийн тоогоор бич.</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>6·100.</t>
+          <t>10-ын зэргүүдийг үржүүлэхэд илтгэгчийг үржүүлэх нь алдаа — илтгэгчүүд нэмэгдэнэ. Хэмжээгээр шалга: $3 \cdot 10^4 = 30000$ ба $2 \cdot 10^{-2} = 0{,}02$ гэж бичээд шууд үржүүлж харьцуул.</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -6122,17 +6122,17 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>a^(m/n) = (ⁿ√a)^m.</t>
+          <t>$a^{\frac{m}{n}} = \left(\sqrt[n]{a}\right)^m$ ба $a^{-r} = \frac{1}{a^r}$ ($a &gt; 0$). Суурийг өөр тооны зэрэг хэлбэрт бичвэл $(b^k)^r = b^{kr}$ дүрмээр хялбар бодогдоно.</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>32 = 2^5 тул 32^(2/5) = 2^2 = 4; 9^(−1/2) = 1/3.</t>
+          <t>32-ыг 2-ын зэрэг, 9-ийг 3-ын зэрэг хэлбэрт бичээд илтгэгчүүдийг үржүүл. Сөрөг илтгэгчтэй гишүүнийг урвуу тоо болгоод, бүхэл тоо ба бутархайг ерөнхий хуваарьт оруулж нэм.</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4 + 1/3.</t>
+          <t>Суурийг илтгэгчээр үржүүлэх ($32 \cdot \frac{2}{5}$) нь алдаа. $9^{-\frac{1}{2}}$ нь эерэг бөгөөд 1-ээс бага; хариугаа энгийн бутархай хэлбэрт үлдээ.</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -6198,17 +6198,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>6^5 = (2·3)^5 = 2^5 · 3^5.</t>
+          <t>Үржвэрийн зэрэг: $(ab)^n = a^n b^n$; ижил суурьтай зэргийн ногдвор: $\frac{a^m}{a^n} = a^{m-n}$ ($a \ne 0$). Ялгаатай суурьтай зэргүүдийг хураахын тулд эхлээд суурийг анхны үржигдэхүүнд задална.</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2^5-ууд хураагдана.</t>
+          <t>6-г $2 \cdot 3$ гэж задлаад хүртвэрийг 2 ба 3-ын зэргүүдийн үржвэр болго. Дараа нь ижил суурьтай зэргүүдийг хүртвэр, хуваарьт тус тусад нь хураа.</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3^5 : 3^3 = 3^2.</t>
+          <t>$\frac{6^5}{2^5}$-ийг илтгэгчгүйгээр 3 гэж хуваах нь алдаа: $\frac{a^n}{b^n} = \left(\frac{a}{b}\right)^n$ тул илтгэгч хадгалагдана. Хариу бүхэл тоо гарч, хуваарьт 2 эсвэл 3 үлдэхгүй байх ёстой.</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -6274,17 +6274,17 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>(a − b)(a + b) томьёог сана.</t>
+          <t>Квадратуудын ялгаврын томьёо: $(a-b)(a+b) = a^2 - b^2$. Мөн $a \ge 0$ үед $(\sqrt{a})^2 = a$ тул язгууртай илэрхийллийн үржвэр бүхэл тоо болж болно.</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>(√5)^2 − 1^2.</t>
+          <t>$a = \sqrt{5}$, $b = 1$ гэж томьёонд тааруул. Гишүүн бүрийг квадрат зэрэгт дэвшүүлж ялгаврыг ол.</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>5 − 1.</t>
+          <t>$\sqrt{5} \cdot \sqrt{5}$ нь $\sqrt{10}$ биш — язгуурын тодорхойлолтоор язгуур доорх тоо өөрөө. Шалгахдаа хаалтыг гишүүнчлэн үржүүл: дунд гишүүд $-\sqrt{5}$ ба $+\sqrt{5}$ хураагдах ёстой.</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6350,17 +6350,17 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Анхны үнийг x гэвэл 20% нэмэгдсэн үнэ x-ийн хэдэн хувь вэ?</t>
+          <t>Хэмжигдэхүүн $p\%$-иар нэмэгдвэл шинэ утга нь $x\left(1 + \frac{p}{100}\right)$ болно. Хувь нь үргэлж анхны утгаас тооцогддог тул анхны утгыг үл мэдэгдэгч болгоно.</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>120% = 1,2 тул 1,2x = 24000.</t>
+          <t>Анхны үнийг $x$ гэж тэмдэглээд, нэмэгдсэн үнэ нь анхны үнийн хэдэн хувь болохыг аравтын бутархайгаар илэрхийл. Тэгшитгэл зохиож, хоёр талыг $x$-ийн коэффициентод хуваа.</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 1,2-т хуваа.</t>
+          <t>24000-ын 20%-ийг хасах нь алдаа: 20% нь эцсийн үнээс биш, анхны үнээс тооцогддог. Шалгахдаа олсон анхны үнээ 20%-иар нэмэгдүүлэхэд 24000 гарах ёстой.</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -6430,17 +6430,17 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>2-ыг хаалтан доторх гишүүн бүрээр үржүүл.</t>
+          <t>Хуваарилах хууль: $a(b + c) = ab + ac$ — хаалтын өмнөх үржигдэхүүн хаалтан доторх гишүүн бүрийг үржүүлнэ. Дараа нь төсөөтэй гишүүдийг коэффициентоор нь нэгтгэнэ.</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>6x + 2 − 4x.</t>
+          <t>2-ыг $3x$-ээр ба 1-ээр хоёуланг нь үржүүлж хаалтыг задал. Дараа нь $x$-тэй гишүүдийг нэгтгэж, сул гишүүнийг тусад нь бич.</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Төсөөтэй гишүүдийг нэгтгэ.</t>
+          <t>2-ыг зөвхөн эхний гишүүнээр үржүүлж, сул гишүүнийг өөрчлөлгүй үлдээх нь алдаа. $x = 1$ орлуулж анхны илэрхийлэл ба таны хариу ижил утгатай эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6510,17 +6510,17 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Хаалтын өмнөх хасах тэмдэг дотор нь орохдоо гишүүн бүрийн тэмдгийг солино.</t>
+          <t>Хаалтын өмнөх хасах тэмдэг нь $-1$-ээр үржүүлэхтэй адил: $-(a - b) = -a + b$. Иймээс хаалт задлахад доторх гишүүн бүрийн тэмдэг эсрэгээр солигдоно.</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>−x + 5 + 3x.</t>
+          <t>Хаалтыг задлахдаа хоёр гишүүний тэмдгийг хоёуланг нь соль. Дараа нь $x$-тэй гишүүдийг нэгтгэж, сул гишүүнийг тусад нь бич.</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Нэгтгэ.</t>
+          <t>Зөвхөн эхний гишүүний тэмдгийг сольж $-x - 5$ гэж бичих нь түгээмэл алдаа. $x = 1$ орлуулж анхны ба хялбарчилсан илэрхийллийн утгыг харьцуул.</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -6590,17 +6590,17 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>x²-тэй гишүүд ба x-тэй гишүүд төсөөтэй биш.</t>
+          <t>Төсөөтэй гишүүдийн хувьсагч ба түүний илтгэгч яг ижил байх ёстой: $x^2$ ба $x$ төсөөтэй биш. Нэгтгэхдээ $mx^k + nx^k = (m+n)x^k$ — илтгэгч өөрчлөгдөхгүй.</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>3x² − x² = 2x².</t>
+          <t>$x^2$-тэй гишүүдийг нэг бүлэг, $x$-тэй гишүүдийг нөгөө бүлэг болгон тэмдэгтэй нь бүлэглэ. Бүлэг тус бүрийн коэффициентыг нэгтгэж, зэргийн бууралтаар бич.</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>2x + 4x = 6x.</t>
+          <t>Бүх гишүүнийг нэгтгэж $x^3$ гаргах нь алдаа — нэмэхэд илтгэгч нэмэгддэггүй. $-x^2$-ийн коэффициент $-1$ гэдгийг анхаар; $x = 1$ орлуулж шалга.</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6670,17 +6670,17 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>6 ба 9-ийн ерөнхий хуваагч хэд вэ? x² ба x-ийн ерөнхий үржигдэхүүн?</t>
+          <t>Ерөнхий үржигдэхүүнийг хаалтын өмнө гаргах нь хуваарилах хуулийн урвуу хэрэглээ: $ab + ac = a(b + c)$. Хамгийн их ерөнхий үржигдэхүүн нь коэффициентуудын ХИЕХ ба хувьсагчийн хамгийн бага илтгэгчтэй зэргийн үржвэр.</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>3x-ийг гарга.</t>
+          <t>6 ба 9-ийн хамгийн их ерөнхий хуваагчийг, мөн $x^2$ ба $x$-д хоёуланд нь орох $x$-ийн хамгийн их зэргийг ол. Гишүүн бүрийг энэ ерөнхий үржигдэхүүнд хувааж, ногдворуудыг хаалтад бич.</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>6x² : 3x = 2x, 9x : 3x = 3.</t>
+          <t>Зөвхөн тоон хүчин зүйлийг гаргаж, $x$-ийг хаалтад үлдээх нь бүрэн задлал биш. Хаалтыг буцааж задлахад анхны илэрхийлэл гарах, хаалтан доторх гишүүдэд ерөнхий үржигдэхүүн үлдээгүйг шалга.</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>x-ийн оронд −2-ыг хаалттай орлуул.</t>
+          <t>Илэрхийллийн утга гэдэг нь хувьсагчийн оронд өгөгдсөн тоог орлуулж, үйлдлийн дарааллаар бодсон тоо. Сөрөг тооны тэгш зэрэг эерэг: $(-a)^2 = a^2$, харин $-a^2 = -(a^2)$.</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>(−2)² = 4, −3·(−2) = 6.</t>
+          <t>$x$ бүрийн оронд $-2$-ыг хаалтанд хийж орлуул. Эхлээд зэргийг, дараа нь үржвэрийг тэмдгийн дүрмээр бодоод, бүх гишүүнийг нэм.</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4 + 6 + 1.</t>
+          <t>$(-2)^2$-ийг $-4$ гэж бодох нь түгээмэл алдаа. Мөн $-3 \cdot (-2)$-т хоёр сөрөг тооны үржвэр эерэг гэдгийг анхаар.</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>(a − b)² = a² − 2ab + b².</t>
+          <t>Ялгаврын квадрат: $(a-b)^2 = a^2 - 2ab + b^2$. $a$ нь коэффициенттэй гишүүн байвал $(ka)^2 = k^2 a^2$ гэдгийг хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>a = 2x, b = 1.</t>
+          <t>$a = 2x$, $b = 1$ гэж тааруул. $a^2$-ийг бодохдоо коэффициент ба хувьсагчийг хоёуланг нь квадрат зэрэгт дэвшүүл, дараа нь давхар үржвэр ба $b^2$-ийг бич.</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>(2x)² − 2·2x·1 + 1.</t>
+          <t>Дунд гишүүн $-2ab$-г мартах, эсвэл $(2x)^2$-ийг $2x^2$ гэж бодох нь түгээмэл алдаа. $x = 1$ орлуулж шалга: $(2 - 1)^2$ нь таны олон гишүүнтийн утгатай тэнцэх ёстой.</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -6910,17 +6910,17 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>(a − b)(a + b) = a² − b².</t>
+          <t>Квадратуудын ялгаврын томьёо: $(a-b)(a+b) = a^2 - b^2$. Гишүүнчлэн үржүүлэхэд $-ab$ ба $+ab$ гишүүд хураагдаж, хоёр гишүүн л үлддэг.</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>a = x, b = 4.</t>
+          <t>Хоёр хаалт зөвхөн дунд тэмдгээрээ ялгаатайг ажигла. $a$ ба $b$-г тодорхойлоод томьёонд орлуул.</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>x² − 4².</t>
+          <t>$-8x$ гэх мэт дунд гишүүн нэмж бичих нь алдаа — эсрэг тэмдэгтэй хоёр дунд гишүүн бие биеэ устгана. Хаалтыг гишүүнчлэн үржүүлж шалга.</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6990,17 +6990,17 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>4x² ба 25 нь юуны квадрат вэ?</t>
+          <t>Квадратуудын ялгавар: $a^2 - b^2 = (a-b)(a+b)$. Коэффициенттэй гишүүнийг $k^2 x^2 = (kx)^2$ гэж бүтэн квадрат хэлбэрт бичиж болно.</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>(2x)² − 5².</t>
+          <t>$4x^2$ ба 25 тус бүр ямар илэрхийллийн квадрат болохыг тодорхойлж $a$, $b$-г ол. Тэдгээрийг $(a-b)(a+b)$-д орлуул.</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>a² − b² = (a − b)(a + b).</t>
+          <t>$a$, $b$ нь квадрат язгуурууд — $4x^2$ ба 25-ыг өөрсдийг нь хаалтад бичих нь алдаа. Хаалтуудаа үржүүлж задлахад $4x^2 - 25$ гарч байгаа эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -7070,17 +7070,17 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр нь 10, нийлбэр нь 7 болох хоёр тоо ол.</t>
+          <t>$(x+p)(x+q) = x^2 + (p+q)x + pq$ адилтгал хүчинтэй. Иймээс $x^2 + bx + c$-г задлахын тулд $p + q = b$, $pq = c$ байх $p$, $q$ тоонуудыг олно.</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2 ба 5.</t>
+          <t>10-ын хуваагчдын хосуудыг жагсаагаад, нийлбэр нь 7 болох хосыг сонго. Үржвэр ба нийлбэр хоёулаа эерэг тул хоёр тоо хоёулаа эерэг.</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>(x + 2)(x + 5).</t>
+          <t>Зөвхөн үржвэрийг тааруулж нийлбэрийг шалгахгүй байх нь алдаа (жишээ нь $1 \cdot 10$). Хаалтуудаа үржүүлж дунд гишүүн $7x$ гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -7150,17 +7150,17 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Гишүүдийг хоёр хоёроор нь бүлэгл.</t>
+          <t>Бүлэглэх арга: гишүүдийг ерөнхий үржигдэхүүнтэй хос болгон бүлэглэж, бүлэг тус бүрээс үржигдэхүүн гаргана. Бүлгүүдэд ижил хаалт үлдвэл $ac + bc = (a+b)c$ дүрмээр түүнийг гаргана.</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>x(x + 3) + y(x + 3).</t>
+          <t>Эхний хоёр гишүүнийг, сүүлийн хоёр гишүүнийг тус тусад нь бүлэглэ. Бүлэг бүрээс ерөнхий үржигдэхүүнийг гаргаад, гарч ирсэн ижил хаалтыг дахин хаалтын өмнө гарга.</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Ерөнхий хаалт (x + 3)-ыг гарга.</t>
+          <t>Хоёр бүлгийн нийлбэр хэлбэрээр зогсох нь задлал дуусаагүй гэсэн үг — үржвэр хэлбэрт хүртэл гүйцээ. Хаалтуудаа үржүүлж дөрвөн гишүүн бүгд гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -7230,17 +7230,17 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэр нь бүтэн квадрат уу?</t>
+          <t>Нийлбэрийн квадрат: $a^2 + 2ab + b^2 = (a+b)^2$; рационал илэрхийллийг хураахдаа $\frac{ac}{bc} = \frac{a}{b}$ ($c \ne 0$). Хүртвэрийг үржигдэхүүнд задалж байж л хураах боломжтой.</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>x² + 6x + 9 = (x + 3)².</t>
+          <t>Хүртвэр бүтэн квадрат эсэхийг шалга: эхний ба сүүлийн гишүүн бүтэн квадрат, дунд гишүүн давхар үржвэр эсэх. Задлаад $x \ne -3$ нөхцөлөөр хуваарьтай ижил үржигдэхүүнийг хураа.</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>(x + 3)² : (x + 3).</t>
+          <t>$x^2$-ийг $x$-д, 9-ийг 3-т тус тусад нь хуваах нь алдаа — зөвхөн үржигдэхүүнийг хураана. $x = 1$ орлуулж анхны бутархай ба хариуны утгыг харьцуул.</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -7310,17 +7310,17 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Хуваариудыг ижил болго: x(x + 1).</t>
+          <t>Рационал бутархайг нэмэхдээ ерөнхий хуваарьт шилжүүлнэ: $\frac{a}{b} + \frac{c}{d} = \frac{ad + bc}{bd}$ ($b, d \ne 0$). Хуваариуд ерөнхий үржигдэхүүнгүй бол ерөнхий хуваарь нь тэдгээрийн үржвэр.</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>(x + 1)/(x(x+1)) + x/(x(x+1)).</t>
+          <t>Ерөнхий хуваарийг $x(x+1)$ гэж ав. Бутархай бүрийн хүртвэрийг дутуу үржигдэхүүнээр үржүүлж өргөтгөөд, хүртвэрүүдийг нэмж төсөөтэй гишүүдийг нэгтгэ.</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэрийг нэм.</t>
+          <t>Хүртвэрийг хүртвэртэй, хуваарийг хуваарьтай нэмэх нь алдаа. Тодорхойлогдох муж: $x \ne 0$, $x \ne -1$; $x = 1$ орлуулж $\frac{1}{1} + \frac{1}{2}$-тэй харьцуулан хариугаа шалга.</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -7390,17 +7390,17 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>(a + b)³ = a³ + 3a²b + 3ab² + b³.</t>
+          <t>Нийлбэрийн куб: $(a+b)^3 = a^3 + 3a^2 b + 3ab^2 + b^3$. Коэффициентууд 1, 3, 3, 1 бөгөөд $a$-ийн зэрэг буурч, $b$-ийн зэрэг өснө.</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>a = x, b = 2.</t>
+          <t>$a = x$, $b = 2$ гэж тааруулаад дөрвөн гишүүн бүрт орлуул. Гишүүн бүрийн тоон хэсгийг ($3$, $b$, $b^2$, $b^3$-ын утгыг ашиглан) тусад нь үржүүлж коэффициентыг ол.</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>x³ + 3·x²·2 + 3·x·4 + 8.</t>
+          <t>$(a+b)^3 \ne a^3 + b^3$ — хоёр дунд гишүүнийг мартах нь түгээмэл алдаа. $x = 1$ орлуулж шалга: $(1+2)^3$-ийн утга таны олон гишүүнтийн коэффициентуудын нийлбэртэй тэнцэх ёстой.</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7470,17 +7470,17 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>x² − 6x нь (x − 3)²-ийн эхлэл: (x − 3)² = x² − 6x + 9.</t>
+          <t>Бүтэн квадрат ялгах: $x^2 + px = \left(x + \frac{p}{2}\right)^2 - \left(\frac{p}{2}\right)^2$. Ингэж $x^2 + px + q$ гурван гишүүнтийг $(x - a)^2 + b$ хэлбэрт бичдэг.</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>x² − 6x + 13 = (x − 3)² − 9 + 13.</t>
+          <t>$x$-ийн коэффициентын хагасыг ашиглаж $a$-г ол, дараа нь $(x - a)^2$-ийг задалж ямар сул гишүүн гарахыг тодорхойл. Анхны сул гишүүн 13-тай тэнцүүлэхэд нөхөх ёстой тоо нь $b$.</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>b = 13 − 9.</t>
+          <t>$b$-г шууд 13 гэж авах нь алдаа — $(x-a)^2$ задлахад өөрөө сул гишүүн өгдөг тул түүнийг харгалзах ёстой. Шалгахдаа $(x - a)^2 + b$-г задалж анхны илэрхийлэлтэй харьцуул.</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -7550,17 +7550,17 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>−3-ыг баруун тал руу шилжүүл.</t>
+          <t>Тэгшитгэлийн хоёр талд ижил тоо нэмэхэд шийд өөрчлөгдөхгүй, тиймээс гишүүнийг эсрэг тэмдэгтэйгээр нөгөө тал руу шилжүүлж болно. Дараа нь $ax = b$ ($a \ne 0$) хэлбэрээс $x = \frac{b}{a}$ гарна.</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>5x = 15.</t>
+          <t>$-3$-ыг баруун тал руу шилжүүлж, зүүн талд зөвхөн $5x$-ийг үлдээ. Баруун талын тоонуудыг нэгтгээд хоёр талыг $5$-д хуваа.</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 5-д хуваа.</t>
+          <t>$-3$ шилжихдээ $+3$ болно — $12$-оос хасвал буруу. Олсон утгаа $5x - 3$-д орлуулж, $12$ гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7630,17 +7630,17 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>x-ийг 4-т хуваасан байна — эсрэг үйлдэл нь юу вэ?</t>
+          <t>Тэгшитгэлийн хоёр талыг тэгээс ялгаатай ижил тоогоор үржүүлэхэд шийд хадгалагдана. Хуваах ба үржүүлэх нь харилцан урвуу үйлдэл тул $\frac{x}{a} = b$ бол $x = ab$ ($a \ne 0$).</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 4-өөр үржүүл.</t>
+          <t>$x$ нь $4$-т хуваагдсан байгаа тул урвуу үйлдлээр — хоёр талыг $4$-өөр үржүүлж хуваарийг арилга.</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>x = 6·4.</t>
+          <t>Хоёр талыг $4$-т хуваах нь алдаа — энэ нь урвуу биш, ижил үйлдэл. Хариугаа $4$-т хувааж, $6$ гарч байгаа эсэхээр шалга.</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -7710,17 +7710,17 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>7-г шилжүүл: −2x = 1 − 7.</t>
+          <t>Тэгшитгэлийн хоёр талыг тэгээс ялгаатай ижил тоонд (сөрөг тоонд ч) хуваахад шийд өөрчлөгдөхгүй. Ижил тэмдэгтэй хоёр тооны ноогдвор эерэг, эсрэг тэмдэгтэйнх сөрөг байна.</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>−2x = −6.</t>
+          <t>$7$-г баруун тал руу эсрэг тэмдэгтэйгээр шилжүүлж, $-2x$-ийг ганцаар нь үлдээ. Дараа нь хоёр талыг $x$-ийн коэффициент $-2$-т хуваа.</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг −2-т хуваа.</t>
+          <t>Сөрөг тоог сөрөг тоонд хуваахад эерэг гарна — энд тэмдэг алдах нь түгээмэл алдаа. Олсон утгаа $7 - 2x$-д орлуулж $1$ гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7790,17 +7790,17 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Хаалтыг задал эсвэл хоёр талыг 3-т хуваа.</t>
+          <t>Үржүүлэх үйлдэл нэмэх, хасах үйлдэлд хуваарилах чанартай: $a(b - c) = ab - ac$. Мөн хоёр талыг тэгээс ялгаатай ижил тоонд хуваахад шийд өөрчлөгдөхгүй.</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>x − 2 = 3.</t>
+          <t>Хоёр арга бий: хоёр талыг $3$-т хувааж хаалтыг шууд чөлөөл, эсвэл хаалтыг задлаад тоонуудыг баруун тал руу шилжүүл. Аль нэгээр нь $x$-ийг ганцааранг нь үлдээ.</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>x = 3 + 2.</t>
+          <t>Хаалт задлахдаа $3$-аар хоёр гишүүнийг хоёуланг нь үржүүл: $3(x-2) \ne 3x - 2$. Олсон утгаа анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -7870,17 +7870,17 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Хаалтыг задал: 2x + 6.</t>
+          <t>Хуваарилах чанар $a(b + c) = ab + ac$-ээр хаалтыг задалсны дараа тэгшитгэл $ax = b$ хэлбэрт шилжинэ. Гишүүнийг тэнцүүгийн нөгөө тал руу шилжүүлэхэд тэмдэг нь эсрэгээр солигдоно.</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>x-тэй гишүүдийг нэг талд: 6 + 6 = 5x − 2x.</t>
+          <t>Зүүн талын хаалтыг задал. $x$-тэй гишүүдийг коэффициент нь эерэг гарахаар нэг тал руу, тоонуудыг нөгөө тал руу цуглуулаад нэгтгэ.</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>12 = 3x.</t>
+          <t>$2$-оор хаалтын доторх хоёр гишүүнийг хоёуланг нь үржүүл — $3$-ыг үржүүлэхгүй орхих нь түгээмэл алдаа. Олсон утгаа хоёр талд орлуулж, тэнцүү утга гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7950,17 +7950,17 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 6-аар (ерөнхий хуваарь) үржүүл.</t>
+          <t>Бутархайтай тэгшитгэлийн хоёр талыг бүх хуваарийн хамгийн бага ерөнхий хуваалтаар үржүүлбэл бутархайгүй тэнцүү чанартай тэгшитгэл гарна. Бутархай нэмэхдээ хуваарийг нэмэхгүй: $\frac{x}{a} + \frac{x}{b} = \frac{bx + ax}{ab}$.</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>3x + 2x = 30.</t>
+          <t>$2$ ба $3$-ын ерөнхий хуваарийг олж, тэгшитгэлийн бүх гишүүнийг (баруун талын $5$-ыг ч) түүгээр үржүүл. Гарсан $x$-тэй гишүүдийг нэгтгээд $x$-ийг ол.</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>5x = 30.</t>
+          <t>$\frac{x}{2} + \frac{x}{3} \ne \frac{x}{5}$ — хуваарь нэмэгддэггүй. Баруун талыг үржүүлэхээ бүү март, хариугаа хоёр бутархайд орлуулж нийлбэр нь $5$ болж байгааг шалга.</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -8030,17 +8030,17 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Пропорцын гол чанар: хөндлөн үржвэрүүд тэнцүү.</t>
+          <t>Пропорцын үндсэн чанар: $\frac{a}{b} = \frac{c}{d}$ ($b, d \ne 0$) бол хөндлөн үржвэрүүд тэнцүү, $ad = bc$. Үл мэдэгдэгч хуваарьт байх тул $x \ne 0$ нөхцөл тавигдана.</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>3·12 = 9·x.</t>
+          <t>Хөндлөн үржүүлж $x$-тэй гишүүнийг нэг талд, тоон үржвэрийг нөгөө талд бич. Дараа нь $x$-ийн коэффициентод хуваа, эсвэл эхлээд $\frac{9}{12}$-ыг хураагаад харьцуул.</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>36 = 9x.</t>
+          <t>Пропорцод нэмэх, хасах үйлдлээр бус, зөвхөн үржүүлэх, хуваахаар ажилла. Олсон утгаа $\frac{3}{x}$-д орлуулж, $\frac{9}{12}$-тай тэнцүү бутархай гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -8110,17 +8110,17 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Хамгийн бага тоог x гэвэл бусад нь x + 1, x + 2.</t>
+          <t>Дараалсан натурал тоонууд бие биенээсээ $1$-ээр ялгаатай тул хамгийн багыг нь $n$ гэвэл $n,\ n+1,\ n+2$ гэж бичнэ. Нөхцөлийг нэг үл мэдэгдэгчтэй шугаман тэгшитгэл болгоно.</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>3x + 3 = 48.</t>
+          <t>Хамгийн бага тоог $x$ гэж аваад гурван тоог $x$-ээр илэрхийл. Тэдгээрийн нийлбэрийг $48$-тай тэнцүүлж, ижил төстэй гишүүдийг нэгтгээд бод.</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3x = 45.</t>
+          <t>$48$-ыг $3$-т хуваахад гарах тоо нь дунд тоо, хамгийн бага нь биш. Олсон гурван тоогоо нэмж $48$ гарч байгааг, мөн натурал тоо эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -8190,17 +8190,17 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Хоёр тэгшитгэлийг гишүүнчлэн нэмбэл y арилна.</t>
+          <t>Нэмэх арга: системийн нэг хувьсагчийн коэффициентууд эсрэг тоо бол тэгшитгэлүүдийг гишүүнчлэн нэмэхэд тэр хувьсагч устаж, нэг хувьсагчтай тэгшитгэл үлдэнэ. Системийн шийд нь хоёр тэгшитгэлийг зэрэг хангах $(x; y)$ хос.</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>2x = 8.</t>
+          <t>$y$-ийн коэффициентууд $1$ ба $-1$ тул хоёр тэгшитгэлийг нэмж $y$-ийг устга. $x$-ийг олсны дараа түүнийг аль нэг тэгшитгэлд орлуулж $y$-ийг ол.</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>x = 4-ийг аль нэгэнд орлуулж y-ийг ол.</t>
+          <t>Хариу нь хоёр тоо — $y$-ийг олохоо бүү март. Олсон хосоо хоёр тэгшитгэлд хоёуланд нь орлуулж шалга.</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -8270,17 +8270,17 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>y-ийн коэффициентууд эсрэг тэмдэгтэй — нэмж болно.</t>
+          <t>Тэгшитгэлүүдийг гишүүнчлэн нэмэхэд зүүн талууд нэмэгдэж, баруун талууд нэмэгдэнэ: $A = B,\ C = D \Rightarrow A + C = B + D$. Нэг хувьсагчийн коэффициентууд эсрэг тоо бол тэр хувьсагч устана.</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>3x = 9.</t>
+          <t>$y$-ийн коэффициентууд $1$ ба $-1$ тул хоёр тэгшитгэлийг нэмж нэг хувьсагчтай тэгшитгэл гарга. $x$-ийг олоод хоёр дахь тэгшитгэлд орлуулж $y$-ийг ол.</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>x = 3 → y = x − 1.</t>
+          <t>Нэмэхдээ гишүүн бүрийг тэмдэгтэй нь нэм: $y + (-y) = 0$, баруун талууд ч нэмэгдэнэ. Олсон хосоо хоёр тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -8350,17 +8350,17 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>x = 2y-г эхний тэгшитгэлд орлуул.</t>
+          <t>Орлуулах арга: нэг тэгшитгэлээс нэг хувьсагчийг нөгөөгөөр нь илэрхийлээд, нөгөө тэгшитгэлд орлуулбал нэг хувьсагчтай тэгшитгэл гарна. Энд хоёр дахь тэгшитгэл $x$-ийг аль хэдийн $y$-ээр илэрхийлсэн байна.</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>3·2y + 2y = 12.</t>
+          <t>Эхний тэгшитгэлийн $x$-ийн оронд $2y$-ийг хаалттай нь орлуул. Гарсан тэгшитгэлээс $y$-ийг олоод, $x = 2y$-ээр $x$-ийг тооцоол.</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>8y = 12.</t>
+          <t>$x = 2y$ гэдэг нь $x$ нь $y$-ээс $2$ дахин их гэсэн утгатай — $2x = y$ гэж андуурч болохгүй. $y$ бутархай гарч болно, хоёр утгаа хоёр тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -8430,17 +8430,17 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Бага тоог x гэвэл их нь x + 8.</t>
+          <t>Хоёр тооны ялгавар өгөгдсөн бол бага тоог $x$ гэж аваад их тоог $x + d$ гэж илэрхийлнэ ($d$ — ялгавар). Нийлбэрийн нөхцөл нэг үл мэдэгдэгчтэй шугаман тэгшитгэл болно.</t>
         </is>
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>2x + 8 = 30.</t>
+          <t>Бага тоог $x$ гэвэл их нь $x + 8$. Хоёр тооны нийлбэрийг $30$-тай тэнцүүлж, ижил төстэй гишүүдийг нэгтгээд $x$-ийг ол.</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>2x = 22.</t>
+          <t>$30$-ыг тэнцүү хоёр хуваах нь ялгаврын нөхцөлийг үл тоосон хэрэг. Олсон хоёр тоогоо нэмж $30$, хасаж $8$ гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -8510,17 +8510,17 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Зам = хурд · хугацаа.</t>
+          <t>Жигд хөдөлгөөний томьёо: $s = v \cdot t$ (зам = хурд $\times$ хугацаа). Хэд хэдэн хэсгээс тогтсон замын нийт урт нь хэсэг бүрийн замуудын нийлбэр.</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>Эхний хэсгийн зам 120 км. Үлдсэн зам 280 − 120.</t>
+          <t>Эхний хэсгийн замыг $60$ км/ц ба $2$ цагаар илэрхийл, хоёр дахь хэсгийг $80t$ гэж бич. Хоёр замын нийлбэрийг $280$-тай тэнцүүлж $t$-г ол.</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>160 = 80t.</t>
+          <t>Нийт замыг шууд $80$-д хуваавал эхний хэсгийг давхар тооцно — эхлээд түүнийг хас. Хариугаа хоёр хэсгийн замыг нэмж $280$ км гарч байгаагаар шалга.</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8590,17 +8590,17 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 2-оор үржүүлж аравтын бутархайгаас сал.</t>
+          <t>Тэгшитгэлийн хоёр талыг тэгээс ялгаатай ижил тоогоор үржүүлэхэд шийд өөрчлөгдөхгүй. Аравтын бутархайтай бол $10^k$ эсвэл тохирох тоогоор үржүүлж бүхэл коэффициенттэй болгоход тооцоо хялбарчилна.</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>x + 3 = 4x − 6.</t>
+          <t>Хоёр талын бүх гишүүнийг $2$-оор үржүүлж бүхэл коэффициенттэй тэгшитгэл гарга. Дараа нь $x$-тэй гишүүдийг нэг тал руу, тоонуудыг нөгөө тал руу шилжүүлж нэгтгэ.</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>9 = 3x.</t>
+          <t>Зөвхөн нэг талыг үржүүлбэл тэнцэтгэл алдагдана — бүх гишүүнийг үржүүл. Олсон утгаа анхны аравтын бутархайтай тэгшитгэлд орлуулж хоёр тал тэнцүү эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Квадрат нь 49 болох тоо хэд вэ? Хоёр байгаа.</t>
+          <t>$x^2 = a$ тэгшитгэл $a &gt; 0$ бол $x = \pm\sqrt{a}$ гэсэн хоёр язгууртай, $a = 0$ бол нэг, $a &lt; 0$ бол бодит язгуургүй. Учир нь эерэг ба сөрөг тоонуудын квадрат хоёулаа эерэг.</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>7² = 49, (−7)² = 49.</t>
+          <t>Баруун тал эерэг тул хоёр язгуур гарна. Квадрат нь баруун талын тоотой тэнцүү байх эерэг тоог олоод, түүний эсрэг тоог мөн бич.</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Хоёуланг нь бич.</t>
+          <t>$\sqrt{a}$ тэмдэглэгээ нь зөвхөн сөрөг биш язгуурыг заадаг ч тэгшитгэл хоёр шийдтэй — сөрөгийг бүү мартаарай. Хоёуланг нь квадрат зэрэгт дэвшүүлж шалга.</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8750,17 +8750,17 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 3-т хуваа.</t>
+          <t>Тэгшитгэлийн хоёр талыг тэгээс ялгаатай ижил тоонд хуваахад шийд өөрчлөгдөхгүй. $x^2 = a$ ($a &gt; 0$) бол $x = \pm\sqrt{a}$.</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>x² = 9.</t>
+          <t>Хоёр талыг $x^2$-ийн коэффициентод хувааж, чөлөөт гишүүнийг шилжүүлээд $x^2 = a$ хэлбэрт оруул. Дараа нь хоёр язгуурыг ол.</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>x = ±3.</t>
+          <t>Коэффициентод хуваахаас өмнө язгуур авбал буруу тоо гарна. Мөн сөрөг язгуурыг бүү мартаарай, хоёуланг нь анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>x-ийг хаалтын өмнө гарга.</t>
+          <t>Үржвэр тэгтэй тэнцүү байх нөхцөл: $A \cdot B = 0 \iff A = 0$ эсвэл $B = 0$. $ax^2 + bx = 0$ хэлбэрийн тэгшитгэлд ерөнхий $x$-ийг хаалтын өмнө гаргаж хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>x(x + 4) = 0.</t>
+          <t>$x$-ийг хаалтын өмнө гаргаж зүүн талыг хоёр үржигдэхүүний үржвэр болго. Үржигдэхүүн бүрийг тэгтэй тэнцүүлж хоёр язгуурыг ол.</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр 0 бол аль нэг үржигдэхүүн 0.</t>
+          <t>$x$-т хуваах нь $x = 0$ язгуурыг алдагдуулна — $x$ тэг байж болох тул хуваахгүй. Хоёр язгуураа тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8910,17 +8910,17 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр нь 6, нийлбэр нь 5 болох хоёр тоо.</t>
+          <t>Виетийн теорем: $x^2 + px + q = 0$ тэгшитгэлийн язгуурууд $x_1 + x_2 = -p$, $x_1 x_2 = q$ нөхцөлийг хангана. Иймээс $x^2 + px + q = (x - x_1)(x - x_2)$ гэж задарна.</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>2 ба 3.</t>
+          <t>Энд $p = -5$, $q = 6$ тул нийлбэр нь $5$, үржвэр нь $6$ болох хоёр тоог хай. $6$-г бүхэл үржигдэхүүнүүдэд задлах хувилбаруудыг шалга.</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Тэмдгийг шалга: x² − (2+3)x + 2·3.</t>
+          <t>Нийлбэр $-p$ гэдгийг анхаар: $p$ сөрөг тул язгуурууд эерэг, тэмдгийг бүү эргүүл. Олсон тоонуудаар $(x - x_1)(x - x_2)$-ийг задалж анхны тэгшитгэл гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -8990,17 +8990,17 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр нь −15, нийлбэр нь −2 болох хоёр тоо.</t>
+          <t>Виетийн теорем: $x^2 + px + q = 0$-ийн язгуурууд $x_1 + x_2 = -p$, $x_1 x_2 = q$. $q &lt; 0$ бол язгуурууд эсрэг тэмдэгтэй, $q &gt; 0$ бол ижил тэмдэгтэй.</t>
         </is>
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>−5 ба 3.</t>
+          <t>Энд $p = 2$, $q = -15$ тул язгууруудын нийлбэр $-2$, үржвэр $-15$. Үржвэр сөрөг тул нэг язгуур эерэг, нөгөө нь сөрөг — модулиар их нь аль тэмдэгтэйг нийлбэрээр тодорхойл.</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>(x + 5)(x − 3) = 0.</t>
+          <t>Нийлбэр $-p$ тул тэмдгийг солиход хоёр язгуур хоёулаа буруу гарна. Олсон тоонуудаа $x^2 + 2x - 15$-д орлуулж тэг гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -9070,17 +9070,17 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>D = b² − 4ac-ийг тооцоол.</t>
+          <t>$D = b^2 - 4ac = 0$ бол квадрат тэгшитгэл нэг давхар язгууртай: $x_0 = -\frac{b}{2a}$. Энэ үед зүүн тал бүтэн квадрат болно: $a^2 - 2ab + b^2 = (a - b)^2$.</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>D = 36 − 36 = 0 → ганц (давхар) язгуур.</t>
+          <t>$D$-г тооцоолж тэгтэй тэнцүү эсэхийг шалга. Тэг бол $-\frac{b}{2a}$ томьёо хэрэглэ, эсвэл зүүн талыг бүтэн квадратын томьёогоор задал.</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>x = −b/(2a) = 6/2.</t>
+          <t>$D = 0$ нь шийдгүй гэсэн үг биш — нэг (давхар) язгуур бий; $D &lt; 0$ үед л бодит язгуургүй. $b$-ийн тэмдгийг анхаарч, язгуураа орлуулж шалга.</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -9150,17 +9150,17 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>D = 25 − 16 = 9.</t>
+          <t>$ax^2 + bx + c = 0$ ($a \ne 0$)-ийн язгуурууд $x_{1,2} = \frac{-b \pm \sqrt{D}}{2a}$, $D = b^2 - 4ac$. $D &gt; 0$ бол хоёр ялгаатай бодит язгууртай.</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>x = (5 ± 3)/4.</t>
+          <t>$a$, $b$, $c$-г тэмдэгтэй нь ялгаад $D$-г ол. $-b$ ба $\sqrt{D}$-г томьёонд орлуулж, $+$ ба $-$ тохиолдлуудыг тус бүр хялбарчил.</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>x₁ = 8/4, x₂ = 2/4.</t>
+          <t>Хуваарь нь $2a$, энд $a = 2$ — зөвхөн $2$-т хуваах нь алдаа. $b$ сөрөг тул $-b$ эерэг, хариугаа язгууруудын үржвэр $\frac{c}{a}$-тай тэнцүү эсэхээр шалга.</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -9230,17 +9230,17 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>D = b² − 4ac.</t>
+          <t>$ax^2 + bx + c = 0$-ийн бодит язгуурын тоог дискриминант $D = b^2 - 4ac$-ийн тэмдэг тодорхойлно: $D &gt; 0$ — хоёр, $D = 0$ — нэг, $D &lt; 0$ — бодит язгуургүй.</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>D = 9 − 20 = −11 &lt; 0.</t>
+          <t>$a$, $b$, $c$-г ялгаж $D$-г тооцоол. Тэгшитгэлийг бодох шаардлагагүй — зөвхөн $D$-ийн тэмдгийг тодорхойлоход хангалттай.</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>D сөрөг бол бодит шийдгүй.</t>
+          <t>$D &lt; 0$ бол томьёонд орлуулж сөрөг тооноос квадрат язгуур авах боломжгүй. $b^2$ ба $4ac$-г зөв тооцоолсон эсэхээ давхар шалга.</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -9310,17 +9310,17 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Өргөнийг x гэвэл урт x + 3.</t>
+          <t>Тэгш өнцөгтийн талбай $S = a \cdot b$ (урт $\times$ өргөн). Нэг талыг $x$ гэвэл нөгөөг $x$-ээр илэрхийлж, талбайн нөхцөлөөс квадрат тэгшитгэл гарна.</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>x² + 3x − 40 = 0.</t>
+          <t>Өргөнийг $x$, уртыг $x + 3$ гэж аваад үржвэрийг $40$-тэй тэнцүүл. Хаалтыг задалж $ax^2 + bx + c = 0$ хэлбэрт оруулаад Виет эсвэл $D$-ээр бод.</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр −40, нийлбэр 3: 8 ба −5. Урт сөрөг байж болохгүй.</t>
+          <t>Квадрат тэгшитгэл сөрөг язгууртай гарч болох ч талын урт эерэг байх ёстой — зохисгүй язгуурыг хая. Олсон өргөн ба уртын үржвэр $40$ эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
@@ -9390,17 +9390,17 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>D = 16 − 4 = 12.</t>
+          <t>Язгуурын томьёо: $x_{1,2} = \frac{-b \pm \sqrt{D}}{2a}$, $D = b^2 - 4ac$. $D$ бүтэн квадрат биш бол язгуурууд иррационал бөгөөд $\sqrt{m^2 k} = m\sqrt{k}$-ээр хялбарчилна.</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>√12 = 2√3.</t>
+          <t>$D$-г олоод $\sqrt{D}$-г хялбарчил. Томьёонд орлуулсны дараа хүртвэрийн гишүүн бүр ба хуваарийн ерөнхий үржигдэхүүнээр бутархайг хураа.</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>x = (−4 ± 2√3)/2 — 2-т хураа.</t>
+          <t>Бутархайг хураахдаа хүртвэрийн хоёр гишүүнийг хоёуланг нь хуваа — зөвхөн нэгийг нь хуваах нь түгээмэл алдаа. Язгууруудын нийлбэр $-\frac{b}{a}$, үржвэр $\frac{c}{a}$-тай тохирч байгааг шалга.</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -9470,17 +9470,17 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Язгуурыг тэгшитгэлд орлуулбал тэнцэтгэл биелнэ.</t>
+          <t>Тоо тэгшитгэлийн язгуур байна гэдэг нь түүнийг орлуулахад үнэн тоон тэнцэтгэл гарна гэсэн үг. Иймээс өгсөн язгуурыг орлуулбал параметрийн хувьд шугаман тэгшитгэл гарна.</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>4 − 16 + c = 0.</t>
+          <t>Тэгшитгэлийн $x$-ийн оронд өгсөн язгуурыг орлуулж, тоон гишүүдийг нэгтгэ. Гарсан тэгшитгэлээс $c$-г илэрхийл, эсвэл Виетээр хоёр дахь язгуурыг олоод үржвэрийг ашигла.</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>c = 12.</t>
+          <t>$c$-г шилжүүлэхдээ тэмдгийг анхаар — тэмдэг алдах нь түгээмэл. Олсон $c$-ээ тавиад $x = 2$ үнэхээр язгуур эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Виет: x₁ + x₂ = 7, x₁x₂ = 10.</t>
+          <t>Виетийн теорем: $x_1 + x_2 = -p$, $x_1 x_2 = q$ ($x^2 + px + q = 0$). Тэгш хэмт илэрхийллийг эдгээрээр илэрхийлнэ: $x_1^2 + x_2^2 = (x_1 + x_2)^2 - 2x_1 x_2$.</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>x₁² + x₂² = (x₁ + x₂)² − 2x₁x₂.</t>
+          <t>Тэгшитгэлээс $p$, $q$-г ялгаж язгууруудын нийлбэр ба үржвэрийг ол. Тэдгээрийг адилтгалд орлуулж тооцоол — язгууруудыг тусад нь олох шаардлагагүй.</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>49 − 20.</t>
+          <t>$(x_1 + x_2)^2 \ne x_1^2 + x_2^2$ — $2x_1 x_2$-ийг хасахаа бүү март. Шалгахдаа язгууруудыг нь олоод квадратуудыг шууд нэмж харьцуул.</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -9630,17 +9630,17 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>t = x² гэж орлуул.</t>
+          <t>Биквадрат тэгшитгэл $ax^4 + bx^2 + c = 0$-ийг $t = x^2$ ($t \ge 0$) орлуулгаар $at^2 + bt + c = 0$ квадрат тэгшитгэл болгоно. $t$-ийн сөрөг биш язгуур бүрээс $x = \pm\sqrt{t}$ гарна.</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>t² − 5t + 4 = 0 → t = 1, t = 4.</t>
+          <t>$t = x^2$ гэж орлуулаад $t$-ийн квадрат тэгшитгэлийг Виет эсвэл $D$-ээр бод. Дараа нь $t$-ийн утга бүрээр $x^2 = t$ тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>x² = 1, x² = 4 — тус бүр 2 шийдтэй.</t>
+          <t>$t$-ийн утгууд эцсийн хариу биш — буцаан $x$-рүү шилжих ёстой, эерэг $t$ бүр хоёр язгуур өгнө. Сөрөг $t$ гарвал бодит язгуургүй тул хая, язгуур бүрээ орлуулж шалга.</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9710,17 +9710,17 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Бага тоог x гэвэл их нь x + 1.</t>
+          <t>Дараалсан натурал тоонууд $1$-ээр ялгаатай: бага нь $n$ бол дараагийнх $n + 1$. Үржвэрийн нөхцөл $n(n+1) = m$ нь квадрат тэгшитгэл болно.</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>x² + x − 72 = 0.</t>
+          <t>Бага тоог $x$ гэж аваад үржвэрийг $72$-той тэнцүүл. $x^2 + bx + c = 0$ хэлбэрт оруулж Виет эсвэл $D$-ээр язгууруудыг ол.</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр −72, нийлбэр 1: 9 ба −8.</t>
+          <t>Квадрат тэгшитгэлийн хоёр язгуурын нэг нь сөрөг — натурал тоо биш тул хая. Олсон тоо ба дараагийн тооны үржвэр $72$ эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -9790,17 +9790,17 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Тэгшитгэл шиг 4-ийг шилжүүл.</t>
+          <t>Тэнцэтгэл бишийн хоёр талаас ижил тоо хасахад тэмдэг өөрчлөгдөхгүй: $a &lt; b \Rightarrow a - c &lt; b - c$. Иймээс гишүүнийг нөгөө тал руу эсрэг тэмдэгтэй шилжүүлж болно.</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>x &lt; 9 − 4.</t>
+          <t>Зүүн талын $+4$-ийг баруун тал руу $-4$ болгон шилжүүлж $x$-ийг ганцааршуул. Тэмдгийг хэвээр нь хадгал.</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Хатуу тэмдэг (&lt;) хэвээр үлдэнэ.</t>
+          <t>Анхны тэмдэг хатуу ($&lt;$) тул хариунд $\le$ бичиж болохгүй. Шалгахдаа хилийн утгыг орлуулахад тэнцэтгэл биш биелэхгүй байх ёстой.</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9870,17 +9870,17 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг 3-т хуваа.</t>
+          <t>Хоёр талыг эерэг тоо $c &gt; 0$-д хуваахад тэнцэтгэл бишийн тэмдэг хэвээр: $a \ge b \Rightarrow \frac{a}{c} \ge \frac{b}{c}$. $x$-ийг ганцааршуулахын тулд коэффициентод нь хуваана.</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>3 эерэг тул тэмдэг өөрчлөгдөхгүй.</t>
+          <t>$x$-ийн коэффициент $3$ эерэг тул хоёр талыг $3$-т хуваа. Тэмдэг $\ge$ хэвээр үлдэнэ.</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>x ≥ 4.</t>
+          <t>$3x$ гэдэг нь үржвэр тул $3$-ыг хасах биш, хуваах ёстой. $\ge$ тэмдэг тул хилийн утга хариунд орно; түүнийг орлуулж тэнцэх эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -9950,17 +9950,17 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Хоёр талыг −2-т хуваана.</t>
+          <t>Хоёр талыг сөрөг тоо $c &lt; 0$-д хуваахад тэмдэг эсрэгээр эргэнэ: $a &gt; b \Rightarrow \frac{a}{c} &lt; \frac{b}{c}$. Жишээ нь $2 &gt; 1$ боловч $-2 &lt; -1$.</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>Сөрөг тоонд хуваахад тэмдэг эргэнэ.</t>
+          <t>$x$-ийн коэффициент $-2$ тул хоёр талыг $-2$-т хувааж, $&gt;$ тэмдгийг эсрэг тэмдгээр соль.</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>x &lt; −4.</t>
+          <t>Тэмдгийг эргүүлэхгүй орхих нь хамгийн түгээмэл алдаа. Шалгахдаа хариуны завсраас нэг утга (жишээ нь $-10$) аваад $-2x &gt; 8$-д орлуулж үнэн эсэхийг хар.</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -10030,17 +10030,17 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>5-ыг шилжүүл: −x ≤ −3.</t>
+          <t>Гишүүнийг нөгөө тал руу шилжүүлэхэд тэмдэг нь өөрчлөгдөнө, харин $-1$-ээр үржүүлэх (хуваах) үед тэнцэтгэл бишийн тэмдэг эргэнэ: $-x \le -a \iff x \ge a$.</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>−1-ээр үржүүлэхэд тэмдэг эргэнэ.</t>
+          <t>$5$-ыг баруун тал руу шилжүүлж $-x \le \dots$ хэлбэрт оруул. Дараа нь хоёр талыг $-1$-ээр үржүүлж, тэмдгийг эргүүл.</t>
         </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>x ≥ 3.</t>
+          <t>$-x$-ээс $x$ руу шилжихдээ тэмдгийг эргүүлэхгүй бол буруу завсар гарна. $\le$ тэмдэг тул хилийн цэг орно; завсраас нэг тоо авч $5 - x \le 2$-т орлуулж шалга.</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Хаалтыг задал: 2x − 2.</t>
+          <t>Хаалт задлахдаа үржүүлэхийн нийлбэрт хамаарах хуулийг хэрэглэнэ: $a(b + c) = ab + ac$. Дараа нь шугаман тэнцэтгэл бишийг тэгшитгэлтэй адил, тэмдгийг анхааран бодно.</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>2x − x &gt; 3 + 2.</t>
+          <t>$2(x-1)$-ийн хаалтыг задал — $2$-ыг хаалт доторх гишүүн бүрээр үржүүл. $x$-тэй гишүүдийг зүүн, тоонуудыг баруун талд цуглуулж хялбарчил.</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>x &gt; 5.</t>
+          <t>$2$-ыг зөвхөн $x$-ээр үржүүлж, $-1$-ийг орхих нь түгээмэл алдаа. $x$-ийн коэффициент эерэг үлдэх тул тэмдэг эргэхгүй; хариуныхаа нэг утгыг анхны тэнцэтгэл бишид орлуулж шалга.</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -10190,17 +10190,17 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Гурван хэсгээс 3-ыг хас.</t>
+          <t>Давхар тэнцэтгэл биш $a \le t &lt; b$ нь хоёр нөхцлийг зэрэг илэрхийлнэ. Гурван хэсэгт ижил тоо нэмэх, эсвэл эерэг тоонд хуваахад бүх тэмдэг хэвээр үлдэнэ.</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>−4 ≤ 2x &lt; 4.</t>
+          <t>$x$-ийг дунд хэсэгт ганцааршуулахын тулд эхлээд гурван хэсгээс $3$-ыг хас. Дараа нь гурван хэсгийг $x$-ийн коэффициентод хуваа.</t>
         </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Гурван хэсгийг 2-т хуваа.</t>
+          <t>Үйлдлийг гурван хэсэгт зэрэг хийх ёстой — нэг хэсгийг орхивол хариу буруу болно. Зүүн тэмдэг $\le$, баруун тэмдэг $&lt;$ тул захын цэгүүдийн аль нь орохыг тус тусад нь анхаар.</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -10270,17 +10270,17 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>|x| ≤ a гэдэг нь x нь −a ба a-ийн хооронд.</t>
+          <t>$a \ge 0$ үед $|x| \le a \iff -a \le x \le a$. Модуль нь тэгээс хүртэлх зай тул энэ нь $0$-ээс $a$-аас хэтрэхгүй зайд орших бүх цэг юм.</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>−3 ≤ x ≤ 3.</t>
+          <t>Модулийн тодорхойлолтоор тэнцэтгэл бишийг давхар тэнцэтгэл биш болгон бич. Тоон шулуун дээр $0$-ээс хоёр тийш ижил зайд хил тавина.</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Хоёр захыг оруулна.</t>
+          <t>Зөвхөн $x \le 3$ гэж бичвэл $-100$ гэх мэт сөрөг тоонууд ч орох болно — гэтэл тэдний модуль их. $\le$ тул хоёр захын цэг хоёулаа хариунд орно.</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>|t| &gt; a бол t &lt; −a эсвэл t &gt; a.</t>
+          <t>$a &gt; 0$ үед $|t| &gt; a \iff t &lt; -a$ эсвэл $t &gt; a$. Зай нь $a$-аас их байх цэгүүд хоёр тийш тархсан тул хариу хоёр завсрын нэгдэл болно.</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>x + 1 &lt; −2 эсвэл x + 1 &gt; 2.</t>
+          <t>$t = x + 1$ гэж үзээд хоёр тусдаа шугаман тэнцэтгэл биш бич. Тус бүрийг бодоод үр дүнг \"эсвэл\"-ээр холбо.</t>
         </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Хоёр завсрын нэгдэл.</t>
+          <t>$|t| &gt; a$-г $-a &lt; t &lt; a$ гэж бичих нь буруу — тэр нь $|t| &lt; a$-ийн шийд. Шалгахдаа хоёр завсар тус бүрээс нэг утга, тэдгээрийн хоорондоос нэг утга авч орлуулаарай.</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -10430,17 +10430,17 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Хоёр нөхцөл зэрэг биелэх ёстой.</t>
+          <t>Тэнцэтгэл бишийн систем гэдэг нь бүх нөхцөл зэрэг биелэх ёстой гэсэн үг тул шийд нь завсруудын огтлолцол ($\cap$) байна. Нэгдэл ($\cup$) нь \"эсвэл\" холбоост тохирно.</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>Тоон шулуун дээр хоёр завсрыг зурж огтлолцлыг ол.</t>
+          <t>Хоёр нөхцлийг нэг тоон шулуун дээр зурж, зураасууд давхцаж буй хэсгийг ол. Захын цэг бүрийн хувьд тэмдэг хатуу эсэхийг тус тусад нь хар.</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>(1; 4].</t>
+          <t>Нэгдлийг авах нь түгээмэл алдаа — тэгвэл бүх бодит тоо гарна. Хатуу ($&gt;$) зах нь орохгүй (дугуй хоосон), сул ($\le$) зах нь орно (дугуй дүүрэн).</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
@@ -10510,17 +10510,17 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>x² − 9 = (x − 3)(x + 3).</t>
+          <t>Квадратуудын ялгавар $a^2 - b^2 = (a - b)(a + b)$. Дээш харсан парабол язгууруудынхаа хооронд сөрөг утгатай.</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>Язгуурууд −3, 3: тэмдгийн мужуудыг шалга.</t>
+          <t>$x^2 - 9$-ийг үржигдэхүүнд задалж язгууруудыг ол. Тоон шулууныг язгуураар хувааж, үржвэр сөрөг байх завсрыг сонго.</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>Парабол дээш харсан тул язгууруудын хооронд сөрөг.</t>
+          <t>$x^2 &lt; 9$-ийг $x &lt; 3$ гэж язгуур авах нь алдаа — тэгвэл $x = -10$ хариунд орох боловч $(-10)^2 = 100$. Хатуу тэмдэг тул язгуурууд орохгүй.</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
@@ -10590,17 +10590,17 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Язгууруудыг ол: x² + x − 6 = 0.</t>
+          <t>$a &gt; 0$, $D &gt; 0$ үед $ax^2 + bx + c \ge 0$ нь язгууруудын гадна талд (язгууруудыг оролцуулан) биелнэ. Квадрат гурван гишүүнтийг $a(x - x_1)(x - x_2)$ хэлбэрт задалж болно.</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>−3 ба 2.</t>
+          <t>$x^2 + x - 6 = 0$-ийн язгуурыг ол (үржвэр $-6$, нийлбэр $-1$ байх хоёр тоо). Тоон шулуунд тэмдэглээд илэрхийлэл сөрөг биш байх завсруудыг сонго.</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Дээш харсан парабол язгууруудын гадна эерэг.</t>
+          <t>Язгууруудын дотор талыг сонгох нь түгээмэл алдаа — тэнд дээш харсан парабол сөрөг. $\ge$ тул язгуурууд орно; хариу хоёр завсрын нэгдэл болохыг тэмдэглэ.</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10670,17 +10670,17 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Хүртвэр, хуваарь хоёулаа ижил тэмдэгтэй байх ёстой.</t>
+          <t>$\frac{P}{Q} &gt; 0 \iff P$ ба $Q$ ижил тэмдэгтэй. Интервалын арга: хүртвэр ба хуваарийн тэгүүдээр тоон шулууныг хувааж, завсар бүрт тэмдгийг тодорхойлно.</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>Чухал цэгүүд: x = 2 (хүртвэр), x = −1 (хуваарь, оруулахгүй).</t>
+          <t>Хүртвэр ба хуваарийг тус бүр тэгтэй тэнцүүлж чухал цэгүүдийг ол. Гарсан завсар бүрээс нэг тоо авч бутархайн тэмдгийг шалга.</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Мужуудад тэмдгийг шалга.</t>
+          <t>$x + 1$-ээр үржүүлж болохгүй — түүний тэмдэг тодорхойгүй тул тэмдэг эргэх эсэх мэдэгдэхгүй. Хуваарь тэг болох цэг хэзээ ч хариунд орохгүй.</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
@@ -10750,17 +10750,17 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Зардал = 1000 + 800·x ≤ 9000.</t>
+          <t>Үгэн бодлогыг тэнцэтгэл биш болгоно: \"хэтрэхгүй\" нь $\le$ тэмдэгт харгалзана. Нийт зардал = тогтмол хэсэг + нэгжийн үнэ $\times$ тоо хэмжээ.</t>
         </is>
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>800x ≤ 8000.</t>
+          <t>Өгөгдсөн $1000 + 800x \le 9000$-ээс суурь үнийг хасаад, хоёр талыг $800$-д хуваа. Гарсан хязгаараас хамгийн их зөвшөөрөгдөх утгыг сонго.</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>x ≤ 10.</t>
+          <t>Нийт мөнгийг шууд км-ийн үнэд хуваах нь алдаа — эхлээд суурь үнийг хас. Хариугаа шалгахдаа олсон км-ийг орлуулж нийт зардал хязгаараас хэтрэхгүй эсэхийг тооцоол.</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10830,17 +10830,17 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Квадрат хэзээ 0-ээс их вэ?</t>
+          <t>Ямар ч бодит $a$-д $a^2 \ge 0$ бөгөөд $a^2 = 0 \iff a = 0$. Иймд квадрат хатуу эерэг байх нь суурь нь тэг биш байхтай тэнцүү.</t>
         </is>
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>Квадрат нь зөвхөн x = 1 үед 0.</t>
+          <t>Квадратын суурийг тэгтэй тэнцүүлж, илэрхийлэл тэг болох ганц утгыг ол. Бусад бүх $x$-д илэрхийлэл ямар тэмдэгтэй болохыг дүгнэ.</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>Бусад бүх x-д эерэг.</t>
+          <t>Хоёр талаас язгуур гаргаж $x - 1 &gt; 0$ гэвэл $x - 1 &lt; 0$ байх утгууд алдагдана. Шалгахдаа $x = 0$ ба $x = 2$ хоёуланг нь орлуулж үзээрэй.</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -10910,17 +10910,17 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>x-ийн оронд −3-ыг хаалттай орлуул.</t>
+          <t>$f(a)$-г олохдоо $x$-ийн оронд $a$-г орлуулна; сөрөг тоог хаалтад авна. $(-a)^2 = a^2$, харин $-a^2 = -(a^2)$ — эдгээр нь өөр.</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>(−3)² = 9.</t>
+          <t>$f(x) = x^2 + 1$-д $x$-ийн оронд $(-3)$-ыг хаалттай нь тавь. Эхлээд зэрэг дэвшүүлж, дараа нь нэм.</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>9 + 1.</t>
+          <t>$(-3)^2$-ийг $-9$ гэж бодох нь алдаа — сөрөг тооны тэгш зэрэг эерэг. Шалгахдаа: $x^2 + 1 \ge 1$ тул функцийн утга $1$-ээс бага байж болохгүй.</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>f(x) = 1 гэдэг нь 5 − 2x = 1.</t>
+          <t>$f(x) = c$ байх $x$-ийг олох нь $f$-ийн томьёог $c$-тэй тэнцүүлсэн тэгшитгэлийг бодох урвуу бодлого. Энд аргумент үл мэдэгдэх, функцийн утга мэдэгдэж байна.</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>−2x = −4.</t>
+          <t>$5 - 2x = 1$ тэгшитгэл бич. $5$-ыг шилжүүлээд хоёр талыг $x$-ийн коэффициентод хуваа.</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>x = 2.</t>
+          <t>$x = 1$-ийг орлуулах нь алдаа — $1$ бол функцийн утга, аргумент биш. Олсон $x$-ээ $f$-д орлуулахад $1$ гарах ёстой.</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -11070,17 +11070,17 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Oy тэнхлэг дээр x = 0.</t>
+          <t>$Oy$ тэнхлэгийн бүх цэгийн абсцисс $x = 0$. $y = kx + b$ шулуунд $x = 0$ тавихад $Oy$-тэй огтлолцох цэгийн ордината нь чөлөөт гишүүн $b$ болдог.</t>
         </is>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>y = −3·0 + 4.</t>
+          <t>Шулууны тэгшитгэлд $x = 0$ орлуулж $y$-ийг тооцоол. Огтлолцлын цэгийг $(0; y)$ хэлбэрээр бич.</t>
         </is>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>y = 4.</t>
+          <t>Налалт $k$-г огтлолцлын цэг гэж андуурах нь түгээмэл. $k$ нь хазайлтыг, $b$ нь $Oy$ дээрх байрлалыг заадаг гэдгийг санаарай.</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -11150,17 +11150,17 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Ox тэнхлэг дээр y = 0.</t>
+          <t>$Ox$ тэнхлэгийн бүх цэгийн ордината $y = 0$. Иймд $Ox$-тэй огтлолцох цэг нь $f(x) = 0$ тэгшитгэлийн шийд — функцийн тэг юм.</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>2x − 6 = 0.</t>
+          <t>Шулууны тэгшитгэлд $y = 0$ тавьж шугаман тэгшитгэл гарга. Түүнийг бодож абсциссыг ол.</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>x = 3.</t>
+          <t>$x = 0$ орлуулбал $Oy$-тэй огтлолцох цэг гарна — энэ өөр асуулт. Олсон абсциссаа тэгшитгэлд орлуулахад $y = 0$ гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -11230,17 +11230,17 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>k = (y₂ − y₁)/(x₂ − x₁).</t>
+          <t>Хоёр цэгийг дайрсан шулууны өнцгийн коэффициент $k = \frac{y_2 - y_1}{x_2 - x_1}$ ($x_1 \ne x_2$). Энэ нь ординатын өөрчлөлтийг абсциссын өөрчлөлтөд харьцуулсан харьцаа.</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>(7 − 1)/(2 − 0).</t>
+          <t>Цэгүүдийн координатыг $x_1, y_1, x_2, y_2$ гэж тэмдэглээд томьёонд орлуул. Хүртвэр ба хуваарийг тооцоолж бутархайг хураа.</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>6/2.</t>
+          <t>$\frac{x_2 - x_1}{y_2 - y_1}$ гэж сольж бичих нь алдаа. Шалгах: $x$ $2$-оор өсөхөд $y$ хэдээр өссөн бэ — налалт нь нэгж алхам дахь өөрчлөлт.</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -11310,17 +11310,17 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Бутархайн хуваарь 0 байж болохгүй.</t>
+          <t>Бутархай $\frac{P(x)}{Q(x)}$ зөвхөн $Q(x) \ne 0$ үед тодорхойлогдоно, учир нь тэгд хуваах үйлдэл тодорхойлогдоогүй. Иймд хуваарийг тэг болгох утгууд мужаас хасагдана.</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>x − 4 = 0.</t>
+          <t>Хуваарийг тэгтэй тэнцүүлсэн тэгшитгэл бичиж шийдийг ол. Тэр утга мужид орохгүй.</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>x = 4 үед функц тодорхойлогдохгүй.</t>
+          <t>$x - 4 = 0$-ийг бодохдоо тэмдэг алдах нь түгээмэл. Олсон утгаа хуваарьт орлуулахад тэг гарч байгааг шалга.</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -11390,17 +11390,17 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Язгуур доорх илэрхийлэл сөрөг биш байх ёстой.</t>
+          <t>$\sqrt{u}$ зөвхөн $u \ge 0$ үед тодорхойлогдоно. Сөрөг коэффициентод хуваахад тэнцэтгэл бишийн тэмдэг эргэнэ.</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>6 − 2x ≥ 0.</t>
+          <t>Язгуур доорх илэрхийлэлд $6 - 2x \ge 0$ нөхцөл тавь. $6$-г шилжүүлээд хоёр талыг $-2$-т хуваа.</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>−2x ≥ −6 → тэмдэг эргэнэ.</t>
+          <t>$-2$-т хуваахдаа тэмдгийг эргүүлэхгүй бол буруу чиглэлийн завсар гарна. Шалгахдаа завсраас нэг тоо (жишээ нь $x = 0$) авч язгуур доорх утга сөрөг биш эсэхийг хар.</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -11470,17 +11470,17 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Ox дээр y = 0.</t>
+          <t>Параболын $Ox$ тэнхлэгтэй огтлолцох цэгүүдийн абсцисс нь $ax^2 + bx + c = 0$ тэгшитгэлийн бодит язгуурууд. $D &gt; 0$ бол хоёр, $D = 0$ бол нэг, $D &lt; 0$ бол огтлолцох цэггүй.</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>x² − 2x − 3 = 0.</t>
+          <t>$y = 0$ тавьж квадрат тэгшитгэл гарга. Виетийн теоремоор (үржвэр $= \frac{c}{a}$, нийлбэр $= -\frac{b}{a}$) эсвэл дискриминантаар язгууруудыг ол.</t>
         </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>Үржвэр −3, нийлбэр 2: 3 ба −1.</t>
+          <t>$x = 0$ орлуулбал $Oy$-тэй огтлолцох цэг олдоно — энэ өөр асуулт. Олсон язгуур бүрийг тэгшитгэлд орлуулж тэг гарахыг шалга.</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -11550,17 +11550,17 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Оройн абсцисс x₀ = −b/(2a).</t>
+          <t>$y = ax^2 + bx + c$ параболын оройн абсцисс $x_0 = -\frac{b}{2a}$. Парабол $x = x_0$ шулууны хувьд тэгш хэмтэй тул орой энэ тэнхлэг дээр оршино.</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>a = 1, b = −6.</t>
+          <t>$a$ ба $b$-г тэмдэгтэй нь бичиж ($b$ нь $x$-ийн өмнөх коэффициент) томьёонд орлуул. Хасах тэмдгүүдийг анхааран хялбарчил.</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>x₀ = 6/2.</t>
+          <t>$-\frac{b}{2a}$-ийн хасахыг орхивол тэмдэг буруу гарна. Шалгах: оройн абсцисс нь Виетийн теоремоор язгууруудын нийлбэрийн хагастай тэнцүү.</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -11630,17 +11630,17 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Шугаман функцийн өсөлт буурал нь k-гийн тэмдгээс хамаарна.</t>
+          <t>$y = kx + b$ шугаман функц $k &gt; 0$ үед өсөх, $k &lt; 0$ үед буурах, $k = 0$ үед тогтмол. Өсөлт, бууралтыг зөвхөн налалтын тэмдэг тодорхойлно.</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>k = −2 &lt; 0.</t>
+          <t>Функцээс $x$-ийн өмнөх коэффициент $k$-г ялгаж, түүний тэмдгийг тогтоо. Дараа нь онолын нөхцөлтэй харьцуулж кодоор бич.</t>
         </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>k сөрөг бол буурна.</t>
+          <t>Чөлөөт гишүүн $b$-ийн тэмдгээр дүгнэх нь алдаа — $b$ зөвхөн $Oy$-тэй огтлолцох цэгийг заана. Шалгахдаа $x = 0$ ба $x = 1$ үеийн утгыг харьцуул.</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -11710,17 +11710,17 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>a &lt; 0 тул парабол доош харсан — оройд хамгийн их утга.</t>
+          <t>$a &lt; 0$ үед $y = ax^2 + bx + c$ парабол доош харсан бөгөөд хамгийн их утгаа оройд $x_0 = -\frac{b}{2a}$ цэгт авна. Хамгийн их утга нь $y(x_0)$.</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>x₀ = −b/(2a) = −4/(−2) = 2.</t>
+          <t>$a$, $b$-г тэмдэгтэй нь тодорхойлж $x_0$-ийг ол. Дараа нь $x_0$-ийг функцид орлуулж утгыг тооцоол.</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>y(2) = −4 + 8 + 1.</t>
+          <t>$a = -1$ үед хуваарь $2a$ сөрөг болдгийг мартаж $x_0$-ийн тэмдгийг алдах нь түгээмэл. Шалгахдаа $x_0$-ийн хоёр талаас нэг нэг утга орлуулж, тэдгээр нь бага гарахыг хар.</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11790,17 +11790,17 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Дотоод функцийг эхлээд тооцно.</t>
+          <t>Найрлага $g(f(x))$-д эхлээд $f$, дараа нь $g$ хэрэглэгдэнэ; $f(g(x))$-д эсрэгээрээ. Найрлага ерөнхийдөө солих хуульгүй: $g(f(x)) \ne f(g(x))$.</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>f(4) = 3 → g(3) = 9; g(4) = 12 → f(12) = 11.</t>
+          <t>$f(4)$-ийг олоод $g$-д орлуул; тусад нь $g(4)$-ийг олоод $f$-д орлуул. Хоёр үр дүнгийн ялгаврыг дарааллаар нь ав.</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>9 − 11.</t>
+          <t>Хоёр найрлагыг ижил гэж үзвэл ялгавар тэг гарна — энэ буруу. Хасахдаа аль нь хасагдагч болохыг анхаар: эхний илэрхийллээс хоёр дахийг хас.</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>(2; 5) цэгийг дайрсан, y = 3x − 1 шулуунтай параллель шулууны чөлөөт гишүүн b-г ол.</t>
+          <t>(2; 7) цэгийг дайрсан, y = 3x − 1 шулуунтай параллель шулууны чөлөөт гишүүн b-г ол.</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>−1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>[-1]</t>
+          <t>[1]</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
@@ -11870,22 +11870,22 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Параллель шулуунууд ижил налалттай: k = 3.</t>
+          <t>$y = k_1x + b_1$ ба $y = k_2x + b_2$ шулуунууд параллель байх нөхцөл: $k_1 = k_2$ ба $b_1 \ne b_2$. Иймд хайж буй шулууны $k$ мэдэгдэж, зөвхөн чөлөөт гишүүн $b$ үл мэдэгдэх үлдэнэ.</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>(2; 5)-ыг y = 3x + b-д орлуул.</t>
+          <t>Өгөгдсөн шулууны налалтыг шинэ шулууны $k$ болгон ав. $y = kx + b$-д $(2; 7)$ цэгийн координатыг орлуулж $b$-ийн хувьд тэгшитгэл гарга.</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>5 = 6 + b.</t>
+          <t>Цэгийн ординат $7$-г шууд $b$ гэж авах нь алдаа — $b$ нь $x = 0$ үеийн утга. Олсон $b$ нь өгөгдсөн шулууныхаас ялгаатай эсэхийг (давхцахгүй байх) шалга.</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>b = 5 гэж цэгийн ординатыг авах</t>
+          <t>b = 7 гэж цэгийн ординатыг авах</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>Параллель шулуунууд ижил налалттай: $k = 3$. || $y = 3x + b$-д $(2;5)$: $5 = 6 + b$. || $b = -1$.</t>
+          <t>Параллель шулуунууд ижил налалттай: $k = 3$. || $y = 3x + b$-д $(2;7)$: $7 = 6 + b$. || $b = 1$; $b \ne -1$ тул шулуунууд давхцахгүй, параллель.</t>
         </is>
       </c>
     </row>
@@ -11950,17 +11950,17 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Дээш харсан парабол оройноосоо баруун тийш өснө.</t>
+          <t>$a &gt; 0$ үед $y = ax^2 + bx + c$ парабол $(-\infty; x_0]$ дээр буурч, $[x_0; +\infty)$ дээр өснө; $x_0 = -\frac{b}{2a}$. Өсөх завсрыг оройн абсциссаар тодорхойлно.</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>Оройн абсцисс x₀ = 0.</t>
+          <t>$a$ ба $b$-г тодорхойлж ($x$-тэй гишүүн байхгүй бол $b = 0$) оройн абсциссыг ол. Дараа нь параболын чиглэлээр өсөх талыг сонго.</t>
         </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>[0; +∞).</t>
+          <t>Чөлөөт гишүүнийг оройн абсцисс гэж андуурах нь түгээмэл — $c$ нь оройн ордината ($b = 0$ үед). Шалгахдаа орой баруун талаас хоёр утга авч, $x$ өсөхөд $y$ өсч байгааг хар.</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -12030,17 +12030,17 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>32-ыг 2-ын зэрэг хэлбэрт бич.</t>
+          <t>Илтгэгч функц $y = a^x$ ($a&gt;0$, $a \ne 1$) нь утга бүрээ зөвхөн нэг удаа авдаг тул $a^m = a^n \Leftrightarrow m = n$. Энэ шинжээр ижил суурьтай хоёр зэргийг илтгэгчээр нь тэнцүүлнэ.</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>32 = 2^5.</t>
+          <t>$32$-ыг 2-ын зэрэг хэлбэрт бич: 2-ыг дараалан үржүүлж хэдэн удаа үржүүлэхэд $32$ гарахыг тоол. Дараа нь хоёр талын илтгэгчийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>Суурь ижил бол илтгэгчүүд тэнцүү.</t>
+          <t>$32$-ыг $2$-т хуваах нь зэргийн илтгэгчийг өгөхгүй. Шалгахдаа олсон $x$-ээ орлуулж $2^x$-ийг тооцоол.</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -12110,17 +12110,17 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Ямар ч тооны тэг зэрэг хэд вэ?</t>
+          <t>Тэг зэргийн тодорхойлолт: $a \ne 0$ бол $a^0 = 1$; энэ нь $\frac{a^n}{a^n} = a^{n-n}$-ээс гардаг. Иймд $1$-ийг ямар ч эерэг суурьтай зэрэг хэлбэрээр бичиж болно.</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>a^0 = 1.</t>
+          <t>Баруун талын $1$-ийг 5 суурьтай зэрэг хэлбэрээр илэрхийл, тэгвэл хоёр тал ижил суурьтай болно. Дараа нь илтгэгчүүдийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>x = 0.</t>
+          <t>Илтгэгчийг $1$ гэж андуурах нь түгээмэл: $5^1 = 5$, харин $1$ биш. $y = 5^x$ өсөх функц тул тэгшитгэл цорын ганц шийдтэй; олсноо орлуулж шалга.</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -12190,17 +12190,17 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,001 = 1/1000.</t>
+          <t>Аравтын бутархайг 10-ын зэрэг хэлбэрт бичихэд $10^{-n} = \frac{1}{10^n}$ томьёо хэрэглэгдэнэ. Хоёр тал ижил суурьтай болбол $a^{f(x)} = a^{g(x)} \Leftrightarrow f(x) = g(x)$.</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>1/1000 = 10^(−3).</t>
+          <t>$0{,}001$-ийг энгийн бутархай $\frac{1}{10^n}$ хэлбэрт шилжүүл, дараа нь сөрөг илтгэгчтэй 10-ын зэрэг болго. Илтгэгчүүдийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>x = −3.</t>
+          <t>$10^x &lt; 1$ байх нь зөвхөн $x &lt; 0$ үед — эерэг хариу гарвал тэмдгээ алдсан. Олсон $x$-ээ орлуулж $10^x$-ийг аравтын бутархайгаар бичээд тулга.</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -12270,17 +12270,17 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>f(2) = 3², f(0) = 3⁰.</t>
+          <t>Функцийн утга $f(x_0)$ гэдэг нь томьёонд $x = x_0$ орлуулж гарсан тоо. Илтгэгч функц $f(x) = a^x$-д тэг зэргийн дүрэм $a^0 = 1$ ($a \ne 0$) хэрэглэгдэнэ.</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>9 + 1.</t>
+          <t>$f(2)$ ба $f(0)$-ийг тусад нь ол: $3^x$-ийн $x$-ийн оронд $2$ ба $0$-ийг орлуул. Гарсан хоёр утгыг нэм.</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>$3^0 = 0$ гэж үзэх нь түгээмэл алдаа — тэг зэрэг тэг биш. Мөн $3^2$-ыг $3 \cdot 2$ гэж үржүүлж болохгүй: зэрэг бол давтан үржвэр.</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -12350,17 +12350,17 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>8 ба 16-г хоёулаа 2-ын зэрэг болго.</t>
+          <t>Зэргийн зэргийн дүрэм $(a^m)^n = a^{mn}$ нь нэг тооны зэрэг болох өөр суурьтай тоонуудыг нийтлэг суурьт шилжүүлэх боломж олгоно. Дараа нь $a^{f(x)} = a^{g(x)} \Leftrightarrow f(x) = g(x)$.</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>(2³)^x = 2⁴.</t>
+          <t>$8$ ба $16$ хоёулаа 2-ын зэрэг; тус бүрийг $2^k$ хэлбэрт бич. Зүүн талыг $(2^k)^x$ гэж хялбарчилж, илтгэгчүүдийг тэнцүүлээд шугаман тэгшитгэл бод.</t>
         </is>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>3x = 4.</t>
+          <t>$16 : 8$ гэж хуваах нь илтгэгч олох арга биш. $8^1 = 8 &lt; 16 &lt; 64 = 8^2$ тул $x$ нь $1$ ба $2$-ын хооронд, бүхэл биш байх ёстой — хариугаа үүгээр шалга.</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -12430,17 +12430,17 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>27 = 3³.</t>
+          <t>Ижил суурьтай илтгэгч тэгшитгэл $a^{f(x)} = a^{g(x)}$ ($a&gt;0$, $a \ne 1$) нь $f(x) = g(x)$-тэй тэнцүү чанартай. Гэхдээ эхлээд хоёр талыг заавал ижил суурьтай болгох шаардлагатай.</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>2x − 1 = 3.</t>
+          <t>$27$-ыг 3 суурьтай зэрэг болгон бич. Дараа нь $2x - 1$-ийг баруун талын илтгэгчтэй тэнцүүлж, шугаман тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>2x = 4.</t>
+          <t>$2x - 1 = 27$ гэж бичих нь алдаа: илтгэгчийг тоотой биш, ижил суурьтай зэргийн илтгэгчтэй тэнцүүлнэ. Олсон $x$-ээ орлуулж $3^{2x-1}$-ийн утгыг шалга.</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
@@ -12510,17 +12510,17 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>1/2 = 2^(−1), 8 = 2³.</t>
+          <t>$\frac{1}{a} = a^{-1}$ ба $(a^m)^n = a^{mn}$ дүрмээр $\left(\frac{1}{a}\right)^x = a^{-x}$ болно. Ингэж бутархай суурийг бүхэл суурьт шилжүүлбэл хоёр талыг ижил суурьтай болгоно.</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>2^(−x) = 2³.</t>
+          <t>$\frac{1}{2}$-ыг $2^{-1}$, $8$-ыг 2-ын зэрэг хэлбэрт бич. Зүүн тал $2^{-x}$ болсны дараа илтгэгчүүдийг тэнцүүлж, $x$-ийг ол.</t>
         </is>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>−x = 3.</t>
+          <t>$\frac{1}{2}$-ыг $2$ гэж үзвэл тэмдэг алдана. $y = \left(\frac{1}{2}\right)^x$ буурах функц бөгөөд $1$-ээс их утгыг зөвхөн $x &lt; 0$ үед авдаг — хариуныхаа тэмдгийг үүгээр шалга.</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -12590,17 +12590,17 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Илтгэгч функцийн шинж суурь a-аас хамаарна.</t>
+          <t>Илтгэгч функц $y = a^x$ ($a &gt; 0$, $a \ne 1$)-ийн монотон чанар зөвхөн суурьнаас хамаарна: $a &gt; 1$ бол өсөх, $0 &lt; a &lt; 1$ бол буурах. Иймд суурийг $1$-тэй харьцуулахад хангалттай.</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>0 &lt; a &lt; 1 бол буурна.</t>
+          <t>Функцийн суурь $a$-г ялгаж бичээд $1$-тэй харьцуул. Аль нөхцөлд тохирохыг тогтоож, бодлогын тохиролцоогоор (өсөх бол $1$, буурах бол $-1$) хариул.</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,5 &lt; 1.</t>
+          <t>Бүх илтгэгч функц өсдөг гэж үзэх нь алдаа. Шалгахдаа хоёр цэгт, жишээ нь $x = 0$ ба $x = 1$ үед утгыг тооцоол: $x$ ихсэхэд $y$ ихсэв үү, багасав уу?</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
@@ -12670,17 +12670,17 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>2^(x+2) = 2^x · 4.</t>
+          <t>Ижил суурьтай зэргүүдийн үржвэр: $a^{m+n} = a^m \cdot a^n$. Иймд $a^{x+k} = a^k \cdot a^x$ гэж задлаад нийтлэг үржигдэхүүн $a^x$-ийг хаалтнаас гаргаж болно.</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>2^x (4 − 1) = 12.</t>
+          <t>$2^{x+2}$-ыг $2^2 \cdot 2^x$ гэж задал, дараа нь $2^x$-ийг хаалтнаас гарга. Гарсан коэффициентэд хоёр талыг хувааж, $2^x = c$ хэлбэрийн энгийн тэгшитгэлд шилжүүл.</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>2^x = 4.</t>
+          <t>$2^{x+2} - 2^x$-ийг $2^2$ гэж илтгэгчүүдийг хасах нь алдаа — зэргийн ялгаварт ийм дүрэм байхгүй. Олсон $x$-ээ орлуулж зүүн талын утга $12$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12750,17 +12750,17 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>4^x = (2^x)². t = 2^x гэж орлуул.</t>
+          <t>$4^x = (2^2)^x = (2^x)^2$ тул тэгшитгэлийг $t = 2^x$ ($t &gt; 0$) орлуулгаар квадрат тэгшитгэл болгоно. Эцэст нь $t$-ийн язгуур бүрээр $2^x = t$ тэгшитгэлийг бодно.</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>t² − 5t + 4 = 0 → t = 1, t = 4.</t>
+          <t>$t = 2^x$ орлуулаад гарсан квадрат тэгшитгэлийг Виетийн теорем эсвэл дискриминантаар бод. Эерэг язгуур бүрийг 2-ын зэрэг хэлбэрт бичиж $x$-ийг ол.</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>2^x = 1 → x = 0; 2^x = 4 → x = 2.</t>
+          <t>$t$-ийн язгуурыг шууд $x$ гэж бичих алдаанаас сэргийл: $t = 2^x$ тул буцаан орлуулах алхам заавал хэрэгтэй. Хоёр шийдийг тус бүр анхны тэгшитгэлд орлуулж шалга.</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
@@ -12830,17 +12830,17 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>t = 5^x.</t>
+          <t>$25^x = (5^x)^2$ адилтгал нь тэгшитгэлийг $t = 5^x$ ($t&gt;0$) орлуулгаар квадрат тэгшитгэл болгоно. Илтгэгч функц харилцан нэг утгатай тул $t$-ийн эерэг язгуур бүр яг нэг $x$ өгнө.</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>t² − 6t + 5 = 0 → t = 1, t = 5.</t>
+          <t>$t = 5^x$ гэж тэмдэглээд квадрат тэгшитгэлийг бод. Олдсон язгуур бүрийг (түүний дотор $1$-ийг ч) $5^k$ хэлбэрт бичиж, $x$-ийг гарга.</t>
         </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>5^x = 1, 5^x = 5.</t>
+          <t>$5^x = t$ үед $x = t$ гэж бичих нь алдаа — $x$ бол $5$-ыг $t$ болгох илтгэгч, $t$ өөрөө биш. Хоёр шийдийг анхны тэгшитгэлд орлуулж $0$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
@@ -12910,17 +12910,17 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>16 = 2⁴.</t>
+          <t>Илтгэгч тэнцэтгэл бишийн дүрэм: $a &gt; 1$ бол $a^{f(x)} &gt; a^{g(x)} \Leftrightarrow f(x) &gt; g(x)$ (тэмдэг хадгалагдана), $0 &lt; a &lt; 1$ бол тэмдэг эргэнэ. Энэ нь $y = a^x$-ийн өсөх/буурах чанараас гардаг.</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>Суурь 2 &gt; 1 тул функц өснө — тэмдэг хадгалагдана.</t>
+          <t>$16$-г 2-ын зэрэг хэлбэрт бичиж хоёр талыг ижил суурьтай болго. Суурь $1$-ээс их эсэхийг тогтоогоод, тохирох тэмдэгтэйгээр илтгэгчүүдийг харьцуул.</t>
         </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>x &gt; 4.</t>
+          <t>Суурь $1$-ээс их үед тэмдгийг эргүүлэх нь алдаа. Шалгахдаа гарсан мужаас нэг тоо, мужаас гадуур нэг тоо авч $2^x &gt; 16$-д орлуулж үз.</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
@@ -12990,17 +12990,17 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>9 = (1/3)^(−2).</t>
+          <t>$0 &lt; a &lt; 1$ үед $y = a^x$ буурах функц тул $a^{f(x)} \ge a^{g(x)} \Leftrightarrow f(x) \le g(x)$ — тэнцэтгэл бишийн тэмдэг эргэнэ. $a &gt; 1$ үед тэмдэг хадгалагдана.</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>Суурь 1/3 &lt; 1 тул функц буурна — тэмдэг эргэнэ.</t>
+          <t>$\frac{1}{3} = 3^{-1}$ гэдгийг ашиглан $9$-ийг $\frac{1}{3}$ суурьтай зэрэг хэлбэрт бич. Дараа нь суурийн утгаас хамааран тэмдгийг зөв сонгож илтгэгчүүдийг харьцуул.</t>
         </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>x ≤ −2.</t>
+          <t>Суурь $1$-ээс бага үед тэмдгийг эргүүлэхээ мартах нь хамгийн түгээмэл алдаа; 3 суурьт шилжүүлсэн бол $-x$-ийн $-1$ коэффициентэд хуваахад тэмдэг эргэнэ. Мужаас нэг тоо авч орлуулж шалга.</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -13070,17 +13070,17 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>100 · 2^t = 1600.</t>
+          <t>Илтгэгч өсөлтийн загвар: $N(t) = N_0 \cdot a^t$, энд $N_0$ — анхны тоо, $a$ — нэгж хугацааны өсөлтийн коэффициент. Хугацаа $t$ илтгэгчид байгаа тул тэгшитгэлийг ижил суурьт шилжүүлж бодно.</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>2^t = 16.</t>
+          <t>Тэгшитгэлийн хоёр талыг $N_0$-д хувааж $2^t = c$ хэлбэрт оруул. Дараа нь $c$-г 2-ын зэрэг болгон бичиж, илтгэгчүүдийг тэнцүүл.</t>
         </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>2⁴ = 16.</t>
+          <t>$1600 : 100$ харьцааг шууд цаг гэж авах алдаа: харьцаа нь хэдэн дахин өссөнийг, харин $t$ нь хэдэн удаа хоёр дахин өссөнийг заана. Цаг тутмын тоог дараалан бичиж шалга.</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
@@ -13150,17 +13150,17 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>log₃ 81 гэдэг нь 3-ыг хэдэн зэрэгт дэвшүүлбэл 81 болох вэ гэсэн асуулт.</t>
+          <t>$\log_a b = c \Leftrightarrow a^c = b$ ($a &gt; 0$, $a \ne 1$, $b &gt; 0$). Иймд логарифмын утга нь суурийг аргумент болгох илтгэгч бөгөөд аргумент суурийн бүхэл зэрэг бол бүхэл тоо гарна.</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>3⁴ = 81.</t>
+          <t>$\log_3 81 = c$ гэвэл $3^c = 81$. $81$-ийг 3-т дараалан хувааж, $1$ гартал хэдэн удаа хуваахыг тоолж илтгэгчийг ол.</t>
         </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>$81 : 3$ гэж нэг удаа хуваах нь логарифм биш. Олсон $c$-ээ $3^c$-д орлуулж $81$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -13230,17 +13230,17 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>1/25 = 5^?</t>
+          <t>$\log_a a^n = n$ ($a&gt;0$, $a \ne 1$) нь сөрөг $n$-д ч хүчинтэй. $\frac{1}{a^n} = a^{-n}$ томьёогоор бутархайг сөрөг илтгэгчтэй зэрэг болгоно.</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>1/25 = 5^(−2).</t>
+          <t>$25$-ыг 5-ын зэрэг хэлбэрт бичээд $\frac{1}{25}$-ыг сөрөг илтгэгчтэй зэрэг болго. Дараа нь тодорхойлолтоор логарифмыг ол.</t>
         </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>−2.</t>
+          <t>$a &gt; 1$ үед $0 &lt; b &lt; 1$ аргументын логарифм сөрөг — эерэг хариу гарвал тэмдгээ алдсан. $5^c$-ийг тооцоолж $\frac{1}{25}$-тай тулга.</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
@@ -13310,17 +13310,17 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>logₐ a хэд вэ? logₐ 1 хэд вэ?</t>
+          <t>Тодорхойлолт $\log_a b = c \Leftrightarrow a^c = b$-ээс $\log_a a$ ба $\log_a 1$-ийн утга шууд гарна: эхнийх нь $a^c = a$, хоёр дахь нь $a^c = 1$ байх $c$. Эдгээр нь суурь $a$-аас хамаардаггүй тогтмол утгууд.</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>logₐ a = 1, logₐ 1 = 0.</t>
+          <t>Нэмэгдэхүүн тус бүрийг тодорхойлолтоор тэгшитгэл болгон бич: $7^c = 7$ ба $7^c = 1$. Хоёр илтгэгчийг олоод нэм.</t>
         </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>1 + 0.</t>
+          <t>$\log_7 1$-ийг $1$ гэж үзэх алдаа: $7^1 \ne 1$. Тэг зэргийн тодорхойлолтыг сана.</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -13390,17 +13390,17 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>0,01 = 1/100 = 10^?</t>
+          <t>$\lg b = \log_{10} b$ ба бүх бүхэл (сөрөг ч) $n$-ийн хувьд $\lg 10^n = n$. Аравтын бутархайг $10^{-n} = \frac{1}{10^n}$ хэлбэрт бичвэл логарифм шууд олдоно.</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>10^(−2).</t>
+          <t>$0{,}01$-ийг энгийн бутархай болгоод хуваарийг $10^n$ хэлбэрт бич, дараа нь сөрөг илтгэгчтэй 10-ын зэрэг болго. Тодорхойлолтоор утгыг ол.</t>
         </is>
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>−2.</t>
+          <t>$\lg 0{,}01$-ийг аргументтай нь адил гэж үзэх алдаа. $0 &lt; b &lt; 1$ үед $\lg b &lt; 0$ тул хариу сөрөг байх ёстой; $10^c$-ийг тооцоолж шалга.</t>
         </is>
       </c>
       <c r="N163" s="2" t="inlineStr">
@@ -13470,17 +13470,17 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Тус бүрийг тооцоол эсвэл үржвэрийн логарифм болго.</t>
+          <t>Үржвэрийн логарифм: $\log_a b + \log_a c = \log_a (bc)$ ($b, c &gt; 0$). Нийлбэрийг нэг логарифм болгох эсвэл нэмэгдэхүүн бүрийг тусад нь тодорхойлолтоор бодож болно.</t>
         </is>
       </c>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>log₂ 8 = 3, log₂ 4 = 2.</t>
+          <t>$8$ ба $4$-ийг 2-ын зэрэг хэлбэрт бичээд логарифм тус бүрийг олж нэм. Шалгалт болгож үржвэрийн чанараар $\log_2 (8 \cdot 4)$-ийг тооцоол.</t>
         </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>3 + 2 (= log₂ 32).</t>
+          <t>$\log_2 (8 + 4)$ гэж аргументуудыг нэмэх нь алдаа — логарифмын нийлбэр аргументын үржвэрт шилжинэ. Хоёр аргын хариу ижил гарах ёстой.</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -13550,17 +13550,17 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>logₐ b − logₐ c = logₐ(b/c).</t>
+          <t>Ялгаврын логарифм: $\log_a b - \log_a c = \log_a \frac{b}{c}$ ($a&gt;0$, $a \ne 1$, $b, c &gt; 0$). Тус бүр нь бүхэл биш логарифмуудыг нэгтгэхэд бүхэл утга гарч болно.</t>
         </is>
       </c>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>log₃(54/2) = log₃ 27.</t>
+          <t>Ялгаврын чанараар нэг логарифм болго: $54$-ийг $2$-т хуваа. Гарсан аргументыг 3-ын зэрэг хэлбэрт бичээд тодорхойлолтоор утгыг ол.</t>
         </is>
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>3³ = 27.</t>
+          <t>$\log_3 (54 - 2)$ гэж аргументуудыг хасах нь алдаа. Хариугаа $3^c$-ийг тооцоолж, нэгтгэсэн аргументтай тулгаж шалга.</t>
         </is>
       </c>
       <c r="N165" s="2" t="inlineStr">
@@ -13630,17 +13630,17 @@
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>√8 = 8^(1/2).</t>
+          <t>Зэргийн логарифм: $\log_a b^n = n \log_a b$ ($b &gt; 0$), мөн язгуурыг бутархай зэрэг болгох $\sqrt{b} = b^{\frac{1}{2}}$ томьёо. Хоёулаа энэ бодлогод хэрэглэгдэнэ.</t>
         </is>
       </c>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>logₐ b^n = n·logₐ b.</t>
+          <t>$\sqrt{8}$-ыг $8^{\frac{1}{2}}$ гэж бичээд зэргийн логарифмын чанараар илтгэгчийг логарифмын өмнө гарга. Үлдсэн $\log_2 8$-ыг тодорхойлолтоор олж, үржүүл.</t>
         </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>(1/2)·log₂ 8 = (1/2)·3.</t>
+          <t>Логарифм ба язгуурын дарааллыг солих (жишээ нь $\sqrt{\log_2 8}$) алдаа. $2 &lt; \sqrt{8} &lt; 4$ тул логарифм $1$ ба $2$-ын хооронд, бүхэл биш байх ёстой.</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -13710,17 +13710,17 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Тодорхойлолтоор: x = 3⁴.</t>
+          <t>Логарифмын тодорхойлолт: $\log_a x = c \Leftrightarrow x = a^c$ ($a &gt; 0$, $a \ne 1$), тодорхойлогдох муж $x &gt; 0$. Иймд үл мэдэгдэгч аргументыг зэргээр шууд илэрхийлнэ.</t>
         </is>
       </c>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>3⁴ = 81.</t>
+          <t>Тодорхойлолтоор логарифмыг арилгаж $x$-ийг суурь $3$-ын зэрэг хэлбэрээр бич. Дараа нь тэр зэргийг тооцоол.</t>
         </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>81.</t>
+          <t>$x = 3 \cdot 4$ гэж үржүүлэх алдаа: $4$ нь илтгэгч. Олсон $x$-ийг шалгахдаа $\log_3 x$-ийг тооцоолж $4$ гарахыг тулга.</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
@@ -13790,17 +13790,17 @@
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>x² = 25.</t>
+          <t>$\log_a b = c \Leftrightarrow a^c = b$, суурийн нөхцөл $a &gt; 0$, $a \ne 1$. Суурь үл мэдэгдэгч бол энэ нөхцөл тодорхойлогдох мужийг тогтооно.</t>
         </is>
       </c>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>Логарифмын суурь эерэг, 1-ээс ялгаатай.</t>
+          <t>Тодорхойлолтоор $x^2 = 25$ хэлбэрт шилжүүлж, квадрат тэгшитгэлийн язгууруудыг ол. Дараа нь язгуур бүрийг суурийн нөхцөлөөр шүү.</t>
         </is>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>x = 5 (x = −5 тохирохгүй).</t>
+          <t>$x^2 = 25$-ийн бүх язгуурыг хариу болгох алдаа: сөрөг тоо логарифмын суурь болж чадахгүй. Язгуур бүрийг $x &gt; 0$, $x \ne 1$ нөхцөлөөр шалга.</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13870,17 +13870,17 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>Ижил суурьтай логарифмууд тэнцүү бол аргументууд тэнцүү.</t>
+          <t>Логарифм функц харилцан нэг утгатай тул $\log_a f(x) = \log_a g(x) \Leftrightarrow f(x) = g(x)$, нэмэлт нөхцөл $f(x) &gt; 0$, $g(x) &gt; 0$. Тодорхойлогдох мужийг тусад нь шалгах ёстой.</t>
         </is>
       </c>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>x + 3 = 2x − 1.</t>
+          <t>ТМ-ийг бич: $x + 3 &gt; 0$ ба $2x - 1 &gt; 0$. Аргументуудыг тэнцүүлж шугаман тэгшитгэлийг бод, дараа нь шийдийг ТМ-тэй тулга.</t>
         </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>x = 4; шалга: 7 &gt; 0, 7 &gt; 0.</t>
+          <t>ТМ шалгахгүй бол илүү шийд үлдэж мэднэ. Олсон $x$-ийг хоёр аргументад орлуулж, хоёулаа эерэг ба тэнцүү гарахыг шалга.</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
@@ -13950,17 +13950,17 @@
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Баруун талыг нэг логарифм болго: log₃(2x).</t>
+          <t>Үржвэрийн логарифм $\log_a b + \log_a c = \log_a (bc)$ ба $\log_a f = \log_a g \Leftrightarrow f = g$ ($f, g &gt; 0$). Тодорхойлогдох муж нь анхны тэгшитгэлийн бүх аргументаас тогтоно.</t>
         </is>
       </c>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>x² − 8 = 2x → x² − 2x − 8 = 0.</t>
+          <t>ТМ: $x^2 - 8 &gt; 0$ ба $x &gt; 0$. Баруун талыг нэг логарифм болгон нэгтгэж аргументуудыг тэнцүүл; гарсан квадрат тэгшитгэлийг бод.</t>
         </is>
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>x = 4, x = −2; −2 тохирохгүй (log₃(−2) байхгүй).</t>
+          <t>Квадрат тэгшитгэлийн язгуур бүхэн шийд биш: $\log_3 x$ сөрөг $x$-д тодорхойлогдохгүй. Язгуур бүрийг $x^2 - 8$ ба $x$-д орлуулж эерэг эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N170" s="2" t="inlineStr">
@@ -14030,17 +14030,17 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>8 ба 4-ийг 2-ын зэргээр бич.</t>
+          <t>Суурь солих томьёо: $\log_a b = \frac{\log_c b}{\log_c a}$ ($a, c &gt; 0$, $a, c \ne 1$, $b &gt; 0$). Суурь ба аргумент хоёулаа нэг тооны зэрэг бол тэр тоог шинэ суурь болгох нь тохиромжтой.</t>
         </is>
       </c>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>log₄ 8 = log₂ 8 / log₂ 4.</t>
+          <t>$4$ ба $8$ хоёулаа 2-ын зэрэг тул 2 суурьт шилжүүлж хүртвэр, хуваарийн логарифмыг тус тусад нь ол. Эсвэл $4^c = 8$ гэж бичээд хоёр талыг 2 суурьт оруулж болно.</t>
         </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>3/2.</t>
+          <t>$8 : 4$ гэж хуваах нь алдаа. $4^1 &lt; 8 &lt; 4^2$ тул хариу $1$ ба $2$-ын хооронд, бүхэл биш байх ёстой.</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
@@ -14110,17 +14110,17 @@
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Тодорхойлогдох муж: x &gt; 0.</t>
+          <t>$a &gt; 1$ үед $y = \log_a x$ өсөх функц тул $\log_a u &lt; \log_a v \Leftrightarrow u &lt; v$ ($u, v &gt; 0$); $0 &lt; a &lt; 1$ үед тэмдэг эргэнэ. Тодорхойлогдох муж $x &gt; 0$-ийг хариунд заавал тусгана.</t>
         </is>
       </c>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>Суурь 2 &gt; 1 тул x &lt; 2³.</t>
+          <t>Баруун талын $3$-ыг $\log_2 2^3$ хэлбэрт бич. Суурь $1$-ээс их эсэхийг тогтоогоод аргументуудыг харьцуулж, гарсан мужийг ТМ-тэй огтлолцуул.</t>
         </is>
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>0 &lt; x &lt; 8.</t>
+          <t>$x &gt; 0$ нөхцөлийг мартах нь түгээмэл алдаа: сөрөг тоо ба тэг логарифмын аргумент болж чадахгүй. Хариу мужаас нэг тоо, мужаас гадуур нэг тоо авч орлуулж шалга.</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -14190,17 +14190,17 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>50 = 100 / 2.</t>
+          <t>Ялгаврын логарифм $\lg \frac{b}{c} = \lg b - \lg c$ ба $\lg 10^n = n$. Тоог 10-ын зэрэг ба мэдэгдэж буй тоо ($2$)-ны ноогдвор хэлбэрт задлах нь гол санаа.</t>
         </is>
       </c>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lg 50 = lg 100 − lg 2.</t>
+          <t>$50$-ийг $100$ ба $2$-ын ноогдвор хэлбэрээр илэрхийл. Ялгаврын чанараар задалж, $\lg 100$-г тодорхойлолтоор олоод $\lg 2$-ыг $a$-аар соль.</t>
         </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>2 − a.</t>
+          <t>$\lg 50 = 25 \lg 2$ гэх алдаа: $\lg (bc) \ne b \lg c$. Шалгахдаа $\lg 2 \approx 0{,}301$ гэж аваад гарсан илэрхийллээ $\lg 50 \approx 1{,}699$-тэй харьцуул.</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
@@ -14270,17 +14270,17 @@
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>30°-ын тусгай утгуудын хүснэгтийг сана.</t>
+          <t>Хурц өнцгийн косинус нь налсан катетыг гипотенузад харьцуулсан харьцаа: $\cos\alpha = \frac{b}{c}$. Тусгай өнцгийн утгыг тэгш талт гурвалжныг өндрөөр нь хагаслахад үүсэх $30^\circ$–$60^\circ$–$90^\circ$ гурвалжнаас гаргадаг.</t>
         </is>
       </c>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>sin 30° = 1/2, cos 30° = ?</t>
+          <t>Тал нь $2$ тэгш талт гурвалжныг хагаславал гипотенуз $2$, богино катет $1$ болно; нөгөө катетыг Пифагорын теоремоор ол. $30^\circ$-ын өнцөгт налсан (эсрэг биш) катетыг сонгож гипотенузад харьцуул.</t>
         </is>
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>√3/2.</t>
+          <t>$\cos 30^\circ$-ыг $\sin 30^\circ$-тай андуурах нь түгээмэл алдаа. Шалгах: $\cos\alpha = \sin(90^\circ - \alpha)$ тул $\cos 30^\circ = \sin 60^\circ$, мөн $\sin^2 30^\circ + \cos^2 30^\circ = 1$ биелэх ёстой.</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
@@ -14350,17 +14350,17 @@
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>tg α = sin α / cos α.</t>
+          <t>Тангенс: $\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha}$ ($\cos\alpha \ne 0$); тэгш өнцөгт гурвалжинд эсрэг катетыг налсан катетад харьцуулсан харьцаа. Тусгай өнцгийн хувьд $30^\circ$–$60^\circ$–$90^\circ$ гурвалжныг ашиглана.</t>
         </is>
       </c>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>sin 60° = √3/2, cos 60° = 1/2.</t>
+          <t>Гипотенуз нь $2$ байх $30^\circ$–$60^\circ$–$90^\circ$ гурвалжинд $60^\circ$-ын эсрэг ба налсан катетыг тодорхойл. Эсрэг катетыг налсан катетад хуваа, эсвэл $\sin 60^\circ$-ыг $\cos 60^\circ$-д хуваа.</t>
         </is>
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>(√3/2) : (1/2).</t>
+          <t>$\operatorname{tg}60^\circ$-ыг $\operatorname{tg}30^\circ$-тай андуурч болохгүй. Тангенс $0^\circ$-аас $90^\circ$ хүртэл өсдөг тул $\operatorname{tg}60^\circ &gt; \operatorname{tg}45^\circ$, өөрөөр хэлбэл хариу $1$-ээс их байх ёстой.</t>
         </is>
       </c>
       <c r="N175" s="2" t="inlineStr">
@@ -14430,17 +14430,17 @@
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>180° = π радиан — энэ бол тодорхойлолт.</t>
+          <t>Радиан нь нумын урт нь радиустай тэнцүү байх төв өнцгийн хэмжээ. Тойргийн урт $2\pi r$ тул бүтэн эргэлт $360^\circ$ нь $2\pi$ радиан болно.</t>
         </is>
       </c>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>π.</t>
+          <t>Градусаас радиан руу $\alpha \cdot \frac{\pi}{180^\circ}$ томьёогоор шилжүүлнэ. Эсвэл өгсөн өнцөг бүтэн эргэлтийн ямар хэсэг (дэлгэсэн өнцөг) болохыг тодорхойлж, бүтэн эргэлтийн радиан хэмжээнээс тэр хэсгийг ав.</t>
         </is>
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>π ≈ 3,14.</t>
+          <t>$2\pi$ нь бүтэн эргэлт тул дэлгэсэн өнцөгтэй андуурч болохгүй. Шалгах: $1$ радиан $\approx 57^\circ$ гэдгийг ашиглан гарсан утгаа буцааж градус болгоход ойролцоогоор $180^\circ$ гарах ёстой.</t>
         </is>
       </c>
       <c r="N176" s="2" t="inlineStr">
@@ -14510,17 +14510,17 @@
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>π = 180°.</t>
+          <t>Радиан ба градусын хамаарал: $\pi$ радиан нь $180^\circ$. Иймээс радианаас градус руу $\alpha \cdot \frac{180^\circ}{\pi}$ томьёогоор шилжүүлнэ.</t>
         </is>
       </c>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>180° : 4.</t>
+          <t>Өгсөн илэрхийлэлд $\pi$-г градусын хэмжээгээр нь орлуулж, хуваарьт байгаа тоонд хуваа. Өөрөөр хэлбэл $\frac{\pi}{4}$ нь дэлгэсэн өнцгийн хэд дэх хэсэг болохыг ол.</t>
         </is>
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>45°.</t>
+          <t>$\frac{\pi}{4}$-ийг $90^\circ$ гэх нь алдаа — $90^\circ$ бол $\frac{\pi}{2}$. Шалгах: гарсан градусыг $\frac{\pi}{180^\circ}$-аар үржүүлж буцаан радиан болгоход анхны утга гарах ёстой.</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
@@ -14590,17 +14590,17 @@
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>sin²α + cos²α = ? (ямар ч α-д).</t>
+          <t>Нэгж тойрог дээрх $(\cos\alpha;\ \sin\alpha)$ цэг төвөөс радиусын зайд оршдог тул Пифагорын теоремоор координатуудын квадратын нийлбэр радиусын квадраттай тэнцүү. Энэ нь тригонометрийн үндсэн адилтгал бөгөөд ямар ч $\alpha$-д биелнэ.</t>
         </is>
       </c>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>Үндсэн адилтгал: 1.</t>
+          <t>Нэг ижил өнцгийн синус ба косинусын квадратын нийлбэр байгаа тул үндсэн адилтгалыг шууд хэрэглэ. Эсвэл $45^\circ$-ын синус, косинусыг тэгш өнцөгт адил хажуут гурвалжнаас олоод квадрат зэрэгт дэвшүүлж нэм.</t>
         </is>
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>Эсвэл (√2/2)² + (√2/2)² = 1/2 + 1/2.</t>
+          <t>$\sin^2 45^\circ$ нь $(\sin 45^\circ)^2$ — $2\sin 45^\circ$ биш. Хоёр аргаар (адилтгал ба шууд тооцоо) бодож, гарсан утгууд давхцаж байгааг шалга.</t>
         </is>
       </c>
       <c r="N178" s="2" t="inlineStr">
@@ -14670,17 +14670,17 @@
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>sin²α = 1 − cos²α.</t>
+          <t>Тригонометрийн үндсэн адилтгал: ямар ч $\alpha$-д $\sin^2\alpha + \cos^2\alpha = 1$. Хурц өнцгийн хувьд синус, косинус хоёулаа эерэг.</t>
         </is>
       </c>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>1 − 25/169 = 144/169.</t>
+          <t>$\sin^2\alpha = 1 - \cos^2\alpha$ гэж илэрхийлээд косинусын утгын квадратыг орлуул; $1$-ийг $\frac{169}{169}$ гэж бичвэл хасахад амар. Гарсан бутархайн хүртвэр, хуваарийн квадрат язгуурыг тус тусад нь гарга.</t>
         </is>
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>√(144/169); хурц өнцөгт sin &gt; 0.</t>
+          <t>$\sin\alpha = 1 - \cos\alpha$ гэж квадратгүй хасах нь алдаа. Хурц өнцөг тул эерэг язгуурыг ав; гарсан утгын квадратыг $\cos^2\alpha$-тай нэмэхэд $1$ гарахыг шалга.</t>
         </is>
       </c>
       <c r="N179" s="2" t="inlineStr">
@@ -14750,17 +14750,17 @@
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Эхлээд cos α-г ол.</t>
+          <t>$\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha}$ ($\cos\alpha \ne 0$), мөн $\sin^2\alpha + \cos^2\alpha = 1$. Тангенсыг олохын тулд эхлээд дутуу байгаа косинусыг адилтгалаар олно.</t>
         </is>
       </c>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>cos α = 4/5.</t>
+          <t>Хурц өнцөг тул $\cos\alpha = \sqrt{1 - \sin^2\alpha}$ гэж эерэг язгуураар ол. Дараа нь синусыг косинуст хувааж, хуваарь ижил хоёр бутархайн харьцааг хялбарчил.</t>
         </is>
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>tg α = sin α / cos α = (3/5)/(4/5).</t>
+          <t>Тангенсыг синустай ижил гэж бодох нь алдаа — тангенс эсрэг катетыг гипотенузад биш, налсан катетад харьцуулна. Шалгах: хурц өнцөгт $0 &lt; \cos\alpha &lt; 1$ тул $\operatorname{tg}\alpha &gt; \sin\alpha$ байх ёстой.</t>
         </is>
       </c>
       <c r="N180" s="2" t="inlineStr">
@@ -14830,17 +14830,17 @@
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>150° = 180° − 30°.</t>
+          <t>Ангижруулах томьёо: $\sin(180^\circ - \alpha) = \sin\alpha$, $\cos(180^\circ - \alpha) = -\cos\alpha$. II мөчлөгийн өнцгийн функцийг хурц өнцгийн функцээр илэрхийлэхэд хэрэглэнэ; II мөчлөгт синус эерэг.</t>
         </is>
       </c>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>sin(180° − α) = sin α.</t>
+          <t>$150^\circ$-ыг $180^\circ - \alpha$ хэлбэрт бичиж, хурц өнцөг $\alpha$-г тодорхойл. Томьёогоор тэр хурц өнцгийн синус руу шилжүүлээд тусгай өнцгийн утгыг ашигла.</t>
         </is>
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>sin 30° = 1/2.</t>
+          <t>II мөчлөгт нэгж тойргийн цэг дээд хагаст оршдог тул синусыг сөрөг болгож болохгүй. Шалгах: $150^\circ$ ба $30^\circ$-ын цэгүүд $y$ тэнхлэгийн хувьд тэгш хэмтэй тул ординат нь ижил.</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
@@ -14910,17 +14910,17 @@
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>120° = 180° − 60°.</t>
+          <t>Ангижруулах томьёо: $\sin(180^\circ - \alpha) = \sin\alpha$, $\cos(180^\circ - \alpha) = -\cos\alpha$. II мөчлөгийн өнцгийн функцийг хурц өнцгийн функцээр илэрхийлэхэд хэрэглэнэ; II мөчлөгт косинус сөрөг.</t>
         </is>
       </c>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>cos(180° − α) = −cos α.</t>
+          <t>$120^\circ$-ыг $180^\circ - \alpha$ хэлбэрт бичиж хурц өнцгийг ол. Томьёогоор тэр хурц өнцгийн косинус руу шилжүүлж, урд нь гарах тэмдгийг анхаарч тусгай утгыг орлуул.</t>
         </is>
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>−cos 60° = −1/2.</t>
+          <t>Тэмдгийг мартах нь түгээмэл алдаа: II мөчлөгт цэг $y$ тэнхлэгийн зүүн талд оршдог тул абсцисс (косинус) сөрөг. Хариуны тэмдэг ба абсолют утгыг тусад нь шалга.</t>
         </is>
       </c>
       <c r="N182" s="2" t="inlineStr">
@@ -14990,17 +14990,17 @@
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>Нэгж тойрог дээр cos = 0 (x координат 0) хаана вэ?</t>
+          <t>Нэгж тойрог дээр $x$ өнцөгт харгалзах цэгийн абсцисс нь $\cos x$. Иймээс $\cos x = 0$ гэдэг нь харгалзах цэг ординатын ($y$) тэнхлэг дээр оршино гэсэн үг.</t>
         </is>
       </c>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>Дээд ба доод цэг.</t>
+          <t>Нэгж тойрог $y$ тэнхлэгтэй хэдэн цэгт огтлолцохыг зургаар тодорхойл. Цэг бүрт харгалзах өнцгийг $0$-ээс цагийн зүүний эсрэг чиглэлд хэмжиж радианаар илэрхийл.</t>
         </is>
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>π/2 ба 3π/2.</t>
+          <t>Зөвхөн нэг шийд бичих нь түгээмэл алдаа — нэг бүтэн эргэлтэд косинус хэдэн удаа тэг болохыг тоол. Шийд бүр $[0; 2\pi]$ завсарт орж, орлуулахад косинус тэг болохыг шалга.</t>
         </is>
       </c>
       <c r="N183" s="2" t="inlineStr">
@@ -15070,17 +15070,17 @@
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>sin x = 1/2.</t>
+          <t>$\sin x = a$ ($0 &lt; a &lt; 1$) тэгшитгэл $[0; 2\pi)$ завсарт хоёр шийдтэй: $x_1 = \arcsin a$ (I мөчлөг) ба $x_2 = \pi - \arcsin a$ (II мөчлөг). Учир нь $y = a$ шулуун нэгж тойргийг хоёр цэгт огтолно.</t>
         </is>
       </c>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>I мөчлөгт x = π/6.</t>
+          <t>Эхлээд тэгшитгэлийг шугаман тэгшитгэл шиг бодож $\sin x$-ийг ганцаарчил. Гарсан утгад харгалзах тусгай өнцгийг радианаар олоод, II мөчлөгийн шийдийг томьёогоор гарга.</t>
         </is>
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>II мөчлөгт x = π − π/6.</t>
+          <t>$\sin$-ийг хаяж $x$-ийг шууд тоогоор олох нь алдаа — эхлээд $\sin x$-ийн утгыг, дараа нь өнцгийг ол. Хоёр шийд хоёулаа $0 \le x &lt; 2\pi$ нөхцөлд орж, анхны тэгшитгэлийг хангаж байгааг шалга.</t>
         </is>
       </c>
       <c r="N184" s="2" t="inlineStr">
@@ -15150,17 +15150,17 @@
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>ctg α = cos α / sin α.</t>
+          <t>Котангенс: $\operatorname{ctg}\alpha = \frac{\cos\alpha}{\sin\alpha}$, $\sin\alpha \ne 0$ үед тодорхойлогдоно. Илэрхийллийг хялбарчлахдаа бүх функцийг синус, косинусаар илэрхийлэх нь үндсэн арга.</t>
         </is>
       </c>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>sin α · cos α / sin α.</t>
+          <t>Котангенсыг тодорхойлолтоор нь бутархай болгон орлуул. Дараа нь үржвэрийг нэг бутархай болгож, хүртвэр ба хуваарьт байгаа ижил үржигдэхүүнийг хураа.</t>
         </is>
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>sin α хураагдана.</t>
+          <t>$\sin\alpha \cdot \operatorname{ctg}\alpha$-г $1$ гэх нь алдаа — $\operatorname{ctg}\alpha$ нь $\sin\alpha$-ийн биш, $\operatorname{tg}\alpha$-ийн урвуу. Шалгах: $\alpha = 60^\circ$ орлуулж анхны ба хялбарчилсан илэрхийллийн утгыг харьцуул.</t>
         </is>
       </c>
       <c r="N185" s="2" t="inlineStr">
@@ -15230,17 +15230,17 @@
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>(1 − s)(1 + s) = 1 − s².</t>
+          <t>Квадратуудын ялгаврын томьёо: $(a-b)(a+b) = a^2 - b^2$. Үндсэн адилтгал $\sin^2\alpha + \cos^2\alpha = 1$-ээс $1 - \sin^2\alpha$ ба $1 - \cos^2\alpha$ хэлбэрийн илэрхийллийг нэг гишүүнээр сольж болно.</t>
         </is>
       </c>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>1 − sin²α.</t>
+          <t>$a = 1$, $b = \sin\alpha$ гэж үзэж үржвэрийг квадратуудын ялгавар болгон бич. Гарсан илэрхийллийг үндсэн адилтгалаас илэрхийлсэн хэлбэртэй тулгаж нэг гишүүн болго.</t>
         </is>
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>Үндсэн адилтгалаар cos²α.</t>
+          <t>Адилтгал квадратуудын тухай тул хувиргалтын явцад квадратыг хаяж болохгүй. Шалгах: $\alpha = 30^\circ$ орлуулж анхны ба хялбарчилсан илэрхийллийн утгыг харьцуул.</t>
         </is>
       </c>
       <c r="N186" s="2" t="inlineStr">
@@ -15310,17 +15310,17 @@
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>390° = 360° + 30°.</t>
+          <t>Синус үелэх функц, үе нь $360^\circ$ ($2\pi$): ямар ч бүхэл $k$-д $\sin(\alpha + 360^\circ k) = \sin\alpha$. Бүтэн эргэлтээс их өнцгийг $[0^\circ; 360^\circ)$ муж руу шилжүүлэхэд хэрэглэнэ.</t>
         </is>
       </c>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>sin үелэх чанартай: үе нь 360°.</t>
+          <t>$390^\circ$-аас бүтэн эргэлтийг хасаж $[0^\circ; 360^\circ)$ мужид орох өнцгийг ол. Дараа нь тэр өнцгийн синусыг тусгай өнцгийн утгаас ав.</t>
         </is>
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>sin 30°.</t>
+          <t>$180^\circ$ хасах нь алдаа — синусын үе $180^\circ$ биш, $180^\circ$ нэмэхэд синусын тэмдэг эсрэгээр солигдоно. Шалгах: $390^\circ$-ын цэг нэгж тойргийн I мөчлөгт оршдог тул хариу эерэг байх ёстой.</t>
         </is>
       </c>
       <c r="N187" s="2" t="inlineStr">
@@ -15390,17 +15390,17 @@
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Нийт хэдэн үр дүн боломжтой вэ?</t>
+          <t>Сонгодог магадлал: бүх үр дүн адил боломжтой үед $P(A) = \frac{m}{n}$, энд $n$ — бүх боломжит үр дүнгийн тоо, $m$ — $A$ үзэгдэлд таатай үр дүнгийн тоо. Магадлал үргэлж $0 \le P(A) \le 1$ байна.</t>
         </is>
       </c>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>2 (сүлд, тоо). Таатай нь 1.</t>
+          <t>Зоосны боломжит үр дүнгүүдийг жагсааж $n$-ийг, сүлд буух таатай үр дүнг тоолж $m$-ийг ол. Зоос тэгш хэмтэй тул үр дүнгүүд адил боломжтой гэж үзнэ.</t>
         </is>
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>1/2.</t>
+          <t>Магадлал $1$ гэдэг нь заавал биелэх үзэгдэл — сүлд буух нь заавал биш. Шалгах: сүлд ба тоо буух магадлалын нийлбэр $1$ болох ёстой.</t>
         </is>
       </c>
       <c r="N188" s="2" t="inlineStr">
@@ -15470,17 +15470,17 @@
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>5-аас их тоо шоон дээр хэд байна?</t>
+          <t>Сонгодог магадлал: бүх үр дүн адил боломжтой үед $P(A) = \frac{m}{n}$, энд $n$ — бүх боломжит үр дүнгийн тоо, $m$ — $A$ үзэгдэлд таатай үр дүнгийн тоо. Магадлал үргэлж $0 \le P(A) \le 1$ байна.</t>
         </is>
       </c>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>Зөвхөн 6.</t>
+          <t>Шооны бүх үр дүнгээс $n$-ийг ол. Тэдгээрээс $5$-аас хатуу их тоонуудыг сонгож $m$-ийг тоолоод $\frac{m}{n}$-ийг бич.</t>
         </is>
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>1/6.</t>
+          <t>«$5$-аас их» гэдэг нь $x &gt; 5$ — $5$ өөрөө орохгүй, $x \ge 5$-тай андуурах нь алдаа. Шалгах: эсрэг үзэгдэл ($x \le 5$)-ийн магадлалтай нийлбэр нь $1$ байх ёстой.</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr">
@@ -15550,17 +15550,17 @@
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>3, 6, 9 — хэдэн тоо вэ?</t>
+          <t>Сонгодог магадлал $P(A) = \frac{m}{n}$. Бүхэл тоо $a$ нь $b$-д хуваагдана гэдэг нь $a = bk$ байх бүхэл $k$ оршино гэсэн үг.</t>
         </is>
       </c>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>3 ширхэг, нийт 10.</t>
+          <t>Сонгох боломжтой бүх тоонуудын тоо $n$-ийг ол. $3$-ын үржвэрүүдийг $10$-аас хэтрүүлэхгүйгээр жагсааж $m$-ийг тоол.</t>
         </is>
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>3/10.</t>
+          <t>«$1$-ээс $10$ хүртэл» гэдэгт хоёр зах хоёулаа орно — хуваарьт $10$-аас цөөн тоо авах нь алдаа. Шалгах: таатай тоонуудыг $3$-т хувааж үлдэгдэлгүй эсэхийг нэг бүрчлэн тулга.</t>
         </is>
       </c>
       <c r="N190" s="2" t="inlineStr">
@@ -15630,17 +15630,17 @@
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Үзэгдэл ба эсрэг үзэгдлийн магадлалын нийлбэр хэд вэ?</t>
+          <t>$\bar A$ — $A$ биелэхгүй байх үзэгдэл; $A$ ба $\bar A$ үл нийцэх бөгөөд нийлээд бүх огторгуйг бүрдүүлдэг. Иймээс $P(A) + P(\bar A) = 1$.</t>
         </is>
       </c>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>Энэ тэнцэтгэлээс $P(\bar A)$-г илэрхийлж, өгсөн $P(A)$-г орлуул. Аравтын бутархайг хасахдаа оронгоо тулгаж бич.</t>
         </is>
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>1 − 0,3.</t>
+          <t>Эсрэг үзэгдлийн магадлалыг анхныхтай ижил гэх нь алдаа. Шалгах: хоёр магадлалын нийлбэр яг $1$, мөн хоёулаа $0$ ба $1$-ийн хооронд байх ёстой.</t>
         </is>
       </c>
       <c r="N191" s="2" t="inlineStr">
@@ -15710,17 +15710,17 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Нийт бөмбөг 4 + 6.</t>
+          <t>Сонгодог магадлал: бүх үр дүн адил боломжтой үед $P(A) = \frac{m}{n}$, энд $n$ — бүх боломжит үр дүнгийн тоо, $m$ — $A$ үзэгдэлд таатай үр дүнгийн тоо. Магадлал үргэлж $0 \le P(A) \le 1$ байна.</t>
         </is>
       </c>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>Таатай нь 6.</t>
+          <t>Нийт бөмбөг (цагаан ба хар нийлээд) нь $n$, хар бөмбөг нь $m$. $\frac{m}{n}$ бутархайг хүртвэр, хуваарийн хамгийн их ерөнхий хуваагчаар хураа.</t>
         </is>
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>6/10-ыг хураа.</t>
+          <t>Хар бөмбөгийг цагаантай харьцуулах нь алдаа — магадлал $1$-ээс хэтрэхгүй тул хуваарь нь нийт тоо. Хураасан бутархай цаашид хураагдахгүй, анхныхтайгаа тэнцүү эсэхийг шалга.</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
@@ -15790,17 +15790,17 @@
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Эхний байранд 4 сонголт, дараагийнд 3, ...</t>
+          <t>$n$ ялгаатай элементийг бүгдийг нь дараалуулан байрлуулах арга бүрийг сэлгэмэл гэнэ, тоо нь $P_n = n! = 1 \cdot 2 \cdot \ldots \cdot n$. Үржүүлэх дүрмээс гарна: байр бүрт өмнөх байрнаасаа нэгээр цөөн сонголт үлдэнэ.</t>
         </is>
       </c>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>4·3·2·1.</t>
+          <t>Тавиурын байруудыг зүүнээс баруун тийш дараалан бөглөнө гэж үзээд байр бүрт хэдэн ном сонгох боломжтойг тоол. Сонголтын тоонуудыг үржүүлж факториалыг бод.</t>
         </is>
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>24.</t>
+          <t>$4 \cdot 4$ гэх нь алдаа — нэг ном хоёр байрт тавигдахгүй. Шалгах: эхний байрт тодорхой ном тавихад үлдсэн номуудыг $3!$ янзаар өрнө; ийм тохиолдлын тоогоор үржүүлж тулга.</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
@@ -15870,17 +15870,17 @@
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>Ахлагчид 6 сонголт.</t>
+          <t>Байрлуулал: $n$ элементээс $k$-г дараалал харгалзан сонгох тоо $A_n^k = \frac{n!}{(n-k)!} = n(n-1)\cdots(n-k+1)$. Ахлагч ба орлогч ялгаатай алба тул хэн аль албанд орох нь чухал.</t>
         </is>
       </c>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>Орлогчид үлдсэн 5.</t>
+          <t>Үржүүлэх дүрмээр бод: эхлээд ахлагчийг сонгох боломжийн тоог, дараа нь үлдсэн сурагчдаас орлогчийг сонгох боломжийн тоог тодорхойл. Хоёр тоог үржүүл.</t>
         </is>
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>6·5.</t>
+          <t>$C_6^2$ хэрэглэх нь алдаа — «А ахлагч, Б орлогч» ба «Б ахлагч, А орлогч» нь өөр хуваарилалт. Шалгах: $A_n^k = C_n^k \cdot k!$ холбоогоор хоёр аргаар бодож тулга.</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -15950,17 +15950,17 @@
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Дараалал чухал биш.</t>
+          <t>Хэсэглэл: $n$ элементээс $k$-г дараалал харгалзахгүй сонгох тоо $C_n^k = \frac{n!}{k!\,(n-k)!}$. Өнгөний хос сонгоход аль нь эхэлж сонгогдсон нь хамаагүй.</t>
         </is>
       </c>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>C(5,2) = 5!/(2!·3!).</t>
+          <t>Томьёонд $n$, $k$-г орлуулж, хүртвэр ба хуваарьт давтагдаж буй факториалыг хураа. Үлдсэн үржвэр ба хуваагчийг бод.</t>
         </is>
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>Байрлуулал шиг $5 \cdot 4$ гэж зогсох нь алдаа — {улаан, ногоон} ба {ногоон, улаан} нэг л сонголт тул давхар тоологдоно. Шалгах: өнгөнүүдийг $1$–$5$ гэж дугаарлаад бүх хосыг жагсааж тоол.</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
@@ -16030,17 +16030,17 @@
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Цамц бүрт хэдэн өмд тохирох вэ?</t>
+          <t>Үржүүлэх дүрэм: эхний сонголтыг $m$ янзаар, тэр бүрд хоёр дахийг $n$ янзаар хийж болох бол хоёуланг нь $m \cdot n$ янзаар хийнэ. Цамц «ба» өмд хоёуланг нь сонгох тул энэ дүрэм тохирно.</t>
         </is>
       </c>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>3 цамц · 4 өмд.</t>
+          <t>Цамц бүрийг нэг мөр, өмд бүрийг нэг багана болгон хүснэгт зурвал нүд бүр нэг хувцаслалт болно. Мөр ба баганын тоог тодорхойлоод нүдний тоог ол.</t>
         </is>
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>12.</t>
+          <t>Нэмэх дүрэм ($m + n$) нь «эсвэл» сонголтод — зөвхөн нэг хувцас сонгох үед хэрэглэгдэнэ. Шалгах: нэг цамцанд тохирох бүх өмдийг жагсаагаад цамц бүрээр давтаж тоол.</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
@@ -16110,17 +16110,17 @@
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Хоёр шоо бие биенээсээ хамаарахгүй.</t>
+          <t>$A$ ба $B$ бие даасан бол (нэг нь нөгөөгийнхөө магадлалд нөлөөлөхгүй) хоёулаа биелэх магадлал $P(A \cap B) = P(A) \cdot P(B)$. Хоёр шооны үр дүн бие биеэсээ хамааралгүй.</t>
         </is>
       </c>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>Бие даасан үзэгдлийн магадлалыг үржүүлнэ.</t>
+          <t>Эхлээд нэг шоонд $6$ буух магадлалыг сонгодог томьёогоор ол. Хоёр шоо тус бүрт ижил магадлалтай тул бие даасан үзэгдлийн үржвэрийн дүрмийг хэрэглэ.</t>
         </is>
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>(1/6)·(1/6).</t>
+          <t>Нэмэх нь алдаа — «ба» холбоонд үржүүлнэ, хоёулаа биелэх магадлал аль нэгийнхээс их байж болохгүй. Шалгах: үр дүнгийн огторгуйг эрэмбэлэгдсэн хосоор бичиж, таатай хосыг тоолох аргаар дахин бод.</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
@@ -16190,17 +16190,17 @@
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Нийт үр дүн 36.</t>
+          <t>Хоёр шооны үр дүнгийн огторгуй нь адил боломжтой $(a; b)$ эрэмбэлэгдсэн хосууд. «$10$-аас багагүй» гэдэг нь $a + b \ge 10$ — $10$ өөрөө орно.</t>
         </is>
       </c>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>Нийлбэр 10: (4,6),(5,5),(6,4); 11: 2 хос; 12: 1 хос.</t>
+          <t>Үржүүлэх дүрмээр нийт хосын тоог ол. Нийлбэр $10$, $11$, $12$ тус бүрийг өгөх бүх эрэмбэлэгдсэн хосыг жагсааж тоог нь нэмээд сонгодог томьёонд орлуул.</t>
         </is>
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>6/36.</t>
+          <t>Нийлбэрийн утга бүрийг нэг үр дүн гэж тоолох нь алдаа — $(4;6)$ ба $(6;4)$ өөр хос, харин $(5;5)$ ганц. Шалгах: $6 \times 6$ хүснэгт зурж нийлбэр нь $\ge 10$ нүднүүдийг тэмдэглэж тоол.</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -16270,17 +16270,17 @@
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Тэгш: 2, 4, 6. 3-т хуваагдах: 3, 6.</t>
+          <t>Нэмэх теорем: $P(A \cup B) = P(A) + P(B) - P(A \cap B)$. $A$ ба $B$ нийцтэй (зэрэг биелж болох) бол огтлолцлыг хасахгүй бол түүнийг хоёр удаа тоолно.</t>
         </is>
       </c>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>6 хоёр удаа тоологдохгүй.</t>
+          <t>Тэгш тоонуудын олонлог $A$, $3$-т хуваагдах тоонуудын олонлог $B$-г бичиж огтлолцлыг ол. Нэмэх теоремоор, эсвэл нэгдэл олонлогийн элементийг шууд тоолж магадлалыг ол.</t>
         </is>
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>{2, 3, 4, 6} → 4/6.</t>
+          <t>$P(A) + P(B)$-г шууд нэмэх нь алдаа — хоёр олонлогт зэрэг орсон тоо давхар тоологдоно. Хоёр аргаар (томьёо ба шууд тоолох) бодож, хариугаа хураагаад тулга.</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -16350,17 +16350,17 @@
       </c>
       <c r="K200" s="2" t="inlineStr">
         <is>
-          <t>Сүлд аль хаялтад буух вэ — 4 сонголт.</t>
+          <t>Бернуллийн томьёо: $n$ бие даасан туршилт бүрт үзэгдэл $p$ магадлалтай бол яг $k$ удаа биелэх магадлал $P_n(k) = C_n^k p^k (1-p)^{n-k}$. Зоосны хаялтууд бие биеэсээ хамааралгүй, $p = \frac{1}{2}$.</t>
         </is>
       </c>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>Тодорхой нэг дараалал: (1/2)⁴ = 1/16.</t>
+          <t>Сүлд аль хаялтад буухыг сонгох боломжийн тоог $C_4^1$-ээр ол. Тодорхой нэг дарааллын (жишээ нь СТТТ) магадлалыг хаялтуудын магадлалын үржвэрээр олоод хоёр тоог үржүүл.</t>
         </is>
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>4 · 1/16.</t>
+          <t>Ганц дарааллын магадлалыг хариу гэж бичих нь алдаа — сүлд дөрвөн хаялтын аль нэгэнд буух бүх хувилбарыг тооцно. Шалгах: нийт $2^4$ дарааллаас яг нэг сүлдтэйг жагсааж тоолоод харьцуул.</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -16430,17 +16430,17 @@
       </c>
       <c r="K201" s="2" t="inlineStr">
         <is>
-          <t>Эхний бөмбөг улаан: 3/5.</t>
+          <t>Үржвэрийн теорем: $P(A \cap B) = P(A) \cdot P(B \mid A)$, энд $P(B \mid A)$ нь $A$ биелсэн нөхцөл дэх $B$-ийн магадлал. Буцаалгүй сонголтод эхний авалт уутны бүрэлдэхүүнийг өөрчилдөг тул хоёр дахь магадлал өөрчлөгдөнө.</t>
         </is>
       </c>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>Хоёр дахь (нэг улаан гарсан): 2/4.</t>
+          <t>Эхний бөмбөг улаан байх магадлалыг анхны уутаар ол. Нэг улаан гарсны дараа уутанд нийт хэд, улаан хэд үлдэхийг тодорхойлж нөхцөлт магадлалыг ол, дараа нь хоёрыг үржүүлж хураа.</t>
         </is>
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>(3/5)·(2/4).</t>
+          <t>Хоёр удаа ижил магадлал үржүүлэх нь буцаасан сонголтын бодолт — энд бөмбөг буцаагдахгүй. Шалгах: хэсэглэлээр $\frac{C_3^2}{C_5^2}$ гэж бодоход ижил хариу гарах ёстой.</t>
         </is>
       </c>
       <c r="N201" s="2" t="inlineStr">
@@ -17103,7 +17103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17137,17 +17137,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>зэрэг</t>
+          <t>анхны утга</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Тоог өөрөөр нь хэд хэдэн удаа үржүүлэх үйлдэл. aⁿ гэвэл a-г n удаа үржүүлнэ.</t>
+          <t>Хувиар өөрчлөгдөхөөс өмнөх хэмжигдэхүүний утга; хувийн өөрчлөлт үргэлж анхны утгаас тооцогддог. Өөрчлөгдсөн утга $y$, өсөлт $p\%$ мэдэгдэж байвал анхны утга $x = \frac{y}{1 + \frac{p}{100}}$.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2³ = 2·2·2 = 8</t>
+          <t>10%-иар нэмэгдээд 550 болсон бол анхны утга $550 : 1{,}1 = 500$</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -17159,17 +17159,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>зэргийн илтгэгч</t>
+          <t>бутархай</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>aⁿ бичлэгт n нь хэдэн удаа үржүүлэхийг заана.</t>
+          <t>$b \ne 0$ үед $\frac{a}{b}$ хэлбэрийн тоо; $a$ нь хүртвэр, $b$ нь хуваарь бөгөөд $a$-г $b$-д хуваасан ногдворыг илэрхийлнэ. Үндсэн шинж чанар: $\frac{a}{b} = \frac{ak}{bk}$ ($k \ne 0$).</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>5² бичлэгт илтгэгч нь 2</t>
+          <t>$\frac{6}{8} = \frac{3}{4}$ — хүртвэр, хуваарийг 2-т хуваав</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -17181,17 +17181,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>сөрөг илтгэгч</t>
+          <t>бутархай илтгэгч</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>a^(−n) = 1/aⁿ. Сөрөг илтгэгч нь бутархайг урвуулна.</t>
+          <t>$a &gt; 0$, $m$ бүхэл, $n \ge 2$ натурал үед $a^{\frac{m}{n}} = \sqrt[n]{a^m} = \left(\sqrt[n]{a}\right)^m$. Илтгэгчийн хуваарь нь язгуурын зэрэг, хүртвэр нь зэргийн илтгэгч.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2^(−3) = 1/8</t>
+          <t>$16^{\frac{3}{4}} = \left(\sqrt[4]{16}\right)^3 = 2^3 = 8$</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -17203,17 +17203,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>бутархай илтгэгч</t>
+          <t>бутархайг үржүүлэх</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>a^(m/n) = ⁿ√(a^m). Хуваарь нь язгуурын зэрэг.</t>
+          <t>Бутархайг үржүүлэхэд хүртвэрийг хүртвэрээр, хуваарийг хуваариар үржүүлнэ: $\frac{a}{b} \cdot \frac{c}{d} = \frac{ac}{bd}$ ($b, d \ne 0$). Ерөнхий хуваарь шаардлагагүй, үржүүлэхээс өмнө хөндлөн хураах нь тооцоог хялбарчилна.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8^(1/3) = ∛8 = 2</t>
+          <t>$\frac{4}{5} \cdot \frac{15}{8} = \frac{1}{1} \cdot \frac{3}{2} = \frac{3}{2}$</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -17225,17 +17225,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>квадрат язгуур</t>
+          <t>ерөнхий хуваарь</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Квадрат нь өгөгдсөн тоотой тэнцэх сөрөг биш тоо.</t>
+          <t>Хэд хэдэн бутархайн хуваарь бүрт хуваагдах тоо (эсвэл илэрхийлэл); бутархайг нэмэх, хасахаас өмнө бүгдийг энэ хуваарьт шилжүүлнэ. Ихэвчлэн хуваариудын хамгийн бага ерөнхий хуваагдагчийг (ХБЕХ) авдаг.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>√25 = 5</t>
+          <t>$\frac{1}{6} + \frac{3}{8}$: ХБЕХ$(6, 8) = 24$, $\frac{4}{24} + \frac{9}{24}$</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -17247,17 +17247,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ерөнхий хуваарь</t>
+          <t>зэргийг задлах</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Хэд хэдэн бутархайн хуваарийн аль алинд нь хуваагдах тоо.</t>
+          <t>Тоо эсвэл суурийг анхны үржигдэхүүнүүдийн зэргийн үржвэр болгон бичих, эсвэл $(ab)^n = a^n b^n$ дүрмээр үржвэрийн зэргийг хүчин зүйлүүдийн зэрэгт хуваах. Ингэснээр ялгаатай суурьтай зэргүүдийг хурааж, харьцуулах боломжтой.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1/4 ба 1/6 → 12</t>
+          <t>$12^3 = (4 \cdot 3)^3 = 2^6 \cdot 3^3$</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -17269,577 +17269,3569 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>төсөөтэй гишүүн</t>
+          <t>зэргийг хуваах</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Үсэгтэй хэсэг нь яг ижил гишүүд. Зөвхөн тэдгээрийг нэмж болно.</t>
+          <t>Ижил суурьтай зэргийг хуваахад суурь хэвээр үлдэж, хуваагдагчийн илтгэгчээс хуваагчийн илтгэгчийг хасна: $a^m : a^n = a^{m-n}$ ($a \ne 0$). Ижил илтгэгчтэй үед $\frac{a^n}{b^n} = \left(\frac{a}{b}\right)^n$.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3x ба 5x төсөөтэй; 3x ба 3x² төсөөтэй биш</t>
+          <t>$\frac{5^7}{5^4} = 5^3 = 125$</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>үржигдэхүүнд задлах</t>
+          <t>зэргийн зэрэг</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Илэрхийллийг хэд хэдэн хүчин зүйлийн үржвэр хэлбэрт бичих.</t>
+          <t>Зэргийг дахин зэрэгт дэвшүүлэхэд илтгэгчүүд үржигдэнэ: $(a^m)^n = a^{mn}$. Үүнийг ижил суурьтай зэргийн үржвэрийн $a^m \cdot a^n = a^{m+n}$ (илтгэгч нэмэгдэх) дүрэмтэй андуурч болохгүй.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>x² − 9 = (x − 3)(x + 3)</t>
+          <t>$(3^2)^3 = 3^6 = 729$</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>квадратуудын ялгавар</t>
+          <t>зэргийн илтгэгч</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>a² − b² = (a − b)(a + b) томьёо.</t>
+          <t>$a^n$ бичлэгт суурийн баруун дээд талд бичигдэх $n$ тоо; натурал $n$ үед суурийг хэдэн удаа үржүүлэхийг заана. Илтгэгч нь тэг, сөрөг, бутархай тоо ч байж болно.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>x² − 16 = (x − 4)(x + 4)</t>
+          <t>$7^5$ бичлэгт илтгэгч нь 5, $2^{-3}$-т илтгэгч нь $-3$</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>үл мэдэгдэгч</t>
+          <t>зэргийн суурь</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Тэгшитгэлд олох ёстой утга, ихэвчлэн x.</t>
+          <t>$a^n$ бичлэгт давтан үржигдэж буй $a$ тоо (эсвэл илэрхийлэл). Сөрөг тоо, бутархай суурьтай зэргийг хаалтанд бичнэ: $(-2)^4 \ne -2^4$. Бутархай илтгэгчтэй зэрэгт суурь эерэг байх шаардлагатай.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2x = 6 → x = 3</t>
+          <t>$(-3)^2 = 9$ бичлэгт суурь нь $-3$</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>шилжүүлэх</t>
+          <t>зэрэг</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Гишүүнийг тэнцүүгийн нөгөө тал руу шилжүүлэхэд тэмдэг нь эсрэгээр солигдоно.</t>
+          <t>$a$ тооны натурал $n$ зэрэг $a^n$ нь $a$-г өөрөөр нь $n$ удаа үржүүлсэн үржвэр; $a^1 = a$, $a \ne 0$ үед $a^0 = 1$. Сөрөг ба бутархай илтгэгчтэй зэрэг нь энэ тодорхойлолтын өргөтгөл бөгөөд $a^m \cdot a^n = a^{m+n}$ зэрэг дүрмүүд хадгалагдана.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>x + 5 = 7 → x = 7 − 5</t>
+          <t>$3^4 = 3 \cdot 3 \cdot 3 \cdot 3 = 81$</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>тэгшитгэлийн систем</t>
+          <t>квадрат язгуур</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Нэгэн зэрэг биелэх ёстой хэд хэдэн тэгшитгэл.</t>
+          <t>$a \ge 0$ тооны арифметик квадрат язгуур $\sqrt{a}$ нь квадрат нь $a$-тай тэнцэх сөрөг биш тоо: $\sqrt{a} \ge 0$, $(\sqrt{a})^2 = a$. Сөрөг тооноос бодит квадрат язгуур гарахгүй, мөн $\sqrt{x^2} = |x|$.</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>x + y = 5, x − y = 1</t>
+          <t>$\sqrt{49} = 7$, учир нь $7 \ge 0$ ба $7^2 = 49$</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>квадрат тэгшитгэл</t>
+          <t>куб язгуур</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ax² + bx + c = 0 (a ≠ 0) хэлбэрийн тэгшитгэл.</t>
+          <t>$a$ тооны куб язгуур $\sqrt[3]{a}$ нь куб нь $a$-тай тэнцэх цорын ганц бодит тоо: $\left(\sqrt[3]{a}\right)^3 = a$. Дурын бодит $a$-д, тэр дундаа сөрөг тоонд тодорхойлогдох ба $\sqrt[3]{a} = a^{\frac{1}{3}}$ ($a \ge 0$).</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>x² − 5x + 6 = 0</t>
+          <t>$\sqrt[3]{64} = 4$, $\sqrt[3]{-27} = -3$</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>дискриминант</t>
+          <t>стандарт хэлбэр</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D = b² − 4ac. D &gt; 0 бол 2 язгуур, D = 0 бол 1, D &lt; 0 бол бодит язгуургүй.</t>
+          <t>Тоог $a \cdot 10^n$ хэлбэрт бичих бичлэг, энд $1 \le |a| &lt; 10$, $n$ бүхэл тоо. Маш их эсвэл маш бага тоог бичих, үржүүлэхэд $10^m \cdot 10^n = 10^{m+n}$ дүрмийг ашиглана.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>x² + 2x + 1: D = 0</t>
+          <t>$45000 = 4{,}5 \cdot 10^4$, $0{,}003 = 3 \cdot 10^{-3}$</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Виетийн теорем</t>
+          <t>сөрөг илтгэгч</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>x² + px + q = 0 тэгшитгэлийн язгуурууд: x₁ + x₂ = −p, x₁·x₂ = q.</t>
+          <t>$a \ne 0$ ба натурал $n$-ийн хувьд $a^{-n} = \frac{1}{a^n}$ гэж тодорхойлно. Сөрөг илтгэгч нь тоог урвуу тоо руу шилжүүлдэг — тэмдгийг нь өөрчлөхгүй; иймээс $\left(\frac{a}{b}\right)^{-n} = \left(\frac{b}{a}\right)^n$.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>x² − 5x + 6: 2 + 3 = 5, 2·3 = 6</t>
+          <t>$5^{-2} = \frac{1}{25}$, $\left(\frac{2}{3}\right)^{-1} = \frac{3}{2}$</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>язгуур (тэгшитгэлийн)</t>
+          <t>хуваарь</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Тэгшитгэлд орлуулахад үнэн тэнцэтгэл болгох утга.</t>
+          <t>$\frac{a}{b}$ бутархайн зураасын доорх $b$ тоо (эсвэл илэрхийлэл); бүхэл зүйлийг хэдэн тэнцүү хэсэгт хуваасныг заана. Хуваарь хэзээ ч тэгтэй тэнцэж болохгүй.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>x = 2 нь x² = 4-ийн язгуур</t>
+          <t>$\frac{5}{7}$-ийн хуваарь 7; $\frac{1}{x-2}$-т $x \ne 2$</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>тэнцэтгэл биш</t>
+          <t>хувь</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>&lt;, &gt;, ≤, ≥ тэмдгээр холбогдсон хоёр илэрхийлэл.</t>
+          <t>Тооны зуугийн нэг хэсэг: $p\% = \frac{p}{100}$. Тооны $p\%$ нь $x \cdot \frac{p}{100}$; $p\%$-иар нэмэгдвэл $x\left(1 + \frac{p}{100}\right)$, буурвал $x\left(1 - \frac{p}{100}\right)$ болно.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2x &gt; 6 → x &gt; 3</t>
+          <t>$80$-ын $15\%$ нь $80 \cdot 0{,}15 = 12$</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>модуль</t>
+          <t>язгуур</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Тооны тэгээс хүртэлх зай; үргэлж сөрөг биш.</t>
+          <t>$a$ тооны $n$ зэргийн язгуур $\sqrt[n]{a}$ нь $n$ зэрэг нь $a$-тай тэнцэх тоо: $\left(\sqrt[n]{a}\right)^n = a$. Тэгш $n$ үед $a \ge 0$ байх ба язгуур сөрөг биш, сондгой $n$ үед дурын бодит $a$-д тодорхойлогдоно.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>|−5| = 5</t>
+          <t>$\sqrt[4]{81} = 3$, $\sqrt[3]{-8} = -2$</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>интервалын арга</t>
+          <t>язгуураас гаргах</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Илэрхийллийн язгууруудаар тоон шулууныг хувааж, завсар бүрийн тэмдгийг шалгах арга.</t>
+          <t>Язгуур доорх илэрхийллийн бүтэн квадрат (бүтэн $n$ зэрэг) үржигдэхүүнийг язгуурын өмнө гаргах хувиргалт: $a, b \ge 0$ үед $\sqrt{a^2 b} = a\sqrt{b}$. Язгуур доор аль болох бага тоо үлдээж, төсөөтэй язгууруудыг нэгтгэхэд хэрэглэнэ.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>(x − 1)(x − 3) &lt; 0 → 1 &lt; x &lt; 3</t>
+          <t>$\sqrt{72} = \sqrt{36 \cdot 2} = 6\sqrt{2}$</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>функц</t>
+          <t>язгуурыг үржүүлэх</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>x-ийн утга бүрт y-ийн ганц утга харгалзуулах дүрэм.</t>
+          <t>Ижил зэргийн язгуурыг үржүүлэхэд язгуур доорх илэрхийллүүдийг үржүүлнэ: $\sqrt[n]{a} \cdot \sqrt[n]{b} = \sqrt[n]{ab}$ ($a, b \ge 0$). Энэ нь нэмэхэд хүчингүй: $\sqrt{a} + \sqrt{b} \ne \sqrt{a+b}$.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>f(x) = 2x + 1</t>
+          <t>$\sqrt{2} \cdot \sqrt{8} = \sqrt{16} = 4$</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>тодорхойлогдох муж</t>
+          <t>үйлдлийн дараалал</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Функц утгатай байх x-ийн бүх утгын олонлог.</t>
+          <t>Илэрхийллийн утгыг бодох тогтсон дараалал: хаалт → зэрэг ба язгуур → үржих, хуваах (зүүнээс баруун) → нэмэх, хасах (зүүнээс баруун). Хаалт нь энэ дарааллыг өөрчлөх цорын ганц арга.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>√x-ийн муж: x ≥ 0</t>
+          <t>$10 - 2 \cdot 3^2 = 10 - 18 = -8$</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>өнцгийн коэффициент</t>
+          <t>бүлэглэх арга</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>y = kx + b шулууны k; шулуун хэр огцом өгсөж/уруудаж байгааг заана.</t>
+          <t>Олон гишүүнтийн гишүүдийг ерөнхий үржигдэхүүнтэй бүлгүүдэд хуваан, бүлэг бүрээс үржигдэхүүн гаргах замаар задлах арга. Бүлгүүдэд ижил хаалт үүсвэл $ac + bc = (a + b)c$ дүрмээр түүнийг гаргаж задлалыг гүйцээнэ.</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>y = 3x − 1 → k = 3</t>
+          <t>$ax + ay + 2x + 2y = a(x+y) + 2(x+y) = (x+y)(a+2)$</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>парабол</t>
+          <t>бүтэн квадрат ялгах</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Квадрат функцийн график. a &gt; 0 бол дээшээ, a &lt; 0 бол доошоо харна.</t>
+          <t>$x^2 + px + q$ гурван гишүүнтийг $\left(x + \frac{p}{2}\right)^2 + q - \frac{p^2}{4}$ хэлбэрт хувиргах арга. Квадрат тэгшитгэл бодох, хамгийн бага (их) утга олох, параболын оройг тодорхойлоход хэрэглэнэ.</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>y = x²</t>
+          <t>$x^2 + 4x + 7 = (x + 2)^2 + 3$</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>логарифм</t>
+          <t>ерөнхий үржигдэхүүн</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>log_a b = c гэдэг нь a^c = b. 'Сууриа хэдэн зэрэгт дэвшүүлбэл b болох вэ?'</t>
+          <t>Олон гишүүнтийн бүх гишүүнд үржигдэхүүн болж орсон тоо эсвэл илэрхийлэл; хаалтын өмнө гаргахдаа $ab + ac = a(b + c)$ гэж бичнэ. Хамгийн их ерөнхий үржигдэхүүн нь коэффициентуудын ХИЕХ ба хувьсагч бүрийн хамгийн бага зэргийн үржвэр.</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>log₂8 = 3, учир нь 2³ = 8</t>
+          <t>$8x^3 - 12x^2 = 4x^2(2x - 3)$</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>логарифмын суурь</t>
+          <t>илэрхийллийн утга</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>log_a b бичлэгт a; a &gt; 0, a ≠ 1.</t>
+          <t>Хувьсагчийн оронд өгөгдсөн тоог орлуулж, үйлдлийн дарааллаар бодсоны дүнд гарах тоо. Утга нь зөвхөн тодорхойлогдох мужид (жишээ нь хуваарь тэг биш үед) оршино.</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>log₃9 бичлэгт суурь 3</t>
+          <t>$x = 3$ үед $2x^2 - x = 18 - 3 = 15$</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>синус</t>
+          <t>квадрат гурван гишүүнт</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Тэгш өнцөгт гурвалжинд хурц өнцгийн эсрэг катетыг гипотенузад харьцуулсан харьцаа.</t>
+          <t>$ax^2 + bx + c$ ($a \ne 0$) хэлбэрийн олон гишүүнт; $a$, $b$, $c$ нь коэффициентууд, $c$ нь сул гишүүн. $D = b^2 - 4ac \ge 0$ үед $a(x - x_1)(x - x_2)$ хэлбэрт задарна, энд $x_1$, $x_2$ нь түүний язгуурууд.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>sin 30° = 1/2</t>
+          <t>$x^2 - x - 6 = (x - 3)(x + 2)$</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>косинус</t>
+          <t>квадратуудын ялгавар</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Хурц өнцгийн хэвтээ (налсан) катетыг гипотенузад харьцуулсан харьцаа.</t>
+          <t>Хоёр илэрхийллийн квадратуудын ялгаврын томьёо: $a^2 - b^2 = (a - b)(a + b)$. Үржигдэхүүнд задлах болон тооцоог хялбарчлахад хэрэглэнэ; квадратуудын нийлбэр $a^2 + b^2$ бодит үржигдэхүүнд ингэж задрахгүй.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>cos 60° = 1/2</t>
+          <t>$9y^2 - 1 = (3y - 1)(3y + 1)$</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>тригонометрийн үндсэн адилтгал</t>
+          <t>коэффициент</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>sin²α + cos²α = 1 нь ямар ч α-д биелнэ.</t>
+          <t>Гишүүний үсэгтэй хэсгийн өмнөх тоон үржигдэхүүн. Тоо бичигдээгүй бол коэффициент нь 1, ганц хасах тэмдэгтэй бол $-1$; сул гишүүн нь хувьсагчгүй гишүүн.</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>sin α = 0.6 → cos α = 0.8</t>
+          <t>$-7x^2y$-ийн коэффициент $-7$; $x$-ийн коэффициент 1</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>магадлал</t>
+          <t>нийлбэрийн квадрат</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Таатай үр дүнгийн тоог нийт боломжит үр дүнгийн тоонд харьцуулсан харьцаа (0-ээс 1).</t>
+          <t>Хоёр илэрхийллийн нийлбэрийн квадратын томьёо: $(a+b)^2 = a^2 + 2ab + b^2$. Дунд гишүүн $2ab$ нь давхар үржвэр бөгөөд $(a+b)^2 \ne a^2 + b^2$.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Шоо: P(6) = 1/6</t>
+          <t>$(y + 5)^2 = y^2 + 10y + 25$</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>сэлгэмэл</t>
+          <t>нийлбэрийн куб</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>n элементийг бүгдийг нь дараалуулан байрлуулах арга, n! ширхэг.</t>
+          <t>Хоёр илэрхийллийн нийлбэрийн кубын томьёо: $(a+b)^3 = a^3 + 3a^2 b + 3ab^2 + b^3$. Коэффициентууд 1, 3, 3, 1 бөгөөд $(a+b)^3 \ne a^3 + b^3$.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3 ном: 3! = 6 янз</t>
+          <t>$(y + 1)^3 = y^3 + 3y^2 + 3y + 1$</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>хэсэглэл</t>
+          <t>орлуулах</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>n элементээс k-г дараалал харгалзахгүй сонгох тоо: C(n,k) = n!/(k!(n−k)!).</t>
+          <t>Илэрхийлэл дэх хувьсагчийг өгөгдсөн тоо эсвэл өөр илэрхийллээр солих үйлдэл. Сөрөг тоо, нийлбэрийг орлуулахдаа заавал хаалтанд хийж, дараа нь үйлдлийн дарааллаар бодно.</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>C(5,2) = 10</t>
+          <t>$x = -1$-ийг $x^2 + 4x$-д: $(-1)^2 + 4 \cdot (-1) = -3$</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>рационал илэрхийлэл</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Олон гишүүнтүүдийн ногдвор $\frac{P(x)}{Q(x)}$ хэлбэрийн илэрхийлэл. Хуваарийг тэг болгох утгууд тодорхойлогдох мужид орохгүй; хураах, нэмэх зэрэг үйлдлийг энгийн бутархайн дүрмээр гүйцэтгэнэ.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{x+1}{x^2 - 4}$, тодорхойлогдох муж: $x \ne \pm 2$</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>сөрөг тоо</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Тэгээс бага бодит тоо; тоон шулуун дээр тэгээс зүүн талд байрлана. Тэмдгийн дүрэм: хоёр сөрөг тооны үржвэр эерэг, сөрөг тооны тэгш зэрэг эерэг, сондгой зэрэг сөрөг; $(-a)^2 \ne -a^2$.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>$(-3)^2 = 9$, харин $-3^2 = -9$; $(-2)^3 = -8$</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>товчилсон үржвэрийн томьёо</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Олон гишүүнтүүдийн түгээмэл үржвэрийг шууд бичих адилтгалууд: $(a \pm b)^2 = a^2 \pm 2ab + b^2$, $(a-b)(a+b) = a^2 - b^2$, $(a \pm b)^3 = a^3 \pm 3a^2b + 3ab^2 \pm b^3$. Зүүнээс баруун тийш хэрэглэвэл хаалт задлах, эсрэгээр хэрэглэвэл үржигдэхүүнд задлах болно.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>$(m - 2)(m + 2) = m^2 - 4$</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>төсөөтэй гишүүн</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Үсэгтэй хэсэг нь (хувьсагчид ба тэдгээрийн илтгэгч) яг ижил, зөвхөн коэффициентоороо ялгаатай гишүүд. Зөвхөн төсөөтэй гишүүдийг $ma + na = (m+n)a$ хуулиар нэгтгэж болно.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>$5xy$ ба $-2xy$ төсөөтэй; $3x$ ба $3x^2$ төсөөтэй биш</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>хаалт задлах</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Хаалттай илэрхийллийг хуваарилах хууль $a(b + c) = ab + ac$ болон товчилсон үржвэрийн томьёогоор хаалтгүй олон гишүүнт болгох хувиргалт. Хаалтын өмнөх үржигдэхүүн доторх гишүүн бүрийг тэмдэгтэй нь үржүүлнэ.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>$-2(x - 3) = -2x + 6$</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>хасах тэмдэг хаалтын өмнө</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Хаалтын өмнөх хасах тэмдэг нь хаалтыг $-1$-ээр үржүүлж буйтай адил: $-(a - b + c) = -a + b - c$. Хаалт задлахад доторх бүх гишүүний тэмдэг эсрэгээр солигдоно.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>$-(2x - 7) = -2x + 7$</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>хураах</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Бутархайн хүртвэр, хуваарийг ижил тэгээс ялгаатай ерөнхий үржигдэхүүнд хуваах хувиргалт: $\frac{ac}{bc} = \frac{a}{b}$ ($c \ne 0$). Зөвхөн үржигдэхүүнийг хураана — нэмэгдэхүүнийг хурааж болохгүй, тиймээс эхлээд үржигдэхүүнд задална.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{3x}{6x^2} = \frac{1}{2x}$ ($x \ne 0$)</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ялгаврын квадрат</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр илэрхийллийн ялгаврын квадратын томьёо: $(a-b)^2 = a^2 - 2ab + b^2$. Дунд гишүүн $-2ab$ заавал байх бөгөөд $b^2$ гишүүн үргэлж эерэг тэмдэгтэй.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>$(3y - 2)^2 = 9y^2 - 12y + 4$</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>үржигдэхүүнд задлах</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Олон гишүүнт (эсвэл тоо)-ийг хэд хэдэн хүчин зүйлийн үржвэр хэлбэрт бичих хувиргалт. Гол аргууд: ерөнхий үржигдэхүүнийг гаргах, бүлэглэх, товчилсон үржвэрийн томьёо хэрэглэх; үр дүнг буцааж үржүүлэхэд анхны илэрхийлэл гарна.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 5x = x(x - 5)$, $a^2 - 1 = (a-1)(a+1)$</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>аравтын бутархай</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Хуваарь нь $10^n$ байх бутархайг таслалтай бичих хэлбэр. Аравтын бутархайтай тэгшитгэлийг хоёр талыг $10$, $100$ эсвэл тохирох тоогоор үржүүлж бүхэл коэффициенттэй болгож болно.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>$0{,}5x = 1{,}5 \Rightarrow 5x = 15$</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>дараалсан тоо</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Бие биенээсээ ижил алхмаар ялгаатай, дараалан ирэх бүхэл тоонууд. Дараалсан натурал тоонуудыг $n,\ n+1,\ n+2, \dots$, дараалсан тэгш (сондгой) тоонуудыг $n,\ n+2,\ n+4, \dots$ гэж бичнэ.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>$14, 15, 16$ — дараалсан натурал тоо</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>зам</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Хөдөлгөөний явцад биеийн туулсан зайн урт. Жигд хөдөлгөөнд $s = v \cdot t$; хэд хэдэн хэсгээс тогтвол нийт зам нь хэсгүүдийн замын нийлбэр.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>$80$ км/ц хурдтай $3$ цаг: $s = 80 \cdot 3 = 240$ км</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>нэмэх арга</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлийн системийг бодох арга: тэгшитгэлүүдийг шаардлагатай бол тоогоор үржүүлж нэг хувьсагчийн коэффициентуудыг эсрэг тоо болгоод гишүүнчлэн нэмнэ. Тэр хувьсагч устаж, нэг хувьсагчтай тэгшитгэл үлдэнэ.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>$x + y = 7$, $x - y = 1$ нэмбэл $2x = 8$</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>орлуулах арга</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлийн системийг бодох арга: нэг тэгшитгэлээс нэг хувьсагчийг нөгөөгөөр нь илэрхийлээд, үлдсэн тэгшитгэлд орлуулна. Нэг хувьсагчтай тэгшитгэл гарч, түүнийг бодоод буцаан орлуулж нөгөө хувьсагчийг олно.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>$y = x + 1$, $x + y = 5$ $\Rightarrow x + (x + 1) = 5$</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>пропорц</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр харьцааны тэнцүү: $\frac{a}{b} = \frac{c}{d}$ ($b, d \ne 0$). Үндсэн чанар: хөндлөн (захын ба дундын) гишүүдийн үржвэрүүд тэнцүү, $ad = bc$.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{3}{4} = \frac{9}{12}$, учир нь $3 \cdot 12 = 4 \cdot 9$</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>сөрөг коэффициент</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Хувьсагчийн өмнөх тоон үржигдэхүүн сөрөг байх тохиолдол. Ийм тэгшитгэлийг бодохдоо хоёр талыг сөрөг коэффициентод хуваахад тэмдгийн дүрмийг баримтална: сөрөгийг сөрөгт хуваавал эерэг.</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>$-2x = -6$: $x$-ийн коэффициент $-2$</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч агуулсан, хоёр илэрхийллийн тэнцүүг илэрхийлсэн тэнцэтгэл. Тэгшитгэлийг бодно гэдэг нь түүний бүх язгуурыг олох эсвэл язгуургүйг батлах явдал. Ижил шийдтэй тэгшитгэлүүдийг тэнцүү чанартай гэнэ.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>$3x - 7 = 2x + 1$ — нэг үл мэдэгдэгчтэй шугаман тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>тэгшитгэл зохиох</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Бодлогын нөхцөлд байгаа хэмжигдэхүүн хоорондын тэнцүү хамаарлыг үл мэдэгдэгч ашиглан математик тэнцэтгэлээр илэрхийлэх. Нэг хэмжигдэхүүнийг $x$ гээд бусдыг нь $x$-ээр илэрхийлж, тэнцүү хоёр илэрхийллийг олно.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Үзэг $x$, дэвтэр $x + 300$; 2 дэвтэр, 3 үзэг 3600: $2(x + 300) + 3x = 3600$</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>тэгшитгэлийн систем</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Нэгэн зэрэг биелэх ёстой хэд хэдэн тэгшитгэл; ихэвчлэн их хаалтаар бичнэ. Системийн шийд нь бүх тэгшитгэлийг зэрэг хангах хувьсагчдын утгын олонлог (жишээ нь $(x; y)$ хос).</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>$\begin{cases} x + y = 5 \\ x - y = 1 \end{cases}$ шийд нь $(3; 2)$</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>хугацаа</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Хөдөлгөөн (үйл явц) үргэлжлэх хугацааны урт; жигд хөдөлгөөнд $t = \frac{s}{v}$. Хурдны нэгжтэй нийцүүлж (цаг, секунд) илэрхийлнэ.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>$150$ км-ийг $50$ км/ц хурдтай: $t = 3$ цаг</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>хурд</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Хөдөлж буй биеийн нэгж хугацаанд туулах зам; жигд хөдөлгөөнд $v = \frac{s}{t}$. Нэгж нь км/ц, м/с гэх мэт; бодлогод бүх хэмжигдэхүүнийг ижил нэгжээр илэрхийлэх ёстой.</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>$120$ км-ийг $2$ цагт туулбал $v = 60$ км/ц</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>хөндлөн үржүүлэх</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{a}{b} = \frac{c}{d}$ ($b, d \ne 0$) пропорцыг $ad = bc$ хэлбэрт шилжүүлэх хувиргалт. Энэ нь хоёр талыг $bd$-ээр үржүүлсэнтэй тэнцүү бөгөөд зөвхөн хоёр бутархайн тэнцүүд хэрэглэгдэнэ.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{x}{3} = \frac{4}{6} \Rightarrow 6x = 12$</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>шилжүүлэх</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлийн гишүүнийг тэнцүүгийн нэг талаас нөгөө тал руу эсрэг тэмдэгтэйгээр зөөх хувиргалт. Хоёр талд ижил тоо нэмэх (хасах)-тай адил тул шийдийг өөрчлөхгүй: $a + b = c \iff a = c - b$.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>$x + 5 = 7 \Rightarrow x = 7 - 5$</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>үгэн бодлого</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Нөхцөл нь үгээр өгөгдсөн, математик загвар (тэгшитгэл, систем) зохиож бодох бодлого. Үе шат: үл мэдэгдэгчийг сонгох, бусад хэмжигдэхүүнийг түүгээр илэрхийлэх, тэгшитгэл зохиож бодох, хариуг нөхцөлтэй тулгах.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>«Нэг тоо нөгөөгөөсөө 2-оор их, нийлбэр нь 10» $\Rightarrow x + (x + 2) = 10$</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>үл мэдэгдэгч</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлд утга нь тодорхойгүй, олох шаардлагатай хэмжигдэхүүн; ихэвчлэн $x$, $y$, $z$ үсгээр тэмдэглэнэ. Тэгшитгэлийг бодох нь үл мэдэгдэгчийн тэнцэтгэлийг үнэн болгох бүх утгыг олох явдал.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>$2x = 6$-д $x$ үл мэдэгдэгч, $x = 3$ үед тэнцэтгэл үнэн</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Виетийн теорем</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 + px + q = 0$ тэгшитгэл $x_1$, $x_2$ язгууртай бол $x_1 + x_2 = -p$, $x_1 x_2 = q$. Ерөнхий $ax^2 + bx + c = 0$-д $x_1 + x_2 = -\frac{b}{a}$, $x_1 x_2 = \frac{c}{a}$. Урвуу теоремоор язгуурыг таамаглан олж болно.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 5x + 6 = 0$: $2 + 3 = 5$, $2 \cdot 3 = 6$ — язгуурууд $2$ ба $3$</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>биквадрат тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>$ax^4 + bx^2 + c = 0$ ($a \ne 0$) хэлбэрийн тэгшитгэл. $t = x^2$ ($t \ge 0$) орлуулгаар квадрат тэгшитгэлд шилжүүлж бодно; $t$-ийн эерэг язгуур бүр $x = \pm\sqrt{t}$ хоёр язгуур өгнө.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>$x^4 - 10x^2 + 9 = 0$: $t^2 - 10t + 9 = 0$</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>давхар язгуур</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Квадрат тэгшитгэлийн $D = 0$ үеийн давхацсан хоёр язгуур: $x_1 = x_2 = -\frac{b}{2a}$. Энэ үед $ax^2 + bx + c = a(x - x_0)^2$ бөгөөд парабол $Ox$ тэнхлэгт шүргэнэ.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 4x + 4 = (x - 2)^2 = 0$: давхар язгуур $x = 2$</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>дискриминант</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>$ax^2+bx+c=0$ ($a \ne 0$) квадрат тэгшитгэлийн $D = b^2 - 4ac$ илэрхийлэл. Бодит язгуурын тоог тодорхойлно: $D&gt;0$ бол хоёр ялгаатай, $D=0$ бол нэг давхар, $D&lt;0$ бол бодит язгуургүй.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 + 2x + 1 = 0$: $D = 4 - 4 = 0$ — давхар язгууртай</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>иррационал язгуур</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Иррационал тоо болох тэгшитгэлийн язгуур, өөрөөр хэлбэл $\frac{p}{q}$ бутархайгаар илэрхийлэгдэхгүй язгуур. Бүхэл коэффициенттэй квадрат тэгшитгэлийн $D &gt; 0$ нь бүтэн квадрат биш үед гарна; $m \pm n\sqrt{k}$ хэлбэрээр бичнэ.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 = 2$-ийн язгуурууд $\pm\sqrt{2}$ — иррационал</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>квадрат тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>$ax^2 + bx + c = 0$ хэлбэрийн тэгшитгэл; энд $a, b, c$ — тоо, $a \ne 0$. $b = 0$ эсвэл $c = 0$ бол бүрэн биш квадрат тэгшитгэл гэнэ. Хамгийн ихдээ хоёр бодит язгууртай.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 5x + 6 = 0$: $a = 1$, $b = -5$, $c = 6$</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>квадрат тэгшитгэлийн томьёо</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>$ax^2 + bx + c = 0$ ($a \ne 0$) тэгшитгэлийн язгуурын ерөнхий томьёо: $x_{1,2} = \frac{-b \pm \sqrt{D}}{2a}$, $D = b^2 - 4ac$. Зөвхөн $D \ge 0$ үед бодит язгуур өгнө; бүтэн квадрат ялгах замаар гаргана.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>$2x^2 - 5x + 2 = 0$: $x = \frac{5 \pm 3}{4}$</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>параметр</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлд үсгээр тэмдэглэгдсэн боловч үл мэдэгдэгч биш, тогтмол гэж үзэх хэмжигдэхүүн. Параметрийн утгаас хамаарч шийдийн тоо, утга өөрчлөгдөх тул «ямар параметрт ... нөхцөл биелэх вэ» гэж судална.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 + kx + 9 = 0$-д $k$ параметр; $D = k^2 - 36$</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>талбай</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Хавтгай дүрсийн эзлэх хэсгийн хэмжээ, квадрат нэгжээр ($\text{см}^2$, $\text{м}^2$) хэмжинэ. Тэгш өнцөгтийнх $S = a \cdot b$, квадратынх $S = a^2$; талуудын холбоо өгөгдвөл квадрат тэгшитгэлд хүргэдэг.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Тал нь $x$ ба $x + 2$, талбай $15$: $x(x + 2) = 15$</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>хаалтын өмнө гаргах</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Олон гишүүнтийн бүх гишүүнд байгаа ерөнхий үржигдэхүүнийг хаалтын гадна бичиж үржвэр болгох хувиргалт: $ab + ac = a(b + c)$. Хуваарилах чанарын урвуу үйлдэл бөгөөд $A \cdot B = 0$ хэлбэрт оруулахад хэрэглэнэ.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 5x = x(x - 5)$</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>шийдийн тоо</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлийн ялгаатай бодит язгууруудын тоо. Квадрат тэгшитгэлийн хувьд дискриминантын тэмдгээр тодорхойлогдоно: $D &gt; 0$ — хоёр, $D = 0$ — нэг, $D &lt; 0$ — бодит шийдгүй.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 + 1 = 0$: $D = -4 &lt; 0$, бодит шийд $0$</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>язгуур (тэгшитгэлийн)</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Тэгшитгэлд орлуулахад түүнийг үнэн тоон тэнцэтгэл болгох үл мэдэгдэгчийн утга; шийд гэж ч нэрлэнэ. Квадрат тэгшитгэл хоёроос илүүгүй бодит язгууртай.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>$x = 2$ ба $x = -2$ нь $x^2 = 4$-ийн язгуурууд</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>язгууруудын нийлбэр ба үржвэр</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>$ax^2 + bx + c = 0$ тэгшитгэлийн язгуурууд $x_1 + x_2 = -\frac{b}{a}$, $x_1 x_2 = \frac{c}{a}$ (Виетийн теорем). Язгуурын тэгш хэмт илэрхийллийг эдгээрээр олно, жишээ нь $x_1^2 + x_2^2 = (x_1 + x_2)^2 - 2x_1 x_2$.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 4x + 3 = 0$: нийлбэр $4$, үржвэр $3$</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>T04</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>давхар тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>$a &lt; f(x) &lt; b$ хэлбэрийн, хоёр нөхцлийг зэрэг илэрхийлсэн тэнцэтгэл биш. Гурван хэсэгт ижил үйлдлийг зэрэг хийж $x$-ийг дунд нь ганцаарчилна; сөрөг тоонд хуваахад хоёр тэмдэг хоёулаа эргэнэ.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>$1 &lt; 2x + 3 &lt; 7 \iff -1 &lt; x &lt; 2$</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>завсар</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Тоон шулууны хоёр цэгийн хоорондох бүх бодит тоон олонлог. Захыг оруулбал дөрвөлжин $[\,]$, оруулахгүй бол дугуй $(\,)$ хаалт хэрэглэнэ; хязгааргүй завсарт $\infty$ талд үргэлж дугуй хаалт тавина. Тэнцэтгэл бишийн шийдийг завсраар бичдэг.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>$-1 \le x &lt; 3 \iff x \in [-1; 3)$</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>интервалын арга</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{P(x)}{Q(x)}$ эсвэл үржвэр хэлбэрийн тэнцэтгэл бишийг бодох арга: хүртвэр ба хуваарийн тэгүүдээр тоон шулууныг завсруудад хувааж, завсар бүрт илэрхийллийн тэмдгийг тогтооно. Тэмдэг зөвхөн эдгээр чухал цэгүүд дээр өөрчлөгдөж болно.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>$(x-1)(x-3) &lt; 0$: цэгүүд $1, 3$ → шийд $1 &lt; x &lt; 3$</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>квадрат тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>$ax^2 + bx + c &gt; 0$ ($&lt;$, $\le$, $\ge$), $a \ne 0$ хэлбэрийн тэнцэтгэл биш. Язгуурыг олж, параболын чиглэлийг ($a$-гийн тэмдэг) ашиглан илэрхийлэл эерэг, сөрөг байх завсруудыг тодорхойлно. $a &gt; 0$, $D &gt; 0$ үед язгууруудын хооронд сөрөг, гадна эерэг.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>$x^2 - 1 &lt; 0 \iff -1 &lt; x &lt; 1$</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>модуль</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Бодит тоо $a$-ийн модуль $|a| = a$ ($a \ge 0$ үед), $|a| = -a$ ($a &lt; 0$ үед). Геометрээр тоон шулуун дээрх $a$ цэгээс $0$ хүртэлх зай, $|a - b|$ нь $a$ ба $b$-ийн хоорондох зай. Үргэлж $|a| \ge 0$.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>$|-5| = 5$; $|x| &lt; 2 \iff -2 &lt; x &lt; 2$</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>нэгдэл</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>$A \cup B$ — $A$ эсвэл $B$-ийн ядаж нэгд нь орох бүх элементийн олонлог. Тэнцэтгэл бишид \"эсвэл\" холбоосоор холбогдсон нөхцлүүдийн шийдийг илэрхийлнэ.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>$x &lt; -1$ эсвэл $x &gt; 2$: $(-\infty; -1) \cup (2; +\infty)$</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>огтлолцол</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>$A \cap B$ — $A$ ба $B$ хоёуланд нь зэрэг орох элементийн олонлог. Тэнцэтгэл бишийн системд \"ба\" холбоосоор холбогдсон нөхцлүүдийн шийдийг илэрхийлнэ; тоон шулуун дээр давхцсан хэсэг юм.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>$[0; 5] \cap (3; 8) = (3; 5]$</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>рационал тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{P(x)}{Q(x)} &gt; 0$ ($&lt;$, $\le$, $\ge$) хэлбэрийн тэнцэтгэл биш, $P$, $Q$ олон гишүүнт. Хуваарийн тэмдэг тодорхойгүй тул түүгээр үржүүлэхгүй, интервалын аргаар бодно; $Q(x) = 0$ болгох цэгүүд шийдэд хэзээ ч орохгүй.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{x}{x - 1} &lt; 0 \iff 0 &lt; x &lt; 1$</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>сөрөг тоонд хуваах</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Тэнцэтгэл бишийн хоёр талыг сөрөг тоо $c$-д хуваах (үржүүлэх) үед тэмдэг эсрэгээр эргэнэ: $a &lt; b,\ c &lt; 0 \Rightarrow \frac{a}{c} &gt; \frac{b}{c}$. Учир нь сөрөг тоогоор үржүүлэхэд тоон шулуун дээрх дараалал урвуу болдог.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>$-2x &lt; 6 \Rightarrow x &gt; -3$</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр илэрхийллийг $&lt;$, $&gt;$, $\le$, $\ge$ тэмдгээр холбосон өгүүлбэр. Шийд нь түүнийг үнэн болгох хувьсагчийн бүх утгын олонлог бөгөөд ихэвчлэн завсар хэлбэртэй. Хоёр талд ижил тоо нэмэхэд эсвэл эерэг тоогоор үржүүлэхэд тэмдэг хэвээр, сөрөг тоогоор үржүүлэхэд эргэнэ.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>$2x &gt; 6 \iff x &gt; 3$, шийд нь $(3; +\infty)$</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>тэнцэтгэл бишийн систем</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Нэг хувьсагчийн хувьд зэрэг биелэх ёстой хэд хэдэн тэнцэтгэл биш, их хаалтаар бичнэ. Шийд нь тэнцэтгэл биш тус бүрийн шийдүүдийн огтлолцол; огтлолцол хоосон бол систем шийдгүй.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>$x &gt; 1$ ба $x &lt; 5$ системийн шийд: $1 &lt; x &lt; 5$</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>тэнцэтгэл бишийн тэмдэг</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>$&lt;$ (бага), $&gt;$ (их) — хатуу тэмдэг, хил орохгүй; $\le$, $\ge$ — сул тэмдэг, хил орно. Сөрөг тоогоор үржүүлэх, хуваахад тэмдэг эсрэгээр эргэнэ; тоон шулуун дээр хатуу хилийг хоосон, сул хилийг дүүрэн дугуйгаар тэмдэглэнэ.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>$x \le 2$: $2$ орно; $x &lt; 2$: $2$ орохгүй</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>эерэг тоонд хуваах</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Тэнцэтгэл бишийн хоёр талыг эерэг тоо $c$-д хуваах (үржүүлэх) үед тэмдэг хэвээр үлдэнэ: $a &lt; b,\ c &gt; 0 \Rightarrow \frac{a}{c} &lt; \frac{b}{c}$. Энэ нь $x$-ийг ганцаарчлахад хэрэглэгдэнэ.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>$4x \ge 8 \Rightarrow x \ge 2$</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>T05</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Ox тэнхлэгтэй огтлолцох</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Функцийн график $Ox$ тэнхлэгийг $y = 0$ үед огтолно; цэгүүдийн абсцисс нь $f(x) = 0$ тэгшитгэлийн язгуурууд. Ийм цэг байхгүй, нэг эсвэл хэд хэд байж болно.</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>$y = x^2 - 1$: $(-1; 0)$ ба $(1; 0)$</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Oy тэнхлэгтэй огтлолцох</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Функцийн график $Oy$ тэнхлэгийг $x = 0$ үед огтолно; огтлолцлын цэг $(0; f(0))$. Функц $x = 0$ үед тодорхойлогдох бол ийм цэг яг нэг байна. $y = kx + b$-д энэ нь $(0; b)$.</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>$y = 2x - 5$: $(0; -5)$</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>аргумент</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Функцийн бие даасан хувьсагч — $y = f(x)$-д $x$. Аргумент тодорхойлогдох мужаас утга авах бөгөөд түүний утга бүрт функцийн нэг утга харгалзана.</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = 3x$-д $x = 2$ аргументад $f(2) = 6$</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>буурах функц</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Завсар дахь дурын $x_1 &lt; x_2$-ийн хувьд $f(x_1) &gt; f(x_2)$ байвал $f$ энэ завсарт буурах функц. График зүүнээс баруун тийш доошилно.</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>$y = -3x + 2$ бүх тоон шулуун дээр буурна</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>давхар функц</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Нэг функцийн утгыг нөгөө функцийн аргумент болгосон нийлмэл функц $f(g(x))$; функцийн найрлагатай ижил ойлголт. Дотоод функц $g$ эхэлж, гадаад функц $f$ дараа нь хэрэглэгдэнэ.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = x + 1$, $g(x) = x^2$: $f(g(3)) = 10$</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>квадрат функц</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = ax^2 + bx + c$ ($a \ne 0$) хэлбэрийн функц. График нь парабол; $a$ нь чиглэл ба өргөнийг, $c$ нь $Oy$-тэй огтлолцох цэгийг, дискриминант $D$ нь $Ox$-тэй огтлолцох цэгийн тоог тодорхойлно.</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = x^2 - 4x + 3$: $a = 1$, $b = -4$, $c = 3$</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>налалт</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Шулууны хазайлтын хэмжүүр буюу өнцгийн коэффициент: $k = \frac{\Delta y}{\Delta x} = \frac{y_2 - y_1}{x_2 - x_1}$. $x$ нэгээр өөрчлөгдөхөд $y$ хэдээр өөрчлөгдөхийг заана; эерэг бол шулуун өгсөнө, сөрөг бол уруудна.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>$(0; 1)$, $(1; 4)$ цэгүүд: налалт $\frac{4 - 1}{1 - 0} = 3$</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>оройн цэг</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Параболын хамгийн доод ($a &gt; 0$) эсвэл хамгийн дээд ($a &lt; 0$) цэг. $y = ax^2 + bx + c$-д $x_0 = -\frac{b}{2a}$, $y_0 = f(x_0)$; $y = a(x - x_0)^2 + y_0$ хэлбэрээс шууд уншигдана.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>$y = (x - 1)^2 + 2$: орой $(1; 2)$</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>парабол</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>$y = ax^2 + bx + c$ ($a \ne 0$) квадрат функцийн график. $a &gt; 0$ бол салаа нь дээш, $a &lt; 0$ бол доош харна. Орой нь $x_0 = -\frac{b}{2a}$ цэгт, тэгш хэмийн тэнхлэг нь $x = x_0$ шулуун.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>$y = x^2$: орой $(0; 0)$, салаа дээш</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>параллель шулуун</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Нэг хавтгайд орших, огтлолцохгүй шулуунууд. $y = k_1x + b_1$ ба $y = k_2x + b_2$ параллель $\iff k_1 = k_2$ ба $b_1 \ne b_2$.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>$y = 2x + 1$ ба $y = 2x - 4$ параллель</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>тодорхойлогдох муж</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Функцийн томьёо утгатай байх аргументын бүх утгын олонлог, $D(f)$ гэж тэмдэглэнэ. Олохдоо хуваарь $\ne 0$, тэгш зэргийн язгуур доорх илэрхийлэл $\ge 0$, логарифмын доорх илэрхийлэл $&gt; 0$ гэх мэт нөхцлүүдийг тавина.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>$\sqrt{x - 1}$: $x \ge 1$; $\frac{1}{x}$: $x \ne 0$</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>тэгш хэмийн тэнхлэг</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Графикийг тусгахад өөртэйгөө давхцдаг шулуун. $y = ax^2 + bx + c$ параболын тэгш хэмийн тэнхлэг нь орой дундуур гарах босоо шулуун $x = -\frac{b}{2a}$; тэнхлэгээс ижил зайтай $x$-үүдэд функцийн утга тэнцүү.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>$y = x^2 - 4x$: тэнхлэг $x = 2$, $f(1) = f(3)$</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>функц</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>$X$ олонлогийн элемент $x$ бүрт $Y$ олонлогийн яг нэг элемент $y = f(x)$-ийг харгалзуулах дүрэм. $x$-ийг аргумент, $y$-ийг функцийн утга, $X$-ийг тодорхойлогдох муж гэнэ. Нэг $x$-д хоёр өөр $y$ харгалзаж болохгүй.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = 2x + 1$: $f(3) = 7$</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>функцийн найрлага</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>$(f \circ g)(x) = f(g(x))$ — эхлээд $g$, дараа нь $f$-ийг хэрэглэсэн функц. $g(x)$ нь $f$-ийн тодорхойлогдох мужид орох ёстой. Ерөнхийдөө $f(g(x)) \ne g(f(x))$.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = 2x$, $g(x) = x + 1$: $f(g(1)) = 4$, $g(f(1)) = 3$</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>функцийн тэг</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = 0$ байх аргументын утга, өөрөөр хэлбэл $f(x) = 0$ тэгшитгэлийн язгуур. Геометрээр график $Ox$ тэнхлэгтэй огтлолцох (шүргэх) цэгийн абсцисс.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = x - 2$-ийн тэг: $x = 2$</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>функцийн утга</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Аргументын тодорхой утга $x = a$-д харгалзах $f(a)$ тоо; томьёонд $x$-ийн оронд $a$-г орлуулж олно. Функцийн бүх утгын олонлогийг утгын муж $E(f)$ гэнэ.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>$f(x) = x^2 + 1$ бол $f(2) = 5$</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>хамгийн их утга</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Функцийн тодорхойлогдох муж (эсвэл өгөгдсөн завсар) дахь бүх утгаас их буюу тэнцүү утга: бүх $x$-д $f(x) \le f(x_0)$. $a &lt; 0$ үед квадрат функц хамгийн их утгаа оройд авна.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>$y = -x^2 + 3$-ийн хамгийн их утга $3$ ($x = 0$ үед)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>хуваарь тэг байж болохгүй</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Тэгд хуваах үйлдэл тодорхойлогдоогүй тул $\frac{P(x)}{Q(x)}$ бутархай зөвхөн $Q(x) \ne 0$ үед утгатай. Иймд $Q(x) = 0$-ийн язгууруудыг тодорхойлогдох мужаас хасна.</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{1}{x + 2}$: $x \ne -2$</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>чөлөөт гишүүн</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Олон гишүүнт эсвэл функцийн хувьсагчгүй гишүүн: $y = kx + b$-д $b$, $ax^2 + bx + c$-д $c$. Энэ нь $x = 0$ үеийн функцийн утга буюу графикийн $Oy$-тэй огтлолцох цэгийн ордината.</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>$y = x^2 - 3x + 7$-ийн чөлөөт гишүүн $7$</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>шугаман функц</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>$y = kx + b$ хэлбэрийн функц, энд $k$, $b$ тогтмол тоо. График нь шулуун: $k$ нь өнцгийн коэффициент, $b$ нь $Oy$-тэй огтлолцох цэгийн ордината. $k &gt; 0$ үед өсөх, $k &lt; 0$ үед буурах.</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>$y = 2x - 3$: $k = 2$, $b = -3$</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>шулууны тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Шулуун дээрх цэгүүдийн координат, зөвхөн тэдгээр нь хангах тэгшитгэл. Налалттай хэлбэр $y = kx + b$; $(x_1; y_1)$ цэг ба налалтаар $y - y_1 = k(x - x_1)$. Босоо шулуун $x = a$ хэлбэртэй.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>$(0; 2)$-ыг дайрсан, $k = 3$: $y = 3x + 2$</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>өнцгийн коэффициент</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>$y = kx + b$ шулууны $k$ коэффициент; $k = \tan\alpha$, энд $\alpha$ нь шулуун ба $Ox$ тэнхлэгийн эерэг чиглэлийн хоорондох өнцөг. Хоёр цэгээр $k = \frac{y_2 - y_1}{x_2 - x_1}$. $k &gt; 0$ бол функц өсөх, $k &lt; 0$ бол буурах.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>$y = 3x - 1$-д $k = 3$: $x$ нэгээр өсөхөд $y$ $3$-аар өснө</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>өсөх функц</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Завсар дахь дурын $x_1 &lt; x_2$-ийн хувьд $f(x_1) &lt; f(x_2)$ байвал $f$ энэ завсарт өсөх функц. График зүүнээс баруун тийш дээшилнэ.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>$y = 2x + 1$ бүх тоон шулуун дээр өснө</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>T06</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>буурах</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Функц $I$ завсарт буурах гэдэг нь $x_1 &lt; x_2$ бүрийн хувьд $f(x_1) &gt; f(x_2)$ байх явдал. $0 &lt; a &lt; 1$ үед $y = a^x$ буурах тул $a^m &lt; a^n \Leftrightarrow m &gt; n$ — тэнцэтгэл бишийн тэмдэг эргэнэ.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>$y = 0{,}5^x$: $0{,}5^1 &gt; 0{,}5^2$</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>ижил суурь</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр зэрэг нэг ижил тоон суурьтай байх тохиолдол: $a^m$ ба $a^n$. Ижил суурьтай зэрэгт $a^m \cdot a^n = a^{m+n}$, $a^m : a^n = a^{m-n}$ дүрэм хэрэглэгдэх ба $a &gt; 0$, $a \ne 1$ үед $a^m = a^n \Leftrightarrow m = n$.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>$8^x = 4$: $2^{3x} = 2^2$ болгон ижил суурьт шилжүүлнэ</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>илтгэгч тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч нь зэргийн илтгэгчид орсон тэгшитгэл, жишээ нь $a^{f(x)} = b$ ($a &gt; 0$, $a \ne 1$). Үндсэн аргууд: ижил суурьт шилжүүлж $a^{f(x)} = a^{g(x)} \Leftrightarrow f(x) = g(x)$ ашиглах, $t = a^x$ ($t&gt;0$) орлуулга, логарифмчлах.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>$3^{x-1} = 9 \Rightarrow x - 1 = 2 \Rightarrow x = 3$</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>илтгэгч тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч нь илтгэгчид орсон тэнцэтгэл биш, жишээ нь $a^{f(x)} &gt; a^{g(x)}$. $a &gt; 1$ бол $f(x) &gt; g(x)$ (тэмдэг хадгалагдана), $0 &lt; a &lt; 1$ бол $f(x) &lt; g(x)$ (тэмдэг эргэнэ).</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>$0{,}5^x &gt; 4 = 0{,}5^{-2} \Rightarrow x &lt; -2$</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>илтгэгч функц</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>$y = a^x$ ($a &gt; 0$, $a \ne 1$) хэлбэрийн функц. Тодорхойлогдох муж бүх бодит тоо, утгын муж $y &gt; 0$; график $(0; 1)$ цэгийг дайрна. $a &gt; 1$ бол өсөх, $0 &lt; a &lt; 1$ бол буурах.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>$y = 2^x$: $x = -1, 0, 3$ үед $y = \frac{1}{2}, 1, 8$</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>илтгэгч өсөлт</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Хэмжигдэхүүн тэнцүү хугацаанд тогтмол дахин өсөх процесс: $N(t) = N_0 \cdot a^t$ ($a &gt; 1$), энд $N_0$ — анхны утга, $a$ — нэгж хугацааны өсөлтийн коэффициент. $0 &lt; a &lt; 1$ бол илтгэгч бууралт болно.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>$N(t) = 50 \cdot 3^t$: 2 цагийн дараа $50 \cdot 9 = 450$</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>орлуулга</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Илэрхийллийн нэг хэсгийг шинэ хувьсагчаар тэмдэглэж ($t = g(x)$) бодлогыг хялбар хэлбэрт шилжүүлэх арга. Шинэ хувьсагчийн утгын мужийг ($a^x$-д $t &gt; 0$) заавал тусгаж, эцэст нь буцаан орлуулж $x$-ийг олно.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>$4^x - 3 \cdot 2^x + 2 = 0$: $t = 2^x$ гэвэл $t^2 - 3t + 2 = 0$</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>суурь</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>$a^n$ зэргийн давтан үржигдэх $a$ тоо; $n$ нь илтгэгч. Илтгэгч функц $y = a^x$-д суурь $a &gt; 0$, $a \ne 1$ байх ёстой бөгөөд $a$-гийн утга функцийн өсөх/буурахыг тодорхойлно.</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>$5^3 = 5 \cdot 5 \cdot 5$: суурь $5$, илтгэгч $3$</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>тэг зэрэг</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Тэгээс ялгаатай дурын тооны тэг зэрэг $1$: $a^0 = 1$ ($a \ne 0$). Энэ нь $\frac{a^n}{a^n} = a^{n-n}$ дүрмээс гардаг; $0^0$ тодорхойлогдохгүй.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>$7^0 = 1$, $(-3)^0 = 1$</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>өсөх</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Функц $I$ завсарт өсөх гэдэг нь $x_1 &lt; x_2$ бүрийн хувьд $f(x_1) &lt; f(x_2)$ байх явдал. Илтгэгч функц $y = a^x$ нь $a &gt; 1$ үед бүх тоон шулуун дээр өснө, тиймээс $a^m &lt; a^n \Leftrightarrow m &lt; n$.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>$y = 3^x$: $3^1 &lt; 3^2$, учир нь $1 &lt; 2$</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>T07</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Аравтын логарифмын тэмдэглэгээ: $\lg b = \log_{10} b$, $b &gt; 0$. Натурал логарифм $\ln b = \log_e b$-ээс ялгаатай; $\lg b = c \Leftrightarrow 10^c = b$.</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>$\lg 100 = 2$, учир нь $10^2 = 100$</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>logₐ 1</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Нэгийн логарифм аль ч зөвшөөрөгдөх сууриар тэг: $\log_a 1 = 0$ ($a &gt; 0$, $a \ne 1$), учир нь $a^0 = 1$. Логарифм функцийн график $(1; 0)$ цэгийг дайрдаг нь үүнээс гарна.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>$\log_7 1 = 0$, $\lg 1 = 0$</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>logₐ a</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Суурь ба аргумент тэнцүү логарифм: $a &gt; 0$, $a \ne 1$ үед $\log_a a = 1$, учир нь $a^1 = a$. Ерөнхийдөө $\log_a a^n = n$.</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>$\log_5 5 = 1$, $\lg 10 = 1$</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>аравтын логарифм</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>10 суурьтай логарифм: $\lg b = \log_{10} b$ ($b &gt; 0$). $\lg 10^n = n$ тул 10-ын бүхэл зэргийн логарифм бүхэл тоо; $0 &lt; b &lt; 1$ үед $\lg b &lt; 0$.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>$\lg 1000 = 3$, $\lg 0{,}1 = -1$</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>зэргийн логарифм</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Зэргийн логарифм нь илтгэгчийг логарифмын өмнө гаргана: $\log_a b^n = n \log_a b$ ($a &gt; 0$, $a \ne 1$, $b &gt; 0$, $n$ — дурын бодит). Язгуурт ч хэрэглэгдэнэ: $\log_a \sqrt{b} = \frac{1}{2} \log_a b$.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 9^5 = 5 \log_3 9 = 10$</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>илүү шийд</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Хувиргалтын явцад (логарифмыг нэгтгэх, квадрат зэрэгт дэвшүүлэх г.м.) тодорхойлогдох муж өргөссөнөөс гарсан, анхны тэгшитгэлийг хангадаггүй язгуур. Иймд язгуур бүрийг ТМ-ээр эсвэл анхны тэгшитгэлд орлуулж шалгаж хаяна.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>$\lg x + \lg (x-3) = 1$: $x^2 - 3x - 10 = 0$, $x = -2$ — илүү шийд</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>логарифм</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>$a &gt; 0$, $a \ne 1$, $b &gt; 0$ үед $\log_a b$ нь $a^c = b$ байх цорын ганц $c$ тоо: $\log_a b = c \Leftrightarrow a^c = b$. Өөрөөр хэлбэл суурийг $b$ болгохын тулд дэвшүүлэх илтгэгч. Логарифм бол илтгэгч функцийн урвуу үйлдэл.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 8 = 3$, учир нь $2^3 = 8$</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>логарифм тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч нь логарифмын аргумент эсвэл сууринд орсон тэгшитгэл. Бодохдоо эхлээд тодорхойлогдох мужийг (аргумент $&gt; 0$, суурь $&gt; 0$, $\ne 1$) олж, $\log_a f(x) = c \Leftrightarrow f(x) = a^c$ эсвэл $\log_a f = \log_a g \Leftrightarrow f = g$ ашиглана. Гарсан язгуурыг ТМ-ээр шүүнэ.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 (x+1) = 2 \Rightarrow x + 1 = 9 \Rightarrow x = 8$</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>логарифм тэнцэтгэл биш</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч нь логарифмын дор орсон тэнцэтгэл биш. $a &gt; 1$ бол $\log_a f &gt; \log_a g \Leftrightarrow f &gt; g &gt; 0$, $0 &lt; a &lt; 1$ бол $0 &lt; f &lt; g$ (тэмдэг эргэнэ); тодорхойлогдох мужийг хариунд заавал тусгана.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 x &gt; 2 \Rightarrow x &gt; 9$</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>логарифмын суурь</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>$\log_a b$ бичлэгийн $a$ тоо — аргументыг гаргахын тулд зэрэгт дэвшүүлэх тоо. Нөхцөл: $a &gt; 0$, $a \ne 1$; $a &gt; 1$ бол логарифм функц өснө, $0 &lt; a &lt; 1$ бол буурна.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>$\log_3 9$-ийн суурь $3$; $\log_1 5$ тодорхойлогдохгүй</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>логарифмын чанар</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>$a &gt; 0$, $a \ne 1$, $b, c &gt; 0$ үед хүчинтэй адилтгалууд: $\log_a (bc) = \log_a b + \log_a c$, $\log_a \frac{b}{c} = \log_a b - \log_a c$, $\log_a b^n = n \log_a b$. Мөн $\log_a a = 1$, $\log_a 1 = 0$, $a^{\log_a b} = b$.</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 12 - \log_2 3 = \log_2 4 = 2$</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>суурь солих</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Логарифмыг өөр суурьт шилжүүлэх томьёо: $\log_a b = \frac{\log_c b}{\log_c a}$ ($a, c &gt; 0$, $a, c \ne 1$, $b &gt; 0$). Онцгой тохиолдол: $\log_a b = \frac{1}{\log_b a}$.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>$\log_9 27 = \frac{\log_3 27}{\log_3 9} = \frac{3}{2}$</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>тодорхойлолт</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Ойлголтын утгыг нарийн тогтоосон математикийн өгүүлбэр. Логарифмын сэдэвт гол нь $\log_a b = c \Leftrightarrow a^c = b$ ($a &gt; 0$, $a \ne 1$, $b &gt; 0$) тодорхойлолт бөгөөд энгийн логарифм тэгшитгэлийг шууд зэргийн тэгшитгэлд шилжүүлнэ.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Тодорхойлолтоор $\log_2 x = 5 \Leftrightarrow x = 2^5$</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>ялгаврын логарифм</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Ижил суурьтай хоёр логарифмын ялгавар нь ноогдворын логарифмтай тэнцүү: $\log_a b - \log_a c = \log_a \frac{b}{c}$ ($a &gt; 0$, $a \ne 1$, $b, c &gt; 0$). $\log_a (b - c)$-тэй андуурч болохгүй.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 24 - \log_2 3 = \log_2 8 = 3$</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>үржвэрийн логарифм</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Эерэг тоонуудын үржвэрийн логарифм нь логарифмуудын нийлбэр: $\log_a (bc) = \log_a b + \log_a c$ ($a &gt; 0$, $a \ne 1$, $b, c &gt; 0$). $\log_a (b + c)$-д ийм задаргаа байхгүй.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>$\log_2 (4 \cdot 8) = 2 + 3 = 5$</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>T08</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>II мөчлөг</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Нэгж тойргийн $90^\circ &lt; \alpha &lt; 180^\circ$ өнцгүүдэд харгалзах хэсэг (зүүн дээд дөрөвний нэг). Энд синус эерэг, косинус, тангенс, котангенс сөрөг.</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>$150^\circ$ II мөчлөгт: $\sin 150^\circ &gt; 0$, $\cos 150^\circ &lt; 0$</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>адилтгал хувиргалт</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Хувьсагчийн тодорхойлогдох мужид илэрхийллийн утгыг өөрчлөхгүйгээр хэлбэрийг нь өөрчлөх хувиргалт. Тригонометрт ихэвчлэн функцуудыг синус, косинусаар илэрхийлж, үндсэн адилтгалыг хэрэглэнэ.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>$\sin\alpha \cdot \operatorname{ctg}\alpha = \sin\alpha \cdot \frac{\cos\alpha}{\sin\alpha} = \cos\alpha$</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ангижруулах томьёо</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>$90^\circ \pm \alpha$, $180^\circ \pm \alpha$, $360^\circ - \alpha$ гэх мэт өнцгийн тригонометрийн функцийг хурц өнцөг $\alpha$-ийн функцээр илэрхийлэх томьёо. Тэмдгийг анхны өнцгийн мөчлөг дэх функцийн тэмдгээр тодорхойлно.</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>$\cos 120^\circ = \cos(180^\circ - 60^\circ) = -\cos 60^\circ = -\frac{1}{2}$</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>градус</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Бүтэн эргэлтийн $\frac{1}{360}$ хэсэгтэй тэнцүү өнцгийн хэмжээний нэгж. Радиантай $180^\circ = \pi$ радиан гэсэн хамаарлаар холбогдоно: $\alpha^\circ = \alpha \cdot \frac{\pi}{180}$ радиан.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{\pi}{6}$ рад $= \frac{180^\circ}{6} = 30^\circ$</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>косинус</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Тэгш өнцөгт гурвалжны хурц өнцөг $\alpha$-ийн налсан катетыг гипотенузад харьцуулсан харьцаа: $\cos\alpha = \frac{b}{c}$. Ерөнхийд нь нэгж тойргийн $\alpha$ өнцөгт харгалзах цэгийн абсциссаар тодорхойлно; утга нь $[-1; 1]$ мужид оршино.</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>$\cos 60^\circ = \frac{1}{2}$, $\cos 180^\circ = -1$</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>котангенс</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{ctg}\alpha = \frac{\cos\alpha}{\sin\alpha}$, $\sin\alpha \ne 0$ үед тодорхойлогдоно. Тэгш өнцөгт гурвалжинд налсан катетыг эсрэг катетад харьцуулсан харьцаа; $\operatorname{tg}\alpha \cdot \operatorname{ctg}\alpha = 1$.</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{ctg}45^\circ = 1$, $\operatorname{ctg}60^\circ = \frac{\sqrt{3}}{3}$</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>нэгж тойрог</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Координатын эх дээр төвтэй, радиус нь $1$ тойрог. $Ox$ тэнхлэгээс цагийн зүүний эсрэг $\alpha$ өнцгөөр эргүүлсэн цэг $(\cos\alpha;\ \sin\alpha)$ координаттай тул дурын өнцгийн синус, косинусыг тодорхойлдог.</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>$90^\circ$-д $(0; 1)$ цэг: $\cos 90^\circ = 0$, $\sin 90^\circ = 1$</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>радиан</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Нумын урт нь радиустай тэнцүү байх төв өнцгийн хэмжээ. Бүтэн эргэлт $2\pi$ радиан тул $\pi$ радиан $= 180^\circ$, $1$ радиан $\approx 57{,}3^\circ$.</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>$90^\circ = \frac{\pi}{2}$ рад, $60^\circ = \frac{\pi}{3}$ рад</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>синус</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Тэгш өнцөгт гурвалжны хурц өнцөг $\alpha$-ийн эсрэг катетыг гипотенузад харьцуулсан харьцаа: $\sin\alpha = \frac{a}{c}$. Ерөнхийд нь нэгж тойргийн $\alpha$ өнцөгт харгалзах цэгийн ординатаар тодорхойлно; утга нь $[-1; 1]$ мужид оршино.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>$\sin 30^\circ = \frac{1}{2}$, $\sin 90^\circ = 1$</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>тангенс</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{tg}\alpha = \frac{\sin\alpha}{\cos\alpha}$, $\cos\alpha \ne 0$ үед тодорхойлогдоно. Тэгш өнцөгт гурвалжинд хурц өнцгийн эсрэг катетыг налсан катетад харьцуулсан харьцаа.</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>$\operatorname{tg}45^\circ = 1$, $\operatorname{tg}60^\circ = \sqrt{3}$</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>тойргийн өнцөг</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Нэгж тойрог дээр $Ox$ тэнхлэгийн эерэг чиглэлээс эргүүлж хэмжсэн дурын хэмжээтэй өнцөг; цагийн зүүний эсрэг эргэлт эерэг. $360^\circ$-аас их ба сөрөг өнцөг ч тодорхойлогдоно, $360^\circ$-аар ялгаатай өнцгүүд нэг цэгт харгалзана.</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>$390^\circ$ ба $30^\circ$ нэг цэгт харгалзана</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>тригонометр тэгшитгэл</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Үл мэдэгдэгч нь тригонометрийн функцийн аргумент дотор орсон тэгшитгэл. Функцууд үелэх тул шийд олон байдаг; өгсөн завсар дахь бүх шийдийг нэгж тойргоор олно.</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>$\cos x = 0$, $[0; 2\pi]$ завсарт: $x = \frac{\pi}{2}$; $x = \frac{3\pi}{2}$</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>тригонометрийн үндсэн адилтгал</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Ямар ч $\alpha$ өнцгийн хувьд $\sin^2\alpha + \cos^2\alpha = 1$ биелнэ — нэгж тойрог дээрх Пифагорын теорем. Нэг функцийн утгаас нөгөөгийнхийг олоход хэрэглэх ба тэмдгийг өнцгийн мөчлөгөөр сонгоно.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>$\sin\alpha = 0{,}6$, $\alpha$ хурц бол $\cos\alpha = \sqrt{1 - 0{,}36} = 0{,}8$</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>тусгай өнцөг</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Тригонометрийн функцийн утга нь язгуураар яг илэрхийлэгддэг $0^\circ$, $30^\circ$, $45^\circ$, $60^\circ$, $90^\circ$ өнцгүүд. Утгыг нь тэгш талт ба тэгш өнцөгт адил хажуут гурвалжнаас гаргадаг тул цээжлэх шаардлагатай.</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>$\sin 45^\circ = \cos 45^\circ = \frac{\sqrt{2}}{2}$</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>хурц өнцөг</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>$0^\circ$-аас их, $90^\circ$-аас бага өнцөг ($0 &lt; \alpha &lt; \frac{\pi}{2}$). Нэгж тойргийн I мөчлөгт оршдог тул бүх тригонометрийн функц нь эерэг утгатай.</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>$\alpha = 40^\circ$ хурц тул $\sin\alpha &gt; 0$, $\cos\alpha &gt; 0$</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>хялбарчлах</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Илэрхийллийг адилтгал хувиргалтаар түүнтэй тэнцүү, илүү энгийн хэлбэрт шилжүүлэх. Хувиргалт бүр тодорхойлогдох мужид хүчинтэй байх ёстой, жишээ нь тэгээс ялгаатай үржигдэхүүнийг л хураана.</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>$\frac{\sin^2\alpha}{\sin\alpha} = \sin\alpha$ ($\sin\alpha \ne 0$)</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>үелэх чанар</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>$f(x + T) = f(x)$ бүх $x$-д биелэх $T \ne 0$ тоо оршдог бол $f$ үелэх функц, хамгийн бага эерэг $T$ нь үе. Синус, косинусын үе $2\pi$ ($360^\circ$), тангенсынх $\pi$.</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>$\sin 390^\circ = \sin(30^\circ + 360^\circ) = \sin 30^\circ$</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>үндсэн адилтгал</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Тригонометрийн үндсэн адилтгал: ямар ч $\alpha$-д $\sin^2\alpha + \cos^2\alpha = 1$. Үүнээс $1 + \operatorname{tg}^2\alpha = \frac{1}{\cos^2\alpha}$ зэрэг бусад адилтгал гарна.</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>$(1-\sin\alpha)(1+\sin\alpha) = 1 - \sin^2\alpha = \cos^2\alpha$</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>T09</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Бернуллийн схем</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>$A$ үзэгдэл бүрт ижил $p$ магадлалтай $n$ бие даасан туршилтын дараалал. $A$ яг $k$ удаа биелэх магадлал $P_n(k) = C_n^k p^k (1-p)^{n-k}$.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Зоосыг $3$ удаа: $P_3(2) = C_3^2 \cdot \frac{1}{8} = \frac{3}{8}$</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>байрлуулал</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>$n$ ялгаатай элементээс $k$-г сонгож, дарааллыг нь харгалзан байрлуулсан эрэмбэлэгдсэн цуваа. Тоо нь $A_n^k = \frac{n!}{(n-k)!} = n(n-1)\cdots(n-k+1)$.</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>$5$ гүйгчээс 1, 2-р байр: $A_5^2 = 5 \cdot 4 = 20$</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>бие даасан туршилт</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Нэг туршилтын үр дүн нөгөө туршилтын үр дүнгийн магадлалд нөлөөлдөггүй туршилтууд. Ийм туршилтуудын үр дүнгүүд зэрэг гарах магадлал нь тус бүрийн магадлалын үржвэртэй тэнцүү.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Зоосыг $3$ удаа хаяхад ССС: $(\frac{1}{2})^3 = \frac{1}{8}$</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>бие даасан үзэгдэл</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Нэг нь биелэх эсэх нь нөгөөгийнх нь магадлалд нөлөөлдөггүй үзэгдлүүд. Тодорхойлолтоор $A$, $B$ бие даасан нь $P(A \cap B) = P(A) \cdot P(B)$ байх явдал.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр зоосонд хоёулаа сүлд: $\frac{1}{2} \cdot \frac{1}{2} = \frac{1}{4}$</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>боломжит үр дүн</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Туршилтын үед гарч болох, хоорондоо давхцахгүй энгийн үр дүн бүр. Бүх боломжит үр дүнгийн тоо $n$ нь сонгодог магадлалын томьёоны хуваарь болно.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Зоос хаяхад: сүлд, тоо — $n = 2$</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>боломжит үр дүнгийн огторгуй</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Туршилтын бүх боломжит энгийн үр дүнгийн олонлог, ихэвчлэн $\Omega$ гэж тэмдэглэнэ. Үзэгдэл бүр нь $\Omega$-ийн дэд олонлог бөгөөд $P(\Omega) = 1$.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр шоо: $\Omega = \{(a; b)\}$, $|\Omega| = 6 \cdot 6 = 36$</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>буцаалгүй сонголт</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Авсан элементийг буцааж хийлгүйгээр дараагийн элементийг сонгох арга. Авалт бүр олонлогийн бүрэлдэхүүнийг өөрчилдөг тул дараагийн магадлал нөхцөлт магадлал болж, үзэгдлүүд бие даасан биш.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>$4$ улаан, $1$ цагаанаас $2$ улаан: $\frac{4}{5} \cdot \frac{3}{4} = \frac{3}{5}$</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>дараалал чухал</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Ижил элементүүдийн байрлалын дарааллыг өөрчлөхөд өөр үр дүн гарах тохиолдол. Ийм сонголтыг байрлуулал $A_n^k$ эсвэл сэлгэмэл $P_n$-ээр тоолно.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Ахлагч А, орлогч Б ба эсрэгээр нь — $2$ өөр хуваарилалт</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>дараалал чухал биш</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Сонгосон элементүүдийн байрлалын дарааллыг өөрчлөхөд шинэ сонголт үүсэхгүй тохиолдол. Ийм сонголтыг хэсэглэл $C_n^k$-аар тоолно.</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>А, Б ба Б, А нь нэг баг; $4$ хүнээс $2$: $C_4^2 = 6$</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>комбинаторик</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Төгсгөлөг олонлогийн элементүүдийг тодорхой нөхцөлөөр сонгох, байрлуулах аргуудын тоог судалдаг математикийн салбар. Үндсэн хэрэгсэл нь нэмэх ба үржүүлэх дүрэм, сэлгэмэл, байрлуулал, хэсэглэл.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>$4$ үсгийг $4! = 24$ янзаар өрнө</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>магадлал</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Үзэгдэл биелэх боломжийн тоон хэмжүүр, $0 \le P(A) \le 1$. Бүх үр дүн адил боломжтой үед сонгодог тодорхойлолт $P(A) = \frac{m}{n}$, энд $m$ — таатай, $n$ — бүх боломжит үр дүнгийн тоо.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Шоо хаяхад $6$ буух: $P = \frac{1}{6}$</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>магадлалын үржвэр</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр үзэгдэл зэрэг биелэх магадлалын томьёо: $P(A \cap B) = P(A) \cdot P(B \mid A)$. $A$, $B$ бие даасан бол $P(B \mid A) = P(B)$ тул $P(A \cap B) = P(A) \cdot P(B)$.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Хоёр шоонд хоёулаа $6$: $\frac{1}{6} \cdot \frac{1}{6} = \frac{1}{36}$</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>нийцтэй үзэгдэл</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Нэг туршилтад зэрэг биелж болох ($A \cap B \ne \varnothing$) үзэгдлүүд. Тэдгээрийн нэгдлийн магадлалыг $P(A \cup B) = P(A) + P(B) - P(A \cap B)$-ээр олно.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Шоонд «тэгш» ба «3-т хуваагдах» хоёулаа $6$-д биелнэ</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>сэлгэмэл</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>$n$ ялгаатай элементийг бүгдийг нь тодорхой дарааллаар байрлуулсан нэг байрлал. Бүх сэлгэмлийн тоо $P_n = n!$ бөгөөд үржүүлэх дүрмээс гарна.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>$3$ номыг тавиурт $P_3 = 3! = 6$ янзаар өрнө</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>таатай үр дүн</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Туршилтын боломжит үр дүнгүүдээс тухайн $A$ үзэгдэл биелэхэд хүргэдэг үр дүн. Таатай үр дүнгийн тоо $m$ нь сонгодог магадлалын $P(A) = \frac{m}{n}$ томьёоны хүртвэр болно.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Шоонд тэгш тоо буух: таатай нь $2, 4, 6$ — $m = 3$</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
           <t>факториал</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>n! = 1·2·…·n.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>4! = 24</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Натурал $n$-ийн факториал нь $1$-ээс $n$ хүртэлх бүх натурал тооны үржвэр: $n! = 1 \cdot 2 \cdot \ldots \cdot n$; тохиролцоогоор $0! = 1$. Рекуррент хамаарал $n! = n \cdot (n-1)!$ биелнэ.</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>$4! = 1 \cdot 2 \cdot 3 \cdot 4 = 24$</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>хуваагдах</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Бүхэл $a$ тоо бүхэл $b \ne 0$ тоонд хуваагдана гэдэг нь $a = b \cdot k$ байх бүхэл $k$ оршино гэсэн үг, $b \mid a$ гэж тэмдэглэнэ. Өөрөөр хэлбэл $a$-г $b$-д хуваахад үлдэгдэл $0$.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>$3 \mid 9$, учир нь $9 = 3 \cdot 3$; $10$ нь $3$-т хуваагдахгүй</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>хэсэглэл</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>$n$ ялгаатай элементээс дараалал харгалзахгүйгээр сонгосон $k$ элементтэй дэд олонлог. Тоо нь $C_n^k = \frac{n!}{k!\,(n-k)!}$, мөн $C_n^k = C_n^{n-k}$.</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>$5$ хүнээс $2$-ыг: $C_5^2 = \frac{5 \cdot 4}{2} = 10$</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>эсрэг үзэгдэл</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>$A$ үзэгдэл биелэхгүй байх үзэгдэл, $\bar A$ гэж тэмдэглэнэ. $A$ ба $\bar A$ үл нийцэх бөгөөд нийлээд бүх огторгуйг бүрдүүлэх тул $P(\bar A) = 1 - P(A)$.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>$P(A) = 0{,}2$ бол $P(\bar A) = 0{,}8$</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>үржүүлэх дүрэм</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Эхний алхмыг $m$ янзаар, тэр бүрд хоёр дахь алхмыг $n$ янзаар хийж болох бол хоёр алхмыг дараалан $m \cdot n$ янзаар хийнэ. Олон алхамтай үед ч сонголтын тоонуудыг үржүүлнэ.</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>$3$ цамц, $2$ малгай: $3 \cdot 2 = 6$ хослол</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D33"/>
+  <autoFilter ref="A1:D169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>